--- a/apps/web/public/templates/roster_import_template.xlsx
+++ b/apps/web/public/templates/roster_import_template.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
+  <dimension ref="A1:P1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -481,7 +481,8 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -557,6 +558,11 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>First Degree Date</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
@@ -624,7 +630,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" s="4" t="n">
+        <v>46270</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Member</t>
         </is>
@@ -635,5992 +644,6990 @@
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="6" t="n"/>
       <c r="M3" s="6" t="n"/>
+      <c r="O3" s="6" t="n"/>
     </row>
     <row r="4">
       <c r="E4" s="5" t="n"/>
       <c r="J4" s="5" t="n"/>
       <c r="K4" s="6" t="n"/>
       <c r="M4" s="6" t="n"/>
+      <c r="O4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="E5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
       <c r="K5" s="6" t="n"/>
       <c r="M5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="E6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="6" t="n"/>
       <c r="M6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="E7" s="5" t="n"/>
       <c r="J7" s="5" t="n"/>
       <c r="K7" s="6" t="n"/>
       <c r="M7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="E8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
       <c r="K8" s="6" t="n"/>
       <c r="M8" s="6" t="n"/>
+      <c r="O8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="E9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
       <c r="K9" s="6" t="n"/>
       <c r="M9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="E10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
       <c r="K10" s="6" t="n"/>
       <c r="M10" s="6" t="n"/>
+      <c r="O10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="E11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="6" t="n"/>
       <c r="M11" s="6" t="n"/>
+      <c r="O11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="E12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="6" t="n"/>
       <c r="M12" s="6" t="n"/>
+      <c r="O12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="E13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="6" t="n"/>
       <c r="M13" s="6" t="n"/>
+      <c r="O13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="E14" s="5" t="n"/>
       <c r="J14" s="5" t="n"/>
       <c r="K14" s="6" t="n"/>
       <c r="M14" s="6" t="n"/>
+      <c r="O14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="E15" s="5" t="n"/>
       <c r="J15" s="5" t="n"/>
       <c r="K15" s="6" t="n"/>
       <c r="M15" s="6" t="n"/>
+      <c r="O15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="E16" s="5" t="n"/>
       <c r="J16" s="5" t="n"/>
       <c r="K16" s="6" t="n"/>
       <c r="M16" s="6" t="n"/>
+      <c r="O16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="E17" s="5" t="n"/>
       <c r="J17" s="5" t="n"/>
       <c r="K17" s="6" t="n"/>
       <c r="M17" s="6" t="n"/>
+      <c r="O17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="E18" s="5" t="n"/>
       <c r="J18" s="5" t="n"/>
       <c r="K18" s="6" t="n"/>
       <c r="M18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="E19" s="5" t="n"/>
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="6" t="n"/>
       <c r="M19" s="6" t="n"/>
+      <c r="O19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="E20" s="5" t="n"/>
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="6" t="n"/>
       <c r="M20" s="6" t="n"/>
+      <c r="O20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="E21" s="5" t="n"/>
       <c r="J21" s="5" t="n"/>
       <c r="K21" s="6" t="n"/>
       <c r="M21" s="6" t="n"/>
+      <c r="O21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="E22" s="5" t="n"/>
       <c r="J22" s="5" t="n"/>
       <c r="K22" s="6" t="n"/>
       <c r="M22" s="6" t="n"/>
+      <c r="O22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="E23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
       <c r="K23" s="6" t="n"/>
       <c r="M23" s="6" t="n"/>
+      <c r="O23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="E24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="6" t="n"/>
       <c r="M24" s="6" t="n"/>
+      <c r="O24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="E25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
       <c r="K25" s="6" t="n"/>
       <c r="M25" s="6" t="n"/>
+      <c r="O25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="E26" s="5" t="n"/>
       <c r="J26" s="5" t="n"/>
       <c r="K26" s="6" t="n"/>
       <c r="M26" s="6" t="n"/>
+      <c r="O26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="E27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="6" t="n"/>
       <c r="M27" s="6" t="n"/>
+      <c r="O27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="E28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="6" t="n"/>
       <c r="M28" s="6" t="n"/>
+      <c r="O28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="E29" s="5" t="n"/>
       <c r="J29" s="5" t="n"/>
       <c r="K29" s="6" t="n"/>
       <c r="M29" s="6" t="n"/>
+      <c r="O29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="E30" s="5" t="n"/>
       <c r="J30" s="5" t="n"/>
       <c r="K30" s="6" t="n"/>
       <c r="M30" s="6" t="n"/>
+      <c r="O30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="E31" s="5" t="n"/>
       <c r="J31" s="5" t="n"/>
       <c r="K31" s="6" t="n"/>
       <c r="M31" s="6" t="n"/>
+      <c r="O31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="E32" s="5" t="n"/>
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="6" t="n"/>
       <c r="M32" s="6" t="n"/>
+      <c r="O32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="E33" s="5" t="n"/>
       <c r="J33" s="5" t="n"/>
       <c r="K33" s="6" t="n"/>
       <c r="M33" s="6" t="n"/>
+      <c r="O33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="E34" s="5" t="n"/>
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="6" t="n"/>
       <c r="M34" s="6" t="n"/>
+      <c r="O34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="E35" s="5" t="n"/>
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="6" t="n"/>
       <c r="M35" s="6" t="n"/>
+      <c r="O35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="E36" s="5" t="n"/>
       <c r="J36" s="5" t="n"/>
       <c r="K36" s="6" t="n"/>
       <c r="M36" s="6" t="n"/>
+      <c r="O36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="E37" s="5" t="n"/>
       <c r="J37" s="5" t="n"/>
       <c r="K37" s="6" t="n"/>
       <c r="M37" s="6" t="n"/>
+      <c r="O37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="E38" s="5" t="n"/>
       <c r="J38" s="5" t="n"/>
       <c r="K38" s="6" t="n"/>
       <c r="M38" s="6" t="n"/>
+      <c r="O38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="E39" s="5" t="n"/>
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="6" t="n"/>
       <c r="M39" s="6" t="n"/>
+      <c r="O39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="E40" s="5" t="n"/>
       <c r="J40" s="5" t="n"/>
       <c r="K40" s="6" t="n"/>
       <c r="M40" s="6" t="n"/>
+      <c r="O40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="E41" s="5" t="n"/>
       <c r="J41" s="5" t="n"/>
       <c r="K41" s="6" t="n"/>
       <c r="M41" s="6" t="n"/>
+      <c r="O41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="E42" s="5" t="n"/>
       <c r="J42" s="5" t="n"/>
       <c r="K42" s="6" t="n"/>
       <c r="M42" s="6" t="n"/>
+      <c r="O42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="E43" s="5" t="n"/>
       <c r="J43" s="5" t="n"/>
       <c r="K43" s="6" t="n"/>
       <c r="M43" s="6" t="n"/>
+      <c r="O43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="E44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
       <c r="K44" s="6" t="n"/>
       <c r="M44" s="6" t="n"/>
+      <c r="O44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="E45" s="5" t="n"/>
       <c r="J45" s="5" t="n"/>
       <c r="K45" s="6" t="n"/>
       <c r="M45" s="6" t="n"/>
+      <c r="O45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="E46" s="5" t="n"/>
       <c r="J46" s="5" t="n"/>
       <c r="K46" s="6" t="n"/>
       <c r="M46" s="6" t="n"/>
+      <c r="O46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="E47" s="5" t="n"/>
       <c r="J47" s="5" t="n"/>
       <c r="K47" s="6" t="n"/>
       <c r="M47" s="6" t="n"/>
+      <c r="O47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="E48" s="5" t="n"/>
       <c r="J48" s="5" t="n"/>
       <c r="K48" s="6" t="n"/>
       <c r="M48" s="6" t="n"/>
+      <c r="O48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="E49" s="5" t="n"/>
       <c r="J49" s="5" t="n"/>
       <c r="K49" s="6" t="n"/>
       <c r="M49" s="6" t="n"/>
+      <c r="O49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="E50" s="5" t="n"/>
       <c r="J50" s="5" t="n"/>
       <c r="K50" s="6" t="n"/>
       <c r="M50" s="6" t="n"/>
+      <c r="O50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="E51" s="5" t="n"/>
       <c r="J51" s="5" t="n"/>
       <c r="K51" s="6" t="n"/>
       <c r="M51" s="6" t="n"/>
+      <c r="O51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="E52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="6" t="n"/>
       <c r="M52" s="6" t="n"/>
+      <c r="O52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="E53" s="5" t="n"/>
       <c r="J53" s="5" t="n"/>
       <c r="K53" s="6" t="n"/>
       <c r="M53" s="6" t="n"/>
+      <c r="O53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="E54" s="5" t="n"/>
       <c r="J54" s="5" t="n"/>
       <c r="K54" s="6" t="n"/>
       <c r="M54" s="6" t="n"/>
+      <c r="O54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="E55" s="5" t="n"/>
       <c r="J55" s="5" t="n"/>
       <c r="K55" s="6" t="n"/>
       <c r="M55" s="6" t="n"/>
+      <c r="O55" s="6" t="n"/>
     </row>
     <row r="56">
       <c r="E56" s="5" t="n"/>
       <c r="J56" s="5" t="n"/>
       <c r="K56" s="6" t="n"/>
       <c r="M56" s="6" t="n"/>
+      <c r="O56" s="6" t="n"/>
     </row>
     <row r="57">
       <c r="E57" s="5" t="n"/>
       <c r="J57" s="5" t="n"/>
       <c r="K57" s="6" t="n"/>
       <c r="M57" s="6" t="n"/>
+      <c r="O57" s="6" t="n"/>
     </row>
     <row r="58">
       <c r="E58" s="5" t="n"/>
       <c r="J58" s="5" t="n"/>
       <c r="K58" s="6" t="n"/>
       <c r="M58" s="6" t="n"/>
+      <c r="O58" s="6" t="n"/>
     </row>
     <row r="59">
       <c r="E59" s="5" t="n"/>
       <c r="J59" s="5" t="n"/>
       <c r="K59" s="6" t="n"/>
       <c r="M59" s="6" t="n"/>
+      <c r="O59" s="6" t="n"/>
     </row>
     <row r="60">
       <c r="E60" s="5" t="n"/>
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="6" t="n"/>
       <c r="M60" s="6" t="n"/>
+      <c r="O60" s="6" t="n"/>
     </row>
     <row r="61">
       <c r="E61" s="5" t="n"/>
       <c r="J61" s="5" t="n"/>
       <c r="K61" s="6" t="n"/>
       <c r="M61" s="6" t="n"/>
+      <c r="O61" s="6" t="n"/>
     </row>
     <row r="62">
       <c r="E62" s="5" t="n"/>
       <c r="J62" s="5" t="n"/>
       <c r="K62" s="6" t="n"/>
       <c r="M62" s="6" t="n"/>
+      <c r="O62" s="6" t="n"/>
     </row>
     <row r="63">
       <c r="E63" s="5" t="n"/>
       <c r="J63" s="5" t="n"/>
       <c r="K63" s="6" t="n"/>
       <c r="M63" s="6" t="n"/>
+      <c r="O63" s="6" t="n"/>
     </row>
     <row r="64">
       <c r="E64" s="5" t="n"/>
       <c r="J64" s="5" t="n"/>
       <c r="K64" s="6" t="n"/>
       <c r="M64" s="6" t="n"/>
+      <c r="O64" s="6" t="n"/>
     </row>
     <row r="65">
       <c r="E65" s="5" t="n"/>
       <c r="J65" s="5" t="n"/>
       <c r="K65" s="6" t="n"/>
       <c r="M65" s="6" t="n"/>
+      <c r="O65" s="6" t="n"/>
     </row>
     <row r="66">
       <c r="E66" s="5" t="n"/>
       <c r="J66" s="5" t="n"/>
       <c r="K66" s="6" t="n"/>
       <c r="M66" s="6" t="n"/>
+      <c r="O66" s="6" t="n"/>
     </row>
     <row r="67">
       <c r="E67" s="5" t="n"/>
       <c r="J67" s="5" t="n"/>
       <c r="K67" s="6" t="n"/>
       <c r="M67" s="6" t="n"/>
+      <c r="O67" s="6" t="n"/>
     </row>
     <row r="68">
       <c r="E68" s="5" t="n"/>
       <c r="J68" s="5" t="n"/>
       <c r="K68" s="6" t="n"/>
       <c r="M68" s="6" t="n"/>
+      <c r="O68" s="6" t="n"/>
     </row>
     <row r="69">
       <c r="E69" s="5" t="n"/>
       <c r="J69" s="5" t="n"/>
       <c r="K69" s="6" t="n"/>
       <c r="M69" s="6" t="n"/>
+      <c r="O69" s="6" t="n"/>
     </row>
     <row r="70">
       <c r="E70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
       <c r="K70" s="6" t="n"/>
       <c r="M70" s="6" t="n"/>
+      <c r="O70" s="6" t="n"/>
     </row>
     <row r="71">
       <c r="E71" s="5" t="n"/>
       <c r="J71" s="5" t="n"/>
       <c r="K71" s="6" t="n"/>
       <c r="M71" s="6" t="n"/>
+      <c r="O71" s="6" t="n"/>
     </row>
     <row r="72">
       <c r="E72" s="5" t="n"/>
       <c r="J72" s="5" t="n"/>
       <c r="K72" s="6" t="n"/>
       <c r="M72" s="6" t="n"/>
+      <c r="O72" s="6" t="n"/>
     </row>
     <row r="73">
       <c r="E73" s="5" t="n"/>
       <c r="J73" s="5" t="n"/>
       <c r="K73" s="6" t="n"/>
       <c r="M73" s="6" t="n"/>
+      <c r="O73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="E74" s="5" t="n"/>
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="6" t="n"/>
       <c r="M74" s="6" t="n"/>
+      <c r="O74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="E75" s="5" t="n"/>
       <c r="J75" s="5" t="n"/>
       <c r="K75" s="6" t="n"/>
       <c r="M75" s="6" t="n"/>
+      <c r="O75" s="6" t="n"/>
     </row>
     <row r="76">
       <c r="E76" s="5" t="n"/>
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="6" t="n"/>
       <c r="M76" s="6" t="n"/>
+      <c r="O76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="E77" s="5" t="n"/>
       <c r="J77" s="5" t="n"/>
       <c r="K77" s="6" t="n"/>
       <c r="M77" s="6" t="n"/>
+      <c r="O77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="E78" s="5" t="n"/>
       <c r="J78" s="5" t="n"/>
       <c r="K78" s="6" t="n"/>
       <c r="M78" s="6" t="n"/>
+      <c r="O78" s="6" t="n"/>
     </row>
     <row r="79">
       <c r="E79" s="5" t="n"/>
       <c r="J79" s="5" t="n"/>
       <c r="K79" s="6" t="n"/>
       <c r="M79" s="6" t="n"/>
+      <c r="O79" s="6" t="n"/>
     </row>
     <row r="80">
       <c r="E80" s="5" t="n"/>
       <c r="J80" s="5" t="n"/>
       <c r="K80" s="6" t="n"/>
       <c r="M80" s="6" t="n"/>
+      <c r="O80" s="6" t="n"/>
     </row>
     <row r="81">
       <c r="E81" s="5" t="n"/>
       <c r="J81" s="5" t="n"/>
       <c r="K81" s="6" t="n"/>
       <c r="M81" s="6" t="n"/>
+      <c r="O81" s="6" t="n"/>
     </row>
     <row r="82">
       <c r="E82" s="5" t="n"/>
       <c r="J82" s="5" t="n"/>
       <c r="K82" s="6" t="n"/>
       <c r="M82" s="6" t="n"/>
+      <c r="O82" s="6" t="n"/>
     </row>
     <row r="83">
       <c r="E83" s="5" t="n"/>
       <c r="J83" s="5" t="n"/>
       <c r="K83" s="6" t="n"/>
       <c r="M83" s="6" t="n"/>
+      <c r="O83" s="6" t="n"/>
     </row>
     <row r="84">
       <c r="E84" s="5" t="n"/>
       <c r="J84" s="5" t="n"/>
       <c r="K84" s="6" t="n"/>
       <c r="M84" s="6" t="n"/>
+      <c r="O84" s="6" t="n"/>
     </row>
     <row r="85">
       <c r="E85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
       <c r="K85" s="6" t="n"/>
       <c r="M85" s="6" t="n"/>
+      <c r="O85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="E86" s="5" t="n"/>
       <c r="J86" s="5" t="n"/>
       <c r="K86" s="6" t="n"/>
       <c r="M86" s="6" t="n"/>
+      <c r="O86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="E87" s="5" t="n"/>
       <c r="J87" s="5" t="n"/>
       <c r="K87" s="6" t="n"/>
       <c r="M87" s="6" t="n"/>
+      <c r="O87" s="6" t="n"/>
     </row>
     <row r="88">
       <c r="E88" s="5" t="n"/>
       <c r="J88" s="5" t="n"/>
       <c r="K88" s="6" t="n"/>
       <c r="M88" s="6" t="n"/>
+      <c r="O88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="E89" s="5" t="n"/>
       <c r="J89" s="5" t="n"/>
       <c r="K89" s="6" t="n"/>
       <c r="M89" s="6" t="n"/>
+      <c r="O89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="E90" s="5" t="n"/>
       <c r="J90" s="5" t="n"/>
       <c r="K90" s="6" t="n"/>
       <c r="M90" s="6" t="n"/>
+      <c r="O90" s="6" t="n"/>
     </row>
     <row r="91">
       <c r="E91" s="5" t="n"/>
       <c r="J91" s="5" t="n"/>
       <c r="K91" s="6" t="n"/>
       <c r="M91" s="6" t="n"/>
+      <c r="O91" s="6" t="n"/>
     </row>
     <row r="92">
       <c r="E92" s="5" t="n"/>
       <c r="J92" s="5" t="n"/>
       <c r="K92" s="6" t="n"/>
       <c r="M92" s="6" t="n"/>
+      <c r="O92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="E93" s="5" t="n"/>
       <c r="J93" s="5" t="n"/>
       <c r="K93" s="6" t="n"/>
       <c r="M93" s="6" t="n"/>
+      <c r="O93" s="6" t="n"/>
     </row>
     <row r="94">
       <c r="E94" s="5" t="n"/>
       <c r="J94" s="5" t="n"/>
       <c r="K94" s="6" t="n"/>
       <c r="M94" s="6" t="n"/>
+      <c r="O94" s="6" t="n"/>
     </row>
     <row r="95">
       <c r="E95" s="5" t="n"/>
       <c r="J95" s="5" t="n"/>
       <c r="K95" s="6" t="n"/>
       <c r="M95" s="6" t="n"/>
+      <c r="O95" s="6" t="n"/>
     </row>
     <row r="96">
       <c r="E96" s="5" t="n"/>
       <c r="J96" s="5" t="n"/>
       <c r="K96" s="6" t="n"/>
       <c r="M96" s="6" t="n"/>
+      <c r="O96" s="6" t="n"/>
     </row>
     <row r="97">
       <c r="E97" s="5" t="n"/>
       <c r="J97" s="5" t="n"/>
       <c r="K97" s="6" t="n"/>
       <c r="M97" s="6" t="n"/>
+      <c r="O97" s="6" t="n"/>
     </row>
     <row r="98">
       <c r="E98" s="5" t="n"/>
       <c r="J98" s="5" t="n"/>
       <c r="K98" s="6" t="n"/>
       <c r="M98" s="6" t="n"/>
+      <c r="O98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="E99" s="5" t="n"/>
       <c r="J99" s="5" t="n"/>
       <c r="K99" s="6" t="n"/>
       <c r="M99" s="6" t="n"/>
+      <c r="O99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="E100" s="5" t="n"/>
       <c r="J100" s="5" t="n"/>
       <c r="K100" s="6" t="n"/>
       <c r="M100" s="6" t="n"/>
+      <c r="O100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="E101" s="5" t="n"/>
       <c r="J101" s="5" t="n"/>
       <c r="K101" s="6" t="n"/>
       <c r="M101" s="6" t="n"/>
+      <c r="O101" s="6" t="n"/>
     </row>
     <row r="102">
       <c r="E102" s="5" t="n"/>
       <c r="J102" s="5" t="n"/>
       <c r="K102" s="6" t="n"/>
       <c r="M102" s="6" t="n"/>
+      <c r="O102" s="6" t="n"/>
     </row>
     <row r="103">
       <c r="E103" s="5" t="n"/>
       <c r="J103" s="5" t="n"/>
       <c r="K103" s="6" t="n"/>
       <c r="M103" s="6" t="n"/>
+      <c r="O103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="E104" s="5" t="n"/>
       <c r="J104" s="5" t="n"/>
       <c r="K104" s="6" t="n"/>
       <c r="M104" s="6" t="n"/>
+      <c r="O104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="E105" s="5" t="n"/>
       <c r="J105" s="5" t="n"/>
       <c r="K105" s="6" t="n"/>
       <c r="M105" s="6" t="n"/>
+      <c r="O105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="E106" s="5" t="n"/>
       <c r="J106" s="5" t="n"/>
       <c r="K106" s="6" t="n"/>
       <c r="M106" s="6" t="n"/>
+      <c r="O106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="E107" s="5" t="n"/>
       <c r="J107" s="5" t="n"/>
       <c r="K107" s="6" t="n"/>
       <c r="M107" s="6" t="n"/>
+      <c r="O107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="E108" s="5" t="n"/>
       <c r="J108" s="5" t="n"/>
       <c r="K108" s="6" t="n"/>
       <c r="M108" s="6" t="n"/>
+      <c r="O108" s="6" t="n"/>
     </row>
     <row r="109">
       <c r="E109" s="5" t="n"/>
       <c r="J109" s="5" t="n"/>
       <c r="K109" s="6" t="n"/>
       <c r="M109" s="6" t="n"/>
+      <c r="O109" s="6" t="n"/>
     </row>
     <row r="110">
       <c r="E110" s="5" t="n"/>
       <c r="J110" s="5" t="n"/>
       <c r="K110" s="6" t="n"/>
       <c r="M110" s="6" t="n"/>
+      <c r="O110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="E111" s="5" t="n"/>
       <c r="J111" s="5" t="n"/>
       <c r="K111" s="6" t="n"/>
       <c r="M111" s="6" t="n"/>
+      <c r="O111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="E112" s="5" t="n"/>
       <c r="J112" s="5" t="n"/>
       <c r="K112" s="6" t="n"/>
       <c r="M112" s="6" t="n"/>
+      <c r="O112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="E113" s="5" t="n"/>
       <c r="J113" s="5" t="n"/>
       <c r="K113" s="6" t="n"/>
       <c r="M113" s="6" t="n"/>
+      <c r="O113" s="6" t="n"/>
     </row>
     <row r="114">
       <c r="E114" s="5" t="n"/>
       <c r="J114" s="5" t="n"/>
       <c r="K114" s="6" t="n"/>
       <c r="M114" s="6" t="n"/>
+      <c r="O114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="E115" s="5" t="n"/>
       <c r="J115" s="5" t="n"/>
       <c r="K115" s="6" t="n"/>
       <c r="M115" s="6" t="n"/>
+      <c r="O115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="E116" s="5" t="n"/>
       <c r="J116" s="5" t="n"/>
       <c r="K116" s="6" t="n"/>
       <c r="M116" s="6" t="n"/>
+      <c r="O116" s="6" t="n"/>
     </row>
     <row r="117">
       <c r="E117" s="5" t="n"/>
       <c r="J117" s="5" t="n"/>
       <c r="K117" s="6" t="n"/>
       <c r="M117" s="6" t="n"/>
+      <c r="O117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="E118" s="5" t="n"/>
       <c r="J118" s="5" t="n"/>
       <c r="K118" s="6" t="n"/>
       <c r="M118" s="6" t="n"/>
+      <c r="O118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="E119" s="5" t="n"/>
       <c r="J119" s="5" t="n"/>
       <c r="K119" s="6" t="n"/>
       <c r="M119" s="6" t="n"/>
+      <c r="O119" s="6" t="n"/>
     </row>
     <row r="120">
       <c r="E120" s="5" t="n"/>
       <c r="J120" s="5" t="n"/>
       <c r="K120" s="6" t="n"/>
       <c r="M120" s="6" t="n"/>
+      <c r="O120" s="6" t="n"/>
     </row>
     <row r="121">
       <c r="E121" s="5" t="n"/>
       <c r="J121" s="5" t="n"/>
       <c r="K121" s="6" t="n"/>
       <c r="M121" s="6" t="n"/>
+      <c r="O121" s="6" t="n"/>
     </row>
     <row r="122">
       <c r="E122" s="5" t="n"/>
       <c r="J122" s="5" t="n"/>
       <c r="K122" s="6" t="n"/>
       <c r="M122" s="6" t="n"/>
+      <c r="O122" s="6" t="n"/>
     </row>
     <row r="123">
       <c r="E123" s="5" t="n"/>
       <c r="J123" s="5" t="n"/>
       <c r="K123" s="6" t="n"/>
       <c r="M123" s="6" t="n"/>
+      <c r="O123" s="6" t="n"/>
     </row>
     <row r="124">
       <c r="E124" s="5" t="n"/>
       <c r="J124" s="5" t="n"/>
       <c r="K124" s="6" t="n"/>
       <c r="M124" s="6" t="n"/>
+      <c r="O124" s="6" t="n"/>
     </row>
     <row r="125">
       <c r="E125" s="5" t="n"/>
       <c r="J125" s="5" t="n"/>
       <c r="K125" s="6" t="n"/>
       <c r="M125" s="6" t="n"/>
+      <c r="O125" s="6" t="n"/>
     </row>
     <row r="126">
       <c r="E126" s="5" t="n"/>
       <c r="J126" s="5" t="n"/>
       <c r="K126" s="6" t="n"/>
       <c r="M126" s="6" t="n"/>
+      <c r="O126" s="6" t="n"/>
     </row>
     <row r="127">
       <c r="E127" s="5" t="n"/>
       <c r="J127" s="5" t="n"/>
       <c r="K127" s="6" t="n"/>
       <c r="M127" s="6" t="n"/>
+      <c r="O127" s="6" t="n"/>
     </row>
     <row r="128">
       <c r="E128" s="5" t="n"/>
       <c r="J128" s="5" t="n"/>
       <c r="K128" s="6" t="n"/>
       <c r="M128" s="6" t="n"/>
+      <c r="O128" s="6" t="n"/>
     </row>
     <row r="129">
       <c r="E129" s="5" t="n"/>
       <c r="J129" s="5" t="n"/>
       <c r="K129" s="6" t="n"/>
       <c r="M129" s="6" t="n"/>
+      <c r="O129" s="6" t="n"/>
     </row>
     <row r="130">
       <c r="E130" s="5" t="n"/>
       <c r="J130" s="5" t="n"/>
       <c r="K130" s="6" t="n"/>
       <c r="M130" s="6" t="n"/>
+      <c r="O130" s="6" t="n"/>
     </row>
     <row r="131">
       <c r="E131" s="5" t="n"/>
       <c r="J131" s="5" t="n"/>
       <c r="K131" s="6" t="n"/>
       <c r="M131" s="6" t="n"/>
+      <c r="O131" s="6" t="n"/>
     </row>
     <row r="132">
       <c r="E132" s="5" t="n"/>
       <c r="J132" s="5" t="n"/>
       <c r="K132" s="6" t="n"/>
       <c r="M132" s="6" t="n"/>
+      <c r="O132" s="6" t="n"/>
     </row>
     <row r="133">
       <c r="E133" s="5" t="n"/>
       <c r="J133" s="5" t="n"/>
       <c r="K133" s="6" t="n"/>
       <c r="M133" s="6" t="n"/>
+      <c r="O133" s="6" t="n"/>
     </row>
     <row r="134">
       <c r="E134" s="5" t="n"/>
       <c r="J134" s="5" t="n"/>
       <c r="K134" s="6" t="n"/>
       <c r="M134" s="6" t="n"/>
+      <c r="O134" s="6" t="n"/>
     </row>
     <row r="135">
       <c r="E135" s="5" t="n"/>
       <c r="J135" s="5" t="n"/>
       <c r="K135" s="6" t="n"/>
       <c r="M135" s="6" t="n"/>
+      <c r="O135" s="6" t="n"/>
     </row>
     <row r="136">
       <c r="E136" s="5" t="n"/>
       <c r="J136" s="5" t="n"/>
       <c r="K136" s="6" t="n"/>
       <c r="M136" s="6" t="n"/>
+      <c r="O136" s="6" t="n"/>
     </row>
     <row r="137">
       <c r="E137" s="5" t="n"/>
       <c r="J137" s="5" t="n"/>
       <c r="K137" s="6" t="n"/>
       <c r="M137" s="6" t="n"/>
+      <c r="O137" s="6" t="n"/>
     </row>
     <row r="138">
       <c r="E138" s="5" t="n"/>
       <c r="J138" s="5" t="n"/>
       <c r="K138" s="6" t="n"/>
       <c r="M138" s="6" t="n"/>
+      <c r="O138" s="6" t="n"/>
     </row>
     <row r="139">
       <c r="E139" s="5" t="n"/>
       <c r="J139" s="5" t="n"/>
       <c r="K139" s="6" t="n"/>
       <c r="M139" s="6" t="n"/>
+      <c r="O139" s="6" t="n"/>
     </row>
     <row r="140">
       <c r="E140" s="5" t="n"/>
       <c r="J140" s="5" t="n"/>
       <c r="K140" s="6" t="n"/>
       <c r="M140" s="6" t="n"/>
+      <c r="O140" s="6" t="n"/>
     </row>
     <row r="141">
       <c r="E141" s="5" t="n"/>
       <c r="J141" s="5" t="n"/>
       <c r="K141" s="6" t="n"/>
       <c r="M141" s="6" t="n"/>
+      <c r="O141" s="6" t="n"/>
     </row>
     <row r="142">
       <c r="E142" s="5" t="n"/>
       <c r="J142" s="5" t="n"/>
       <c r="K142" s="6" t="n"/>
       <c r="M142" s="6" t="n"/>
+      <c r="O142" s="6" t="n"/>
     </row>
     <row r="143">
       <c r="E143" s="5" t="n"/>
       <c r="J143" s="5" t="n"/>
       <c r="K143" s="6" t="n"/>
       <c r="M143" s="6" t="n"/>
+      <c r="O143" s="6" t="n"/>
     </row>
     <row r="144">
       <c r="E144" s="5" t="n"/>
       <c r="J144" s="5" t="n"/>
       <c r="K144" s="6" t="n"/>
       <c r="M144" s="6" t="n"/>
+      <c r="O144" s="6" t="n"/>
     </row>
     <row r="145">
       <c r="E145" s="5" t="n"/>
       <c r="J145" s="5" t="n"/>
       <c r="K145" s="6" t="n"/>
       <c r="M145" s="6" t="n"/>
+      <c r="O145" s="6" t="n"/>
     </row>
     <row r="146">
       <c r="E146" s="5" t="n"/>
       <c r="J146" s="5" t="n"/>
       <c r="K146" s="6" t="n"/>
       <c r="M146" s="6" t="n"/>
+      <c r="O146" s="6" t="n"/>
     </row>
     <row r="147">
       <c r="E147" s="5" t="n"/>
       <c r="J147" s="5" t="n"/>
       <c r="K147" s="6" t="n"/>
       <c r="M147" s="6" t="n"/>
+      <c r="O147" s="6" t="n"/>
     </row>
     <row r="148">
       <c r="E148" s="5" t="n"/>
       <c r="J148" s="5" t="n"/>
       <c r="K148" s="6" t="n"/>
       <c r="M148" s="6" t="n"/>
+      <c r="O148" s="6" t="n"/>
     </row>
     <row r="149">
       <c r="E149" s="5" t="n"/>
       <c r="J149" s="5" t="n"/>
       <c r="K149" s="6" t="n"/>
       <c r="M149" s="6" t="n"/>
+      <c r="O149" s="6" t="n"/>
     </row>
     <row r="150">
       <c r="E150" s="5" t="n"/>
       <c r="J150" s="5" t="n"/>
       <c r="K150" s="6" t="n"/>
       <c r="M150" s="6" t="n"/>
+      <c r="O150" s="6" t="n"/>
     </row>
     <row r="151">
       <c r="E151" s="5" t="n"/>
       <c r="J151" s="5" t="n"/>
       <c r="K151" s="6" t="n"/>
       <c r="M151" s="6" t="n"/>
+      <c r="O151" s="6" t="n"/>
     </row>
     <row r="152">
       <c r="E152" s="5" t="n"/>
       <c r="J152" s="5" t="n"/>
       <c r="K152" s="6" t="n"/>
       <c r="M152" s="6" t="n"/>
+      <c r="O152" s="6" t="n"/>
     </row>
     <row r="153">
       <c r="E153" s="5" t="n"/>
       <c r="J153" s="5" t="n"/>
       <c r="K153" s="6" t="n"/>
       <c r="M153" s="6" t="n"/>
+      <c r="O153" s="6" t="n"/>
     </row>
     <row r="154">
       <c r="E154" s="5" t="n"/>
       <c r="J154" s="5" t="n"/>
       <c r="K154" s="6" t="n"/>
       <c r="M154" s="6" t="n"/>
+      <c r="O154" s="6" t="n"/>
     </row>
     <row r="155">
       <c r="E155" s="5" t="n"/>
       <c r="J155" s="5" t="n"/>
       <c r="K155" s="6" t="n"/>
       <c r="M155" s="6" t="n"/>
+      <c r="O155" s="6" t="n"/>
     </row>
     <row r="156">
       <c r="E156" s="5" t="n"/>
       <c r="J156" s="5" t="n"/>
       <c r="K156" s="6" t="n"/>
       <c r="M156" s="6" t="n"/>
+      <c r="O156" s="6" t="n"/>
     </row>
     <row r="157">
       <c r="E157" s="5" t="n"/>
       <c r="J157" s="5" t="n"/>
       <c r="K157" s="6" t="n"/>
       <c r="M157" s="6" t="n"/>
+      <c r="O157" s="6" t="n"/>
     </row>
     <row r="158">
       <c r="E158" s="5" t="n"/>
       <c r="J158" s="5" t="n"/>
       <c r="K158" s="6" t="n"/>
       <c r="M158" s="6" t="n"/>
+      <c r="O158" s="6" t="n"/>
     </row>
     <row r="159">
       <c r="E159" s="5" t="n"/>
       <c r="J159" s="5" t="n"/>
       <c r="K159" s="6" t="n"/>
       <c r="M159" s="6" t="n"/>
+      <c r="O159" s="6" t="n"/>
     </row>
     <row r="160">
       <c r="E160" s="5" t="n"/>
       <c r="J160" s="5" t="n"/>
       <c r="K160" s="6" t="n"/>
       <c r="M160" s="6" t="n"/>
+      <c r="O160" s="6" t="n"/>
     </row>
     <row r="161">
       <c r="E161" s="5" t="n"/>
       <c r="J161" s="5" t="n"/>
       <c r="K161" s="6" t="n"/>
       <c r="M161" s="6" t="n"/>
+      <c r="O161" s="6" t="n"/>
     </row>
     <row r="162">
       <c r="E162" s="5" t="n"/>
       <c r="J162" s="5" t="n"/>
       <c r="K162" s="6" t="n"/>
       <c r="M162" s="6" t="n"/>
+      <c r="O162" s="6" t="n"/>
     </row>
     <row r="163">
       <c r="E163" s="5" t="n"/>
       <c r="J163" s="5" t="n"/>
       <c r="K163" s="6" t="n"/>
       <c r="M163" s="6" t="n"/>
+      <c r="O163" s="6" t="n"/>
     </row>
     <row r="164">
       <c r="E164" s="5" t="n"/>
       <c r="J164" s="5" t="n"/>
       <c r="K164" s="6" t="n"/>
       <c r="M164" s="6" t="n"/>
+      <c r="O164" s="6" t="n"/>
     </row>
     <row r="165">
       <c r="E165" s="5" t="n"/>
       <c r="J165" s="5" t="n"/>
       <c r="K165" s="6" t="n"/>
       <c r="M165" s="6" t="n"/>
+      <c r="O165" s="6" t="n"/>
     </row>
     <row r="166">
       <c r="E166" s="5" t="n"/>
       <c r="J166" s="5" t="n"/>
       <c r="K166" s="6" t="n"/>
       <c r="M166" s="6" t="n"/>
+      <c r="O166" s="6" t="n"/>
     </row>
     <row r="167">
       <c r="E167" s="5" t="n"/>
       <c r="J167" s="5" t="n"/>
       <c r="K167" s="6" t="n"/>
       <c r="M167" s="6" t="n"/>
+      <c r="O167" s="6" t="n"/>
     </row>
     <row r="168">
       <c r="E168" s="5" t="n"/>
       <c r="J168" s="5" t="n"/>
       <c r="K168" s="6" t="n"/>
       <c r="M168" s="6" t="n"/>
+      <c r="O168" s="6" t="n"/>
     </row>
     <row r="169">
       <c r="E169" s="5" t="n"/>
       <c r="J169" s="5" t="n"/>
       <c r="K169" s="6" t="n"/>
       <c r="M169" s="6" t="n"/>
+      <c r="O169" s="6" t="n"/>
     </row>
     <row r="170">
       <c r="E170" s="5" t="n"/>
       <c r="J170" s="5" t="n"/>
       <c r="K170" s="6" t="n"/>
       <c r="M170" s="6" t="n"/>
+      <c r="O170" s="6" t="n"/>
     </row>
     <row r="171">
       <c r="E171" s="5" t="n"/>
       <c r="J171" s="5" t="n"/>
       <c r="K171" s="6" t="n"/>
       <c r="M171" s="6" t="n"/>
+      <c r="O171" s="6" t="n"/>
     </row>
     <row r="172">
       <c r="E172" s="5" t="n"/>
       <c r="J172" s="5" t="n"/>
       <c r="K172" s="6" t="n"/>
       <c r="M172" s="6" t="n"/>
+      <c r="O172" s="6" t="n"/>
     </row>
     <row r="173">
       <c r="E173" s="5" t="n"/>
       <c r="J173" s="5" t="n"/>
       <c r="K173" s="6" t="n"/>
       <c r="M173" s="6" t="n"/>
+      <c r="O173" s="6" t="n"/>
     </row>
     <row r="174">
       <c r="E174" s="5" t="n"/>
       <c r="J174" s="5" t="n"/>
       <c r="K174" s="6" t="n"/>
       <c r="M174" s="6" t="n"/>
+      <c r="O174" s="6" t="n"/>
     </row>
     <row r="175">
       <c r="E175" s="5" t="n"/>
       <c r="J175" s="5" t="n"/>
       <c r="K175" s="6" t="n"/>
       <c r="M175" s="6" t="n"/>
+      <c r="O175" s="6" t="n"/>
     </row>
     <row r="176">
       <c r="E176" s="5" t="n"/>
       <c r="J176" s="5" t="n"/>
       <c r="K176" s="6" t="n"/>
       <c r="M176" s="6" t="n"/>
+      <c r="O176" s="6" t="n"/>
     </row>
     <row r="177">
       <c r="E177" s="5" t="n"/>
       <c r="J177" s="5" t="n"/>
       <c r="K177" s="6" t="n"/>
       <c r="M177" s="6" t="n"/>
+      <c r="O177" s="6" t="n"/>
     </row>
     <row r="178">
       <c r="E178" s="5" t="n"/>
       <c r="J178" s="5" t="n"/>
       <c r="K178" s="6" t="n"/>
       <c r="M178" s="6" t="n"/>
+      <c r="O178" s="6" t="n"/>
     </row>
     <row r="179">
       <c r="E179" s="5" t="n"/>
       <c r="J179" s="5" t="n"/>
       <c r="K179" s="6" t="n"/>
       <c r="M179" s="6" t="n"/>
+      <c r="O179" s="6" t="n"/>
     </row>
     <row r="180">
       <c r="E180" s="5" t="n"/>
       <c r="J180" s="5" t="n"/>
       <c r="K180" s="6" t="n"/>
       <c r="M180" s="6" t="n"/>
+      <c r="O180" s="6" t="n"/>
     </row>
     <row r="181">
       <c r="E181" s="5" t="n"/>
       <c r="J181" s="5" t="n"/>
       <c r="K181" s="6" t="n"/>
       <c r="M181" s="6" t="n"/>
+      <c r="O181" s="6" t="n"/>
     </row>
     <row r="182">
       <c r="E182" s="5" t="n"/>
       <c r="J182" s="5" t="n"/>
       <c r="K182" s="6" t="n"/>
       <c r="M182" s="6" t="n"/>
+      <c r="O182" s="6" t="n"/>
     </row>
     <row r="183">
       <c r="E183" s="5" t="n"/>
       <c r="J183" s="5" t="n"/>
       <c r="K183" s="6" t="n"/>
       <c r="M183" s="6" t="n"/>
+      <c r="O183" s="6" t="n"/>
     </row>
     <row r="184">
       <c r="E184" s="5" t="n"/>
       <c r="J184" s="5" t="n"/>
       <c r="K184" s="6" t="n"/>
       <c r="M184" s="6" t="n"/>
+      <c r="O184" s="6" t="n"/>
     </row>
     <row r="185">
       <c r="E185" s="5" t="n"/>
       <c r="J185" s="5" t="n"/>
       <c r="K185" s="6" t="n"/>
       <c r="M185" s="6" t="n"/>
+      <c r="O185" s="6" t="n"/>
     </row>
     <row r="186">
       <c r="E186" s="5" t="n"/>
       <c r="J186" s="5" t="n"/>
       <c r="K186" s="6" t="n"/>
       <c r="M186" s="6" t="n"/>
+      <c r="O186" s="6" t="n"/>
     </row>
     <row r="187">
       <c r="E187" s="5" t="n"/>
       <c r="J187" s="5" t="n"/>
       <c r="K187" s="6" t="n"/>
       <c r="M187" s="6" t="n"/>
+      <c r="O187" s="6" t="n"/>
     </row>
     <row r="188">
       <c r="E188" s="5" t="n"/>
       <c r="J188" s="5" t="n"/>
       <c r="K188" s="6" t="n"/>
       <c r="M188" s="6" t="n"/>
+      <c r="O188" s="6" t="n"/>
     </row>
     <row r="189">
       <c r="E189" s="5" t="n"/>
       <c r="J189" s="5" t="n"/>
       <c r="K189" s="6" t="n"/>
       <c r="M189" s="6" t="n"/>
+      <c r="O189" s="6" t="n"/>
     </row>
     <row r="190">
       <c r="E190" s="5" t="n"/>
       <c r="J190" s="5" t="n"/>
       <c r="K190" s="6" t="n"/>
       <c r="M190" s="6" t="n"/>
+      <c r="O190" s="6" t="n"/>
     </row>
     <row r="191">
       <c r="E191" s="5" t="n"/>
       <c r="J191" s="5" t="n"/>
       <c r="K191" s="6" t="n"/>
       <c r="M191" s="6" t="n"/>
+      <c r="O191" s="6" t="n"/>
     </row>
     <row r="192">
       <c r="E192" s="5" t="n"/>
       <c r="J192" s="5" t="n"/>
       <c r="K192" s="6" t="n"/>
       <c r="M192" s="6" t="n"/>
+      <c r="O192" s="6" t="n"/>
     </row>
     <row r="193">
       <c r="E193" s="5" t="n"/>
       <c r="J193" s="5" t="n"/>
       <c r="K193" s="6" t="n"/>
       <c r="M193" s="6" t="n"/>
+      <c r="O193" s="6" t="n"/>
     </row>
     <row r="194">
       <c r="E194" s="5" t="n"/>
       <c r="J194" s="5" t="n"/>
       <c r="K194" s="6" t="n"/>
       <c r="M194" s="6" t="n"/>
+      <c r="O194" s="6" t="n"/>
     </row>
     <row r="195">
       <c r="E195" s="5" t="n"/>
       <c r="J195" s="5" t="n"/>
       <c r="K195" s="6" t="n"/>
       <c r="M195" s="6" t="n"/>
+      <c r="O195" s="6" t="n"/>
     </row>
     <row r="196">
       <c r="E196" s="5" t="n"/>
       <c r="J196" s="5" t="n"/>
       <c r="K196" s="6" t="n"/>
       <c r="M196" s="6" t="n"/>
+      <c r="O196" s="6" t="n"/>
     </row>
     <row r="197">
       <c r="E197" s="5" t="n"/>
       <c r="J197" s="5" t="n"/>
       <c r="K197" s="6" t="n"/>
       <c r="M197" s="6" t="n"/>
+      <c r="O197" s="6" t="n"/>
     </row>
     <row r="198">
       <c r="E198" s="5" t="n"/>
       <c r="J198" s="5" t="n"/>
       <c r="K198" s="6" t="n"/>
       <c r="M198" s="6" t="n"/>
+      <c r="O198" s="6" t="n"/>
     </row>
     <row r="199">
       <c r="E199" s="5" t="n"/>
       <c r="J199" s="5" t="n"/>
       <c r="K199" s="6" t="n"/>
       <c r="M199" s="6" t="n"/>
+      <c r="O199" s="6" t="n"/>
     </row>
     <row r="200">
       <c r="E200" s="5" t="n"/>
       <c r="J200" s="5" t="n"/>
       <c r="K200" s="6" t="n"/>
       <c r="M200" s="6" t="n"/>
+      <c r="O200" s="6" t="n"/>
     </row>
     <row r="201">
       <c r="E201" s="5" t="n"/>
       <c r="J201" s="5" t="n"/>
       <c r="K201" s="6" t="n"/>
       <c r="M201" s="6" t="n"/>
+      <c r="O201" s="6" t="n"/>
     </row>
     <row r="202">
       <c r="E202" s="5" t="n"/>
       <c r="J202" s="5" t="n"/>
       <c r="K202" s="6" t="n"/>
       <c r="M202" s="6" t="n"/>
+      <c r="O202" s="6" t="n"/>
     </row>
     <row r="203">
       <c r="E203" s="5" t="n"/>
       <c r="J203" s="5" t="n"/>
       <c r="K203" s="6" t="n"/>
       <c r="M203" s="6" t="n"/>
+      <c r="O203" s="6" t="n"/>
     </row>
     <row r="204">
       <c r="E204" s="5" t="n"/>
       <c r="J204" s="5" t="n"/>
       <c r="K204" s="6" t="n"/>
       <c r="M204" s="6" t="n"/>
+      <c r="O204" s="6" t="n"/>
     </row>
     <row r="205">
       <c r="E205" s="5" t="n"/>
       <c r="J205" s="5" t="n"/>
       <c r="K205" s="6" t="n"/>
       <c r="M205" s="6" t="n"/>
+      <c r="O205" s="6" t="n"/>
     </row>
     <row r="206">
       <c r="E206" s="5" t="n"/>
       <c r="J206" s="5" t="n"/>
       <c r="K206" s="6" t="n"/>
       <c r="M206" s="6" t="n"/>
+      <c r="O206" s="6" t="n"/>
     </row>
     <row r="207">
       <c r="E207" s="5" t="n"/>
       <c r="J207" s="5" t="n"/>
       <c r="K207" s="6" t="n"/>
       <c r="M207" s="6" t="n"/>
+      <c r="O207" s="6" t="n"/>
     </row>
     <row r="208">
       <c r="E208" s="5" t="n"/>
       <c r="J208" s="5" t="n"/>
       <c r="K208" s="6" t="n"/>
       <c r="M208" s="6" t="n"/>
+      <c r="O208" s="6" t="n"/>
     </row>
     <row r="209">
       <c r="E209" s="5" t="n"/>
       <c r="J209" s="5" t="n"/>
       <c r="K209" s="6" t="n"/>
       <c r="M209" s="6" t="n"/>
+      <c r="O209" s="6" t="n"/>
     </row>
     <row r="210">
       <c r="E210" s="5" t="n"/>
       <c r="J210" s="5" t="n"/>
       <c r="K210" s="6" t="n"/>
       <c r="M210" s="6" t="n"/>
+      <c r="O210" s="6" t="n"/>
     </row>
     <row r="211">
       <c r="E211" s="5" t="n"/>
       <c r="J211" s="5" t="n"/>
       <c r="K211" s="6" t="n"/>
       <c r="M211" s="6" t="n"/>
+      <c r="O211" s="6" t="n"/>
     </row>
     <row r="212">
       <c r="E212" s="5" t="n"/>
       <c r="J212" s="5" t="n"/>
       <c r="K212" s="6" t="n"/>
       <c r="M212" s="6" t="n"/>
+      <c r="O212" s="6" t="n"/>
     </row>
     <row r="213">
       <c r="E213" s="5" t="n"/>
       <c r="J213" s="5" t="n"/>
       <c r="K213" s="6" t="n"/>
       <c r="M213" s="6" t="n"/>
+      <c r="O213" s="6" t="n"/>
     </row>
     <row r="214">
       <c r="E214" s="5" t="n"/>
       <c r="J214" s="5" t="n"/>
       <c r="K214" s="6" t="n"/>
       <c r="M214" s="6" t="n"/>
+      <c r="O214" s="6" t="n"/>
     </row>
     <row r="215">
       <c r="E215" s="5" t="n"/>
       <c r="J215" s="5" t="n"/>
       <c r="K215" s="6" t="n"/>
       <c r="M215" s="6" t="n"/>
+      <c r="O215" s="6" t="n"/>
     </row>
     <row r="216">
       <c r="E216" s="5" t="n"/>
       <c r="J216" s="5" t="n"/>
       <c r="K216" s="6" t="n"/>
       <c r="M216" s="6" t="n"/>
+      <c r="O216" s="6" t="n"/>
     </row>
     <row r="217">
       <c r="E217" s="5" t="n"/>
       <c r="J217" s="5" t="n"/>
       <c r="K217" s="6" t="n"/>
       <c r="M217" s="6" t="n"/>
+      <c r="O217" s="6" t="n"/>
     </row>
     <row r="218">
       <c r="E218" s="5" t="n"/>
       <c r="J218" s="5" t="n"/>
       <c r="K218" s="6" t="n"/>
       <c r="M218" s="6" t="n"/>
+      <c r="O218" s="6" t="n"/>
     </row>
     <row r="219">
       <c r="E219" s="5" t="n"/>
       <c r="J219" s="5" t="n"/>
       <c r="K219" s="6" t="n"/>
       <c r="M219" s="6" t="n"/>
+      <c r="O219" s="6" t="n"/>
     </row>
     <row r="220">
       <c r="E220" s="5" t="n"/>
       <c r="J220" s="5" t="n"/>
       <c r="K220" s="6" t="n"/>
       <c r="M220" s="6" t="n"/>
+      <c r="O220" s="6" t="n"/>
     </row>
     <row r="221">
       <c r="E221" s="5" t="n"/>
       <c r="J221" s="5" t="n"/>
       <c r="K221" s="6" t="n"/>
       <c r="M221" s="6" t="n"/>
+      <c r="O221" s="6" t="n"/>
     </row>
     <row r="222">
       <c r="E222" s="5" t="n"/>
       <c r="J222" s="5" t="n"/>
       <c r="K222" s="6" t="n"/>
       <c r="M222" s="6" t="n"/>
+      <c r="O222" s="6" t="n"/>
     </row>
     <row r="223">
       <c r="E223" s="5" t="n"/>
       <c r="J223" s="5" t="n"/>
       <c r="K223" s="6" t="n"/>
       <c r="M223" s="6" t="n"/>
+      <c r="O223" s="6" t="n"/>
     </row>
     <row r="224">
       <c r="E224" s="5" t="n"/>
       <c r="J224" s="5" t="n"/>
       <c r="K224" s="6" t="n"/>
       <c r="M224" s="6" t="n"/>
+      <c r="O224" s="6" t="n"/>
     </row>
     <row r="225">
       <c r="E225" s="5" t="n"/>
       <c r="J225" s="5" t="n"/>
       <c r="K225" s="6" t="n"/>
       <c r="M225" s="6" t="n"/>
+      <c r="O225" s="6" t="n"/>
     </row>
     <row r="226">
       <c r="E226" s="5" t="n"/>
       <c r="J226" s="5" t="n"/>
       <c r="K226" s="6" t="n"/>
       <c r="M226" s="6" t="n"/>
+      <c r="O226" s="6" t="n"/>
     </row>
     <row r="227">
       <c r="E227" s="5" t="n"/>
       <c r="J227" s="5" t="n"/>
       <c r="K227" s="6" t="n"/>
       <c r="M227" s="6" t="n"/>
+      <c r="O227" s="6" t="n"/>
     </row>
     <row r="228">
       <c r="E228" s="5" t="n"/>
       <c r="J228" s="5" t="n"/>
       <c r="K228" s="6" t="n"/>
       <c r="M228" s="6" t="n"/>
+      <c r="O228" s="6" t="n"/>
     </row>
     <row r="229">
       <c r="E229" s="5" t="n"/>
       <c r="J229" s="5" t="n"/>
       <c r="K229" s="6" t="n"/>
       <c r="M229" s="6" t="n"/>
+      <c r="O229" s="6" t="n"/>
     </row>
     <row r="230">
       <c r="E230" s="5" t="n"/>
       <c r="J230" s="5" t="n"/>
       <c r="K230" s="6" t="n"/>
       <c r="M230" s="6" t="n"/>
+      <c r="O230" s="6" t="n"/>
     </row>
     <row r="231">
       <c r="E231" s="5" t="n"/>
       <c r="J231" s="5" t="n"/>
       <c r="K231" s="6" t="n"/>
       <c r="M231" s="6" t="n"/>
+      <c r="O231" s="6" t="n"/>
     </row>
     <row r="232">
       <c r="E232" s="5" t="n"/>
       <c r="J232" s="5" t="n"/>
       <c r="K232" s="6" t="n"/>
       <c r="M232" s="6" t="n"/>
+      <c r="O232" s="6" t="n"/>
     </row>
     <row r="233">
       <c r="E233" s="5" t="n"/>
       <c r="J233" s="5" t="n"/>
       <c r="K233" s="6" t="n"/>
       <c r="M233" s="6" t="n"/>
+      <c r="O233" s="6" t="n"/>
     </row>
     <row r="234">
       <c r="E234" s="5" t="n"/>
       <c r="J234" s="5" t="n"/>
       <c r="K234" s="6" t="n"/>
       <c r="M234" s="6" t="n"/>
+      <c r="O234" s="6" t="n"/>
     </row>
     <row r="235">
       <c r="E235" s="5" t="n"/>
       <c r="J235" s="5" t="n"/>
       <c r="K235" s="6" t="n"/>
       <c r="M235" s="6" t="n"/>
+      <c r="O235" s="6" t="n"/>
     </row>
     <row r="236">
       <c r="E236" s="5" t="n"/>
       <c r="J236" s="5" t="n"/>
       <c r="K236" s="6" t="n"/>
       <c r="M236" s="6" t="n"/>
+      <c r="O236" s="6" t="n"/>
     </row>
     <row r="237">
       <c r="E237" s="5" t="n"/>
       <c r="J237" s="5" t="n"/>
       <c r="K237" s="6" t="n"/>
       <c r="M237" s="6" t="n"/>
+      <c r="O237" s="6" t="n"/>
     </row>
     <row r="238">
       <c r="E238" s="5" t="n"/>
       <c r="J238" s="5" t="n"/>
       <c r="K238" s="6" t="n"/>
       <c r="M238" s="6" t="n"/>
+      <c r="O238" s="6" t="n"/>
     </row>
     <row r="239">
       <c r="E239" s="5" t="n"/>
       <c r="J239" s="5" t="n"/>
       <c r="K239" s="6" t="n"/>
       <c r="M239" s="6" t="n"/>
+      <c r="O239" s="6" t="n"/>
     </row>
     <row r="240">
       <c r="E240" s="5" t="n"/>
       <c r="J240" s="5" t="n"/>
       <c r="K240" s="6" t="n"/>
       <c r="M240" s="6" t="n"/>
+      <c r="O240" s="6" t="n"/>
     </row>
     <row r="241">
       <c r="E241" s="5" t="n"/>
       <c r="J241" s="5" t="n"/>
       <c r="K241" s="6" t="n"/>
       <c r="M241" s="6" t="n"/>
+      <c r="O241" s="6" t="n"/>
     </row>
     <row r="242">
       <c r="E242" s="5" t="n"/>
       <c r="J242" s="5" t="n"/>
       <c r="K242" s="6" t="n"/>
       <c r="M242" s="6" t="n"/>
+      <c r="O242" s="6" t="n"/>
     </row>
     <row r="243">
       <c r="E243" s="5" t="n"/>
       <c r="J243" s="5" t="n"/>
       <c r="K243" s="6" t="n"/>
       <c r="M243" s="6" t="n"/>
+      <c r="O243" s="6" t="n"/>
     </row>
     <row r="244">
       <c r="E244" s="5" t="n"/>
       <c r="J244" s="5" t="n"/>
       <c r="K244" s="6" t="n"/>
       <c r="M244" s="6" t="n"/>
+      <c r="O244" s="6" t="n"/>
     </row>
     <row r="245">
       <c r="E245" s="5" t="n"/>
       <c r="J245" s="5" t="n"/>
       <c r="K245" s="6" t="n"/>
       <c r="M245" s="6" t="n"/>
+      <c r="O245" s="6" t="n"/>
     </row>
     <row r="246">
       <c r="E246" s="5" t="n"/>
       <c r="J246" s="5" t="n"/>
       <c r="K246" s="6" t="n"/>
       <c r="M246" s="6" t="n"/>
+      <c r="O246" s="6" t="n"/>
     </row>
     <row r="247">
       <c r="E247" s="5" t="n"/>
       <c r="J247" s="5" t="n"/>
       <c r="K247" s="6" t="n"/>
       <c r="M247" s="6" t="n"/>
+      <c r="O247" s="6" t="n"/>
     </row>
     <row r="248">
       <c r="E248" s="5" t="n"/>
       <c r="J248" s="5" t="n"/>
       <c r="K248" s="6" t="n"/>
       <c r="M248" s="6" t="n"/>
+      <c r="O248" s="6" t="n"/>
     </row>
     <row r="249">
       <c r="E249" s="5" t="n"/>
       <c r="J249" s="5" t="n"/>
       <c r="K249" s="6" t="n"/>
       <c r="M249" s="6" t="n"/>
+      <c r="O249" s="6" t="n"/>
     </row>
     <row r="250">
       <c r="E250" s="5" t="n"/>
       <c r="J250" s="5" t="n"/>
       <c r="K250" s="6" t="n"/>
       <c r="M250" s="6" t="n"/>
+      <c r="O250" s="6" t="n"/>
     </row>
     <row r="251">
       <c r="E251" s="5" t="n"/>
       <c r="J251" s="5" t="n"/>
       <c r="K251" s="6" t="n"/>
       <c r="M251" s="6" t="n"/>
+      <c r="O251" s="6" t="n"/>
     </row>
     <row r="252">
       <c r="E252" s="5" t="n"/>
       <c r="J252" s="5" t="n"/>
       <c r="K252" s="6" t="n"/>
       <c r="M252" s="6" t="n"/>
+      <c r="O252" s="6" t="n"/>
     </row>
     <row r="253">
       <c r="E253" s="5" t="n"/>
       <c r="J253" s="5" t="n"/>
       <c r="K253" s="6" t="n"/>
       <c r="M253" s="6" t="n"/>
+      <c r="O253" s="6" t="n"/>
     </row>
     <row r="254">
       <c r="E254" s="5" t="n"/>
       <c r="J254" s="5" t="n"/>
       <c r="K254" s="6" t="n"/>
       <c r="M254" s="6" t="n"/>
+      <c r="O254" s="6" t="n"/>
     </row>
     <row r="255">
       <c r="E255" s="5" t="n"/>
       <c r="J255" s="5" t="n"/>
       <c r="K255" s="6" t="n"/>
       <c r="M255" s="6" t="n"/>
+      <c r="O255" s="6" t="n"/>
     </row>
     <row r="256">
       <c r="E256" s="5" t="n"/>
       <c r="J256" s="5" t="n"/>
       <c r="K256" s="6" t="n"/>
       <c r="M256" s="6" t="n"/>
+      <c r="O256" s="6" t="n"/>
     </row>
     <row r="257">
       <c r="E257" s="5" t="n"/>
       <c r="J257" s="5" t="n"/>
       <c r="K257" s="6" t="n"/>
       <c r="M257" s="6" t="n"/>
+      <c r="O257" s="6" t="n"/>
     </row>
     <row r="258">
       <c r="E258" s="5" t="n"/>
       <c r="J258" s="5" t="n"/>
       <c r="K258" s="6" t="n"/>
       <c r="M258" s="6" t="n"/>
+      <c r="O258" s="6" t="n"/>
     </row>
     <row r="259">
       <c r="E259" s="5" t="n"/>
       <c r="J259" s="5" t="n"/>
       <c r="K259" s="6" t="n"/>
       <c r="M259" s="6" t="n"/>
+      <c r="O259" s="6" t="n"/>
     </row>
     <row r="260">
       <c r="E260" s="5" t="n"/>
       <c r="J260" s="5" t="n"/>
       <c r="K260" s="6" t="n"/>
       <c r="M260" s="6" t="n"/>
+      <c r="O260" s="6" t="n"/>
     </row>
     <row r="261">
       <c r="E261" s="5" t="n"/>
       <c r="J261" s="5" t="n"/>
       <c r="K261" s="6" t="n"/>
       <c r="M261" s="6" t="n"/>
+      <c r="O261" s="6" t="n"/>
     </row>
     <row r="262">
       <c r="E262" s="5" t="n"/>
       <c r="J262" s="5" t="n"/>
       <c r="K262" s="6" t="n"/>
       <c r="M262" s="6" t="n"/>
+      <c r="O262" s="6" t="n"/>
     </row>
     <row r="263">
       <c r="E263" s="5" t="n"/>
       <c r="J263" s="5" t="n"/>
       <c r="K263" s="6" t="n"/>
       <c r="M263" s="6" t="n"/>
+      <c r="O263" s="6" t="n"/>
     </row>
     <row r="264">
       <c r="E264" s="5" t="n"/>
       <c r="J264" s="5" t="n"/>
       <c r="K264" s="6" t="n"/>
       <c r="M264" s="6" t="n"/>
+      <c r="O264" s="6" t="n"/>
     </row>
     <row r="265">
       <c r="E265" s="5" t="n"/>
       <c r="J265" s="5" t="n"/>
       <c r="K265" s="6" t="n"/>
       <c r="M265" s="6" t="n"/>
+      <c r="O265" s="6" t="n"/>
     </row>
     <row r="266">
       <c r="E266" s="5" t="n"/>
       <c r="J266" s="5" t="n"/>
       <c r="K266" s="6" t="n"/>
       <c r="M266" s="6" t="n"/>
+      <c r="O266" s="6" t="n"/>
     </row>
     <row r="267">
       <c r="E267" s="5" t="n"/>
       <c r="J267" s="5" t="n"/>
       <c r="K267" s="6" t="n"/>
       <c r="M267" s="6" t="n"/>
+      <c r="O267" s="6" t="n"/>
     </row>
     <row r="268">
       <c r="E268" s="5" t="n"/>
       <c r="J268" s="5" t="n"/>
       <c r="K268" s="6" t="n"/>
       <c r="M268" s="6" t="n"/>
+      <c r="O268" s="6" t="n"/>
     </row>
     <row r="269">
       <c r="E269" s="5" t="n"/>
       <c r="J269" s="5" t="n"/>
       <c r="K269" s="6" t="n"/>
       <c r="M269" s="6" t="n"/>
+      <c r="O269" s="6" t="n"/>
     </row>
     <row r="270">
       <c r="E270" s="5" t="n"/>
       <c r="J270" s="5" t="n"/>
       <c r="K270" s="6" t="n"/>
       <c r="M270" s="6" t="n"/>
+      <c r="O270" s="6" t="n"/>
     </row>
     <row r="271">
       <c r="E271" s="5" t="n"/>
       <c r="J271" s="5" t="n"/>
       <c r="K271" s="6" t="n"/>
       <c r="M271" s="6" t="n"/>
+      <c r="O271" s="6" t="n"/>
     </row>
     <row r="272">
       <c r="E272" s="5" t="n"/>
       <c r="J272" s="5" t="n"/>
       <c r="K272" s="6" t="n"/>
       <c r="M272" s="6" t="n"/>
+      <c r="O272" s="6" t="n"/>
     </row>
     <row r="273">
       <c r="E273" s="5" t="n"/>
       <c r="J273" s="5" t="n"/>
       <c r="K273" s="6" t="n"/>
       <c r="M273" s="6" t="n"/>
+      <c r="O273" s="6" t="n"/>
     </row>
     <row r="274">
       <c r="E274" s="5" t="n"/>
       <c r="J274" s="5" t="n"/>
       <c r="K274" s="6" t="n"/>
       <c r="M274" s="6" t="n"/>
+      <c r="O274" s="6" t="n"/>
     </row>
     <row r="275">
       <c r="E275" s="5" t="n"/>
       <c r="J275" s="5" t="n"/>
       <c r="K275" s="6" t="n"/>
       <c r="M275" s="6" t="n"/>
+      <c r="O275" s="6" t="n"/>
     </row>
     <row r="276">
       <c r="E276" s="5" t="n"/>
       <c r="J276" s="5" t="n"/>
       <c r="K276" s="6" t="n"/>
       <c r="M276" s="6" t="n"/>
+      <c r="O276" s="6" t="n"/>
     </row>
     <row r="277">
       <c r="E277" s="5" t="n"/>
       <c r="J277" s="5" t="n"/>
       <c r="K277" s="6" t="n"/>
       <c r="M277" s="6" t="n"/>
+      <c r="O277" s="6" t="n"/>
     </row>
     <row r="278">
       <c r="E278" s="5" t="n"/>
       <c r="J278" s="5" t="n"/>
       <c r="K278" s="6" t="n"/>
       <c r="M278" s="6" t="n"/>
+      <c r="O278" s="6" t="n"/>
     </row>
     <row r="279">
       <c r="E279" s="5" t="n"/>
       <c r="J279" s="5" t="n"/>
       <c r="K279" s="6" t="n"/>
       <c r="M279" s="6" t="n"/>
+      <c r="O279" s="6" t="n"/>
     </row>
     <row r="280">
       <c r="E280" s="5" t="n"/>
       <c r="J280" s="5" t="n"/>
       <c r="K280" s="6" t="n"/>
       <c r="M280" s="6" t="n"/>
+      <c r="O280" s="6" t="n"/>
     </row>
     <row r="281">
       <c r="E281" s="5" t="n"/>
       <c r="J281" s="5" t="n"/>
       <c r="K281" s="6" t="n"/>
       <c r="M281" s="6" t="n"/>
+      <c r="O281" s="6" t="n"/>
     </row>
     <row r="282">
       <c r="E282" s="5" t="n"/>
       <c r="J282" s="5" t="n"/>
       <c r="K282" s="6" t="n"/>
       <c r="M282" s="6" t="n"/>
+      <c r="O282" s="6" t="n"/>
     </row>
     <row r="283">
       <c r="E283" s="5" t="n"/>
       <c r="J283" s="5" t="n"/>
       <c r="K283" s="6" t="n"/>
       <c r="M283" s="6" t="n"/>
+      <c r="O283" s="6" t="n"/>
     </row>
     <row r="284">
       <c r="E284" s="5" t="n"/>
       <c r="J284" s="5" t="n"/>
       <c r="K284" s="6" t="n"/>
       <c r="M284" s="6" t="n"/>
+      <c r="O284" s="6" t="n"/>
     </row>
     <row r="285">
       <c r="E285" s="5" t="n"/>
       <c r="J285" s="5" t="n"/>
       <c r="K285" s="6" t="n"/>
       <c r="M285" s="6" t="n"/>
+      <c r="O285" s="6" t="n"/>
     </row>
     <row r="286">
       <c r="E286" s="5" t="n"/>
       <c r="J286" s="5" t="n"/>
       <c r="K286" s="6" t="n"/>
       <c r="M286" s="6" t="n"/>
+      <c r="O286" s="6" t="n"/>
     </row>
     <row r="287">
       <c r="E287" s="5" t="n"/>
       <c r="J287" s="5" t="n"/>
       <c r="K287" s="6" t="n"/>
       <c r="M287" s="6" t="n"/>
+      <c r="O287" s="6" t="n"/>
     </row>
     <row r="288">
       <c r="E288" s="5" t="n"/>
       <c r="J288" s="5" t="n"/>
       <c r="K288" s="6" t="n"/>
       <c r="M288" s="6" t="n"/>
+      <c r="O288" s="6" t="n"/>
     </row>
     <row r="289">
       <c r="E289" s="5" t="n"/>
       <c r="J289" s="5" t="n"/>
       <c r="K289" s="6" t="n"/>
       <c r="M289" s="6" t="n"/>
+      <c r="O289" s="6" t="n"/>
     </row>
     <row r="290">
       <c r="E290" s="5" t="n"/>
       <c r="J290" s="5" t="n"/>
       <c r="K290" s="6" t="n"/>
       <c r="M290" s="6" t="n"/>
+      <c r="O290" s="6" t="n"/>
     </row>
     <row r="291">
       <c r="E291" s="5" t="n"/>
       <c r="J291" s="5" t="n"/>
       <c r="K291" s="6" t="n"/>
       <c r="M291" s="6" t="n"/>
+      <c r="O291" s="6" t="n"/>
     </row>
     <row r="292">
       <c r="E292" s="5" t="n"/>
       <c r="J292" s="5" t="n"/>
       <c r="K292" s="6" t="n"/>
       <c r="M292" s="6" t="n"/>
+      <c r="O292" s="6" t="n"/>
     </row>
     <row r="293">
       <c r="E293" s="5" t="n"/>
       <c r="J293" s="5" t="n"/>
       <c r="K293" s="6" t="n"/>
       <c r="M293" s="6" t="n"/>
+      <c r="O293" s="6" t="n"/>
     </row>
     <row r="294">
       <c r="E294" s="5" t="n"/>
       <c r="J294" s="5" t="n"/>
       <c r="K294" s="6" t="n"/>
       <c r="M294" s="6" t="n"/>
+      <c r="O294" s="6" t="n"/>
     </row>
     <row r="295">
       <c r="E295" s="5" t="n"/>
       <c r="J295" s="5" t="n"/>
       <c r="K295" s="6" t="n"/>
       <c r="M295" s="6" t="n"/>
+      <c r="O295" s="6" t="n"/>
     </row>
     <row r="296">
       <c r="E296" s="5" t="n"/>
       <c r="J296" s="5" t="n"/>
       <c r="K296" s="6" t="n"/>
       <c r="M296" s="6" t="n"/>
+      <c r="O296" s="6" t="n"/>
     </row>
     <row r="297">
       <c r="E297" s="5" t="n"/>
       <c r="J297" s="5" t="n"/>
       <c r="K297" s="6" t="n"/>
       <c r="M297" s="6" t="n"/>
+      <c r="O297" s="6" t="n"/>
     </row>
     <row r="298">
       <c r="E298" s="5" t="n"/>
       <c r="J298" s="5" t="n"/>
       <c r="K298" s="6" t="n"/>
       <c r="M298" s="6" t="n"/>
+      <c r="O298" s="6" t="n"/>
     </row>
     <row r="299">
       <c r="E299" s="5" t="n"/>
       <c r="J299" s="5" t="n"/>
       <c r="K299" s="6" t="n"/>
       <c r="M299" s="6" t="n"/>
+      <c r="O299" s="6" t="n"/>
     </row>
     <row r="300">
       <c r="E300" s="5" t="n"/>
       <c r="J300" s="5" t="n"/>
       <c r="K300" s="6" t="n"/>
       <c r="M300" s="6" t="n"/>
+      <c r="O300" s="6" t="n"/>
     </row>
     <row r="301">
       <c r="E301" s="5" t="n"/>
       <c r="J301" s="5" t="n"/>
       <c r="K301" s="6" t="n"/>
       <c r="M301" s="6" t="n"/>
+      <c r="O301" s="6" t="n"/>
     </row>
     <row r="302">
       <c r="E302" s="5" t="n"/>
       <c r="J302" s="5" t="n"/>
       <c r="K302" s="6" t="n"/>
       <c r="M302" s="6" t="n"/>
+      <c r="O302" s="6" t="n"/>
     </row>
     <row r="303">
       <c r="E303" s="5" t="n"/>
       <c r="J303" s="5" t="n"/>
       <c r="K303" s="6" t="n"/>
       <c r="M303" s="6" t="n"/>
+      <c r="O303" s="6" t="n"/>
     </row>
     <row r="304">
       <c r="E304" s="5" t="n"/>
       <c r="J304" s="5" t="n"/>
       <c r="K304" s="6" t="n"/>
       <c r="M304" s="6" t="n"/>
+      <c r="O304" s="6" t="n"/>
     </row>
     <row r="305">
       <c r="E305" s="5" t="n"/>
       <c r="J305" s="5" t="n"/>
       <c r="K305" s="6" t="n"/>
       <c r="M305" s="6" t="n"/>
+      <c r="O305" s="6" t="n"/>
     </row>
     <row r="306">
       <c r="E306" s="5" t="n"/>
       <c r="J306" s="5" t="n"/>
       <c r="K306" s="6" t="n"/>
       <c r="M306" s="6" t="n"/>
+      <c r="O306" s="6" t="n"/>
     </row>
     <row r="307">
       <c r="E307" s="5" t="n"/>
       <c r="J307" s="5" t="n"/>
       <c r="K307" s="6" t="n"/>
       <c r="M307" s="6" t="n"/>
+      <c r="O307" s="6" t="n"/>
     </row>
     <row r="308">
       <c r="E308" s="5" t="n"/>
       <c r="J308" s="5" t="n"/>
       <c r="K308" s="6" t="n"/>
       <c r="M308" s="6" t="n"/>
+      <c r="O308" s="6" t="n"/>
     </row>
     <row r="309">
       <c r="E309" s="5" t="n"/>
       <c r="J309" s="5" t="n"/>
       <c r="K309" s="6" t="n"/>
       <c r="M309" s="6" t="n"/>
+      <c r="O309" s="6" t="n"/>
     </row>
     <row r="310">
       <c r="E310" s="5" t="n"/>
       <c r="J310" s="5" t="n"/>
       <c r="K310" s="6" t="n"/>
       <c r="M310" s="6" t="n"/>
+      <c r="O310" s="6" t="n"/>
     </row>
     <row r="311">
       <c r="E311" s="5" t="n"/>
       <c r="J311" s="5" t="n"/>
       <c r="K311" s="6" t="n"/>
       <c r="M311" s="6" t="n"/>
+      <c r="O311" s="6" t="n"/>
     </row>
     <row r="312">
       <c r="E312" s="5" t="n"/>
       <c r="J312" s="5" t="n"/>
       <c r="K312" s="6" t="n"/>
       <c r="M312" s="6" t="n"/>
+      <c r="O312" s="6" t="n"/>
     </row>
     <row r="313">
       <c r="E313" s="5" t="n"/>
       <c r="J313" s="5" t="n"/>
       <c r="K313" s="6" t="n"/>
       <c r="M313" s="6" t="n"/>
+      <c r="O313" s="6" t="n"/>
     </row>
     <row r="314">
       <c r="E314" s="5" t="n"/>
       <c r="J314" s="5" t="n"/>
       <c r="K314" s="6" t="n"/>
       <c r="M314" s="6" t="n"/>
+      <c r="O314" s="6" t="n"/>
     </row>
     <row r="315">
       <c r="E315" s="5" t="n"/>
       <c r="J315" s="5" t="n"/>
       <c r="K315" s="6" t="n"/>
       <c r="M315" s="6" t="n"/>
+      <c r="O315" s="6" t="n"/>
     </row>
     <row r="316">
       <c r="E316" s="5" t="n"/>
       <c r="J316" s="5" t="n"/>
       <c r="K316" s="6" t="n"/>
       <c r="M316" s="6" t="n"/>
+      <c r="O316" s="6" t="n"/>
     </row>
     <row r="317">
       <c r="E317" s="5" t="n"/>
       <c r="J317" s="5" t="n"/>
       <c r="K317" s="6" t="n"/>
       <c r="M317" s="6" t="n"/>
+      <c r="O317" s="6" t="n"/>
     </row>
     <row r="318">
       <c r="E318" s="5" t="n"/>
       <c r="J318" s="5" t="n"/>
       <c r="K318" s="6" t="n"/>
       <c r="M318" s="6" t="n"/>
+      <c r="O318" s="6" t="n"/>
     </row>
     <row r="319">
       <c r="E319" s="5" t="n"/>
       <c r="J319" s="5" t="n"/>
       <c r="K319" s="6" t="n"/>
       <c r="M319" s="6" t="n"/>
+      <c r="O319" s="6" t="n"/>
     </row>
     <row r="320">
       <c r="E320" s="5" t="n"/>
       <c r="J320" s="5" t="n"/>
       <c r="K320" s="6" t="n"/>
       <c r="M320" s="6" t="n"/>
+      <c r="O320" s="6" t="n"/>
     </row>
     <row r="321">
       <c r="E321" s="5" t="n"/>
       <c r="J321" s="5" t="n"/>
       <c r="K321" s="6" t="n"/>
       <c r="M321" s="6" t="n"/>
+      <c r="O321" s="6" t="n"/>
     </row>
     <row r="322">
       <c r="E322" s="5" t="n"/>
       <c r="J322" s="5" t="n"/>
       <c r="K322" s="6" t="n"/>
       <c r="M322" s="6" t="n"/>
+      <c r="O322" s="6" t="n"/>
     </row>
     <row r="323">
       <c r="E323" s="5" t="n"/>
       <c r="J323" s="5" t="n"/>
       <c r="K323" s="6" t="n"/>
       <c r="M323" s="6" t="n"/>
+      <c r="O323" s="6" t="n"/>
     </row>
     <row r="324">
       <c r="E324" s="5" t="n"/>
       <c r="J324" s="5" t="n"/>
       <c r="K324" s="6" t="n"/>
       <c r="M324" s="6" t="n"/>
+      <c r="O324" s="6" t="n"/>
     </row>
     <row r="325">
       <c r="E325" s="5" t="n"/>
       <c r="J325" s="5" t="n"/>
       <c r="K325" s="6" t="n"/>
       <c r="M325" s="6" t="n"/>
+      <c r="O325" s="6" t="n"/>
     </row>
     <row r="326">
       <c r="E326" s="5" t="n"/>
       <c r="J326" s="5" t="n"/>
       <c r="K326" s="6" t="n"/>
       <c r="M326" s="6" t="n"/>
+      <c r="O326" s="6" t="n"/>
     </row>
     <row r="327">
       <c r="E327" s="5" t="n"/>
       <c r="J327" s="5" t="n"/>
       <c r="K327" s="6" t="n"/>
       <c r="M327" s="6" t="n"/>
+      <c r="O327" s="6" t="n"/>
     </row>
     <row r="328">
       <c r="E328" s="5" t="n"/>
       <c r="J328" s="5" t="n"/>
       <c r="K328" s="6" t="n"/>
       <c r="M328" s="6" t="n"/>
+      <c r="O328" s="6" t="n"/>
     </row>
     <row r="329">
       <c r="E329" s="5" t="n"/>
       <c r="J329" s="5" t="n"/>
       <c r="K329" s="6" t="n"/>
       <c r="M329" s="6" t="n"/>
+      <c r="O329" s="6" t="n"/>
     </row>
     <row r="330">
       <c r="E330" s="5" t="n"/>
       <c r="J330" s="5" t="n"/>
       <c r="K330" s="6" t="n"/>
       <c r="M330" s="6" t="n"/>
+      <c r="O330" s="6" t="n"/>
     </row>
     <row r="331">
       <c r="E331" s="5" t="n"/>
       <c r="J331" s="5" t="n"/>
       <c r="K331" s="6" t="n"/>
       <c r="M331" s="6" t="n"/>
+      <c r="O331" s="6" t="n"/>
     </row>
     <row r="332">
       <c r="E332" s="5" t="n"/>
       <c r="J332" s="5" t="n"/>
       <c r="K332" s="6" t="n"/>
       <c r="M332" s="6" t="n"/>
+      <c r="O332" s="6" t="n"/>
     </row>
     <row r="333">
       <c r="E333" s="5" t="n"/>
       <c r="J333" s="5" t="n"/>
       <c r="K333" s="6" t="n"/>
       <c r="M333" s="6" t="n"/>
+      <c r="O333" s="6" t="n"/>
     </row>
     <row r="334">
       <c r="E334" s="5" t="n"/>
       <c r="J334" s="5" t="n"/>
       <c r="K334" s="6" t="n"/>
       <c r="M334" s="6" t="n"/>
+      <c r="O334" s="6" t="n"/>
     </row>
     <row r="335">
       <c r="E335" s="5" t="n"/>
       <c r="J335" s="5" t="n"/>
       <c r="K335" s="6" t="n"/>
       <c r="M335" s="6" t="n"/>
+      <c r="O335" s="6" t="n"/>
     </row>
     <row r="336">
       <c r="E336" s="5" t="n"/>
       <c r="J336" s="5" t="n"/>
       <c r="K336" s="6" t="n"/>
       <c r="M336" s="6" t="n"/>
+      <c r="O336" s="6" t="n"/>
     </row>
     <row r="337">
       <c r="E337" s="5" t="n"/>
       <c r="J337" s="5" t="n"/>
       <c r="K337" s="6" t="n"/>
       <c r="M337" s="6" t="n"/>
+      <c r="O337" s="6" t="n"/>
     </row>
     <row r="338">
       <c r="E338" s="5" t="n"/>
       <c r="J338" s="5" t="n"/>
       <c r="K338" s="6" t="n"/>
       <c r="M338" s="6" t="n"/>
+      <c r="O338" s="6" t="n"/>
     </row>
     <row r="339">
       <c r="E339" s="5" t="n"/>
       <c r="J339" s="5" t="n"/>
       <c r="K339" s="6" t="n"/>
       <c r="M339" s="6" t="n"/>
+      <c r="O339" s="6" t="n"/>
     </row>
     <row r="340">
       <c r="E340" s="5" t="n"/>
       <c r="J340" s="5" t="n"/>
       <c r="K340" s="6" t="n"/>
       <c r="M340" s="6" t="n"/>
+      <c r="O340" s="6" t="n"/>
     </row>
     <row r="341">
       <c r="E341" s="5" t="n"/>
       <c r="J341" s="5" t="n"/>
       <c r="K341" s="6" t="n"/>
       <c r="M341" s="6" t="n"/>
+      <c r="O341" s="6" t="n"/>
     </row>
     <row r="342">
       <c r="E342" s="5" t="n"/>
       <c r="J342" s="5" t="n"/>
       <c r="K342" s="6" t="n"/>
       <c r="M342" s="6" t="n"/>
+      <c r="O342" s="6" t="n"/>
     </row>
     <row r="343">
       <c r="E343" s="5" t="n"/>
       <c r="J343" s="5" t="n"/>
       <c r="K343" s="6" t="n"/>
       <c r="M343" s="6" t="n"/>
+      <c r="O343" s="6" t="n"/>
     </row>
     <row r="344">
       <c r="E344" s="5" t="n"/>
       <c r="J344" s="5" t="n"/>
       <c r="K344" s="6" t="n"/>
       <c r="M344" s="6" t="n"/>
+      <c r="O344" s="6" t="n"/>
     </row>
     <row r="345">
       <c r="E345" s="5" t="n"/>
       <c r="J345" s="5" t="n"/>
       <c r="K345" s="6" t="n"/>
       <c r="M345" s="6" t="n"/>
+      <c r="O345" s="6" t="n"/>
     </row>
     <row r="346">
       <c r="E346" s="5" t="n"/>
       <c r="J346" s="5" t="n"/>
       <c r="K346" s="6" t="n"/>
       <c r="M346" s="6" t="n"/>
+      <c r="O346" s="6" t="n"/>
     </row>
     <row r="347">
       <c r="E347" s="5" t="n"/>
       <c r="J347" s="5" t="n"/>
       <c r="K347" s="6" t="n"/>
       <c r="M347" s="6" t="n"/>
+      <c r="O347" s="6" t="n"/>
     </row>
     <row r="348">
       <c r="E348" s="5" t="n"/>
       <c r="J348" s="5" t="n"/>
       <c r="K348" s="6" t="n"/>
       <c r="M348" s="6" t="n"/>
+      <c r="O348" s="6" t="n"/>
     </row>
     <row r="349">
       <c r="E349" s="5" t="n"/>
       <c r="J349" s="5" t="n"/>
       <c r="K349" s="6" t="n"/>
       <c r="M349" s="6" t="n"/>
+      <c r="O349" s="6" t="n"/>
     </row>
     <row r="350">
       <c r="E350" s="5" t="n"/>
       <c r="J350" s="5" t="n"/>
       <c r="K350" s="6" t="n"/>
       <c r="M350" s="6" t="n"/>
+      <c r="O350" s="6" t="n"/>
     </row>
     <row r="351">
       <c r="E351" s="5" t="n"/>
       <c r="J351" s="5" t="n"/>
       <c r="K351" s="6" t="n"/>
       <c r="M351" s="6" t="n"/>
+      <c r="O351" s="6" t="n"/>
     </row>
     <row r="352">
       <c r="E352" s="5" t="n"/>
       <c r="J352" s="5" t="n"/>
       <c r="K352" s="6" t="n"/>
       <c r="M352" s="6" t="n"/>
+      <c r="O352" s="6" t="n"/>
     </row>
     <row r="353">
       <c r="E353" s="5" t="n"/>
       <c r="J353" s="5" t="n"/>
       <c r="K353" s="6" t="n"/>
       <c r="M353" s="6" t="n"/>
+      <c r="O353" s="6" t="n"/>
     </row>
     <row r="354">
       <c r="E354" s="5" t="n"/>
       <c r="J354" s="5" t="n"/>
       <c r="K354" s="6" t="n"/>
       <c r="M354" s="6" t="n"/>
+      <c r="O354" s="6" t="n"/>
     </row>
     <row r="355">
       <c r="E355" s="5" t="n"/>
       <c r="J355" s="5" t="n"/>
       <c r="K355" s="6" t="n"/>
       <c r="M355" s="6" t="n"/>
+      <c r="O355" s="6" t="n"/>
     </row>
     <row r="356">
       <c r="E356" s="5" t="n"/>
       <c r="J356" s="5" t="n"/>
       <c r="K356" s="6" t="n"/>
       <c r="M356" s="6" t="n"/>
+      <c r="O356" s="6" t="n"/>
     </row>
     <row r="357">
       <c r="E357" s="5" t="n"/>
       <c r="J357" s="5" t="n"/>
       <c r="K357" s="6" t="n"/>
       <c r="M357" s="6" t="n"/>
+      <c r="O357" s="6" t="n"/>
     </row>
     <row r="358">
       <c r="E358" s="5" t="n"/>
       <c r="J358" s="5" t="n"/>
       <c r="K358" s="6" t="n"/>
       <c r="M358" s="6" t="n"/>
+      <c r="O358" s="6" t="n"/>
     </row>
     <row r="359">
       <c r="E359" s="5" t="n"/>
       <c r="J359" s="5" t="n"/>
       <c r="K359" s="6" t="n"/>
       <c r="M359" s="6" t="n"/>
+      <c r="O359" s="6" t="n"/>
     </row>
     <row r="360">
       <c r="E360" s="5" t="n"/>
       <c r="J360" s="5" t="n"/>
       <c r="K360" s="6" t="n"/>
       <c r="M360" s="6" t="n"/>
+      <c r="O360" s="6" t="n"/>
     </row>
     <row r="361">
       <c r="E361" s="5" t="n"/>
       <c r="J361" s="5" t="n"/>
       <c r="K361" s="6" t="n"/>
       <c r="M361" s="6" t="n"/>
+      <c r="O361" s="6" t="n"/>
     </row>
     <row r="362">
       <c r="E362" s="5" t="n"/>
       <c r="J362" s="5" t="n"/>
       <c r="K362" s="6" t="n"/>
       <c r="M362" s="6" t="n"/>
+      <c r="O362" s="6" t="n"/>
     </row>
     <row r="363">
       <c r="E363" s="5" t="n"/>
       <c r="J363" s="5" t="n"/>
       <c r="K363" s="6" t="n"/>
       <c r="M363" s="6" t="n"/>
+      <c r="O363" s="6" t="n"/>
     </row>
     <row r="364">
       <c r="E364" s="5" t="n"/>
       <c r="J364" s="5" t="n"/>
       <c r="K364" s="6" t="n"/>
       <c r="M364" s="6" t="n"/>
+      <c r="O364" s="6" t="n"/>
     </row>
     <row r="365">
       <c r="E365" s="5" t="n"/>
       <c r="J365" s="5" t="n"/>
       <c r="K365" s="6" t="n"/>
       <c r="M365" s="6" t="n"/>
+      <c r="O365" s="6" t="n"/>
     </row>
     <row r="366">
       <c r="E366" s="5" t="n"/>
       <c r="J366" s="5" t="n"/>
       <c r="K366" s="6" t="n"/>
       <c r="M366" s="6" t="n"/>
+      <c r="O366" s="6" t="n"/>
     </row>
     <row r="367">
       <c r="E367" s="5" t="n"/>
       <c r="J367" s="5" t="n"/>
       <c r="K367" s="6" t="n"/>
       <c r="M367" s="6" t="n"/>
+      <c r="O367" s="6" t="n"/>
     </row>
     <row r="368">
       <c r="E368" s="5" t="n"/>
       <c r="J368" s="5" t="n"/>
       <c r="K368" s="6" t="n"/>
       <c r="M368" s="6" t="n"/>
+      <c r="O368" s="6" t="n"/>
     </row>
     <row r="369">
       <c r="E369" s="5" t="n"/>
       <c r="J369" s="5" t="n"/>
       <c r="K369" s="6" t="n"/>
       <c r="M369" s="6" t="n"/>
+      <c r="O369" s="6" t="n"/>
     </row>
     <row r="370">
       <c r="E370" s="5" t="n"/>
       <c r="J370" s="5" t="n"/>
       <c r="K370" s="6" t="n"/>
       <c r="M370" s="6" t="n"/>
+      <c r="O370" s="6" t="n"/>
     </row>
     <row r="371">
       <c r="E371" s="5" t="n"/>
       <c r="J371" s="5" t="n"/>
       <c r="K371" s="6" t="n"/>
       <c r="M371" s="6" t="n"/>
+      <c r="O371" s="6" t="n"/>
     </row>
     <row r="372">
       <c r="E372" s="5" t="n"/>
       <c r="J372" s="5" t="n"/>
       <c r="K372" s="6" t="n"/>
       <c r="M372" s="6" t="n"/>
+      <c r="O372" s="6" t="n"/>
     </row>
     <row r="373">
       <c r="E373" s="5" t="n"/>
       <c r="J373" s="5" t="n"/>
       <c r="K373" s="6" t="n"/>
       <c r="M373" s="6" t="n"/>
+      <c r="O373" s="6" t="n"/>
     </row>
     <row r="374">
       <c r="E374" s="5" t="n"/>
       <c r="J374" s="5" t="n"/>
       <c r="K374" s="6" t="n"/>
       <c r="M374" s="6" t="n"/>
+      <c r="O374" s="6" t="n"/>
     </row>
     <row r="375">
       <c r="E375" s="5" t="n"/>
       <c r="J375" s="5" t="n"/>
       <c r="K375" s="6" t="n"/>
       <c r="M375" s="6" t="n"/>
+      <c r="O375" s="6" t="n"/>
     </row>
     <row r="376">
       <c r="E376" s="5" t="n"/>
       <c r="J376" s="5" t="n"/>
       <c r="K376" s="6" t="n"/>
       <c r="M376" s="6" t="n"/>
+      <c r="O376" s="6" t="n"/>
     </row>
     <row r="377">
       <c r="E377" s="5" t="n"/>
       <c r="J377" s="5" t="n"/>
       <c r="K377" s="6" t="n"/>
       <c r="M377" s="6" t="n"/>
+      <c r="O377" s="6" t="n"/>
     </row>
     <row r="378">
       <c r="E378" s="5" t="n"/>
       <c r="J378" s="5" t="n"/>
       <c r="K378" s="6" t="n"/>
       <c r="M378" s="6" t="n"/>
+      <c r="O378" s="6" t="n"/>
     </row>
     <row r="379">
       <c r="E379" s="5" t="n"/>
       <c r="J379" s="5" t="n"/>
       <c r="K379" s="6" t="n"/>
       <c r="M379" s="6" t="n"/>
+      <c r="O379" s="6" t="n"/>
     </row>
     <row r="380">
       <c r="E380" s="5" t="n"/>
       <c r="J380" s="5" t="n"/>
       <c r="K380" s="6" t="n"/>
       <c r="M380" s="6" t="n"/>
+      <c r="O380" s="6" t="n"/>
     </row>
     <row r="381">
       <c r="E381" s="5" t="n"/>
       <c r="J381" s="5" t="n"/>
       <c r="K381" s="6" t="n"/>
       <c r="M381" s="6" t="n"/>
+      <c r="O381" s="6" t="n"/>
     </row>
     <row r="382">
       <c r="E382" s="5" t="n"/>
       <c r="J382" s="5" t="n"/>
       <c r="K382" s="6" t="n"/>
       <c r="M382" s="6" t="n"/>
+      <c r="O382" s="6" t="n"/>
     </row>
     <row r="383">
       <c r="E383" s="5" t="n"/>
       <c r="J383" s="5" t="n"/>
       <c r="K383" s="6" t="n"/>
       <c r="M383" s="6" t="n"/>
+      <c r="O383" s="6" t="n"/>
     </row>
     <row r="384">
       <c r="E384" s="5" t="n"/>
       <c r="J384" s="5" t="n"/>
       <c r="K384" s="6" t="n"/>
       <c r="M384" s="6" t="n"/>
+      <c r="O384" s="6" t="n"/>
     </row>
     <row r="385">
       <c r="E385" s="5" t="n"/>
       <c r="J385" s="5" t="n"/>
       <c r="K385" s="6" t="n"/>
       <c r="M385" s="6" t="n"/>
+      <c r="O385" s="6" t="n"/>
     </row>
     <row r="386">
       <c r="E386" s="5" t="n"/>
       <c r="J386" s="5" t="n"/>
       <c r="K386" s="6" t="n"/>
       <c r="M386" s="6" t="n"/>
+      <c r="O386" s="6" t="n"/>
     </row>
     <row r="387">
       <c r="E387" s="5" t="n"/>
       <c r="J387" s="5" t="n"/>
       <c r="K387" s="6" t="n"/>
       <c r="M387" s="6" t="n"/>
+      <c r="O387" s="6" t="n"/>
     </row>
     <row r="388">
       <c r="E388" s="5" t="n"/>
       <c r="J388" s="5" t="n"/>
       <c r="K388" s="6" t="n"/>
       <c r="M388" s="6" t="n"/>
+      <c r="O388" s="6" t="n"/>
     </row>
     <row r="389">
       <c r="E389" s="5" t="n"/>
       <c r="J389" s="5" t="n"/>
       <c r="K389" s="6" t="n"/>
       <c r="M389" s="6" t="n"/>
+      <c r="O389" s="6" t="n"/>
     </row>
     <row r="390">
       <c r="E390" s="5" t="n"/>
       <c r="J390" s="5" t="n"/>
       <c r="K390" s="6" t="n"/>
       <c r="M390" s="6" t="n"/>
+      <c r="O390" s="6" t="n"/>
     </row>
     <row r="391">
       <c r="E391" s="5" t="n"/>
       <c r="J391" s="5" t="n"/>
       <c r="K391" s="6" t="n"/>
       <c r="M391" s="6" t="n"/>
+      <c r="O391" s="6" t="n"/>
     </row>
     <row r="392">
       <c r="E392" s="5" t="n"/>
       <c r="J392" s="5" t="n"/>
       <c r="K392" s="6" t="n"/>
       <c r="M392" s="6" t="n"/>
+      <c r="O392" s="6" t="n"/>
     </row>
     <row r="393">
       <c r="E393" s="5" t="n"/>
       <c r="J393" s="5" t="n"/>
       <c r="K393" s="6" t="n"/>
       <c r="M393" s="6" t="n"/>
+      <c r="O393" s="6" t="n"/>
     </row>
     <row r="394">
       <c r="E394" s="5" t="n"/>
       <c r="J394" s="5" t="n"/>
       <c r="K394" s="6" t="n"/>
       <c r="M394" s="6" t="n"/>
+      <c r="O394" s="6" t="n"/>
     </row>
     <row r="395">
       <c r="E395" s="5" t="n"/>
       <c r="J395" s="5" t="n"/>
       <c r="K395" s="6" t="n"/>
       <c r="M395" s="6" t="n"/>
+      <c r="O395" s="6" t="n"/>
     </row>
     <row r="396">
       <c r="E396" s="5" t="n"/>
       <c r="J396" s="5" t="n"/>
       <c r="K396" s="6" t="n"/>
       <c r="M396" s="6" t="n"/>
+      <c r="O396" s="6" t="n"/>
     </row>
     <row r="397">
       <c r="E397" s="5" t="n"/>
       <c r="J397" s="5" t="n"/>
       <c r="K397" s="6" t="n"/>
       <c r="M397" s="6" t="n"/>
+      <c r="O397" s="6" t="n"/>
     </row>
     <row r="398">
       <c r="E398" s="5" t="n"/>
       <c r="J398" s="5" t="n"/>
       <c r="K398" s="6" t="n"/>
       <c r="M398" s="6" t="n"/>
+      <c r="O398" s="6" t="n"/>
     </row>
     <row r="399">
       <c r="E399" s="5" t="n"/>
       <c r="J399" s="5" t="n"/>
       <c r="K399" s="6" t="n"/>
       <c r="M399" s="6" t="n"/>
+      <c r="O399" s="6" t="n"/>
     </row>
     <row r="400">
       <c r="E400" s="5" t="n"/>
       <c r="J400" s="5" t="n"/>
       <c r="K400" s="6" t="n"/>
       <c r="M400" s="6" t="n"/>
+      <c r="O400" s="6" t="n"/>
     </row>
     <row r="401">
       <c r="E401" s="5" t="n"/>
       <c r="J401" s="5" t="n"/>
       <c r="K401" s="6" t="n"/>
       <c r="M401" s="6" t="n"/>
+      <c r="O401" s="6" t="n"/>
     </row>
     <row r="402">
       <c r="E402" s="5" t="n"/>
       <c r="J402" s="5" t="n"/>
       <c r="K402" s="6" t="n"/>
       <c r="M402" s="6" t="n"/>
+      <c r="O402" s="6" t="n"/>
     </row>
     <row r="403">
       <c r="E403" s="5" t="n"/>
       <c r="J403" s="5" t="n"/>
       <c r="K403" s="6" t="n"/>
       <c r="M403" s="6" t="n"/>
+      <c r="O403" s="6" t="n"/>
     </row>
     <row r="404">
       <c r="E404" s="5" t="n"/>
       <c r="J404" s="5" t="n"/>
       <c r="K404" s="6" t="n"/>
       <c r="M404" s="6" t="n"/>
+      <c r="O404" s="6" t="n"/>
     </row>
     <row r="405">
       <c r="E405" s="5" t="n"/>
       <c r="J405" s="5" t="n"/>
       <c r="K405" s="6" t="n"/>
       <c r="M405" s="6" t="n"/>
+      <c r="O405" s="6" t="n"/>
     </row>
     <row r="406">
       <c r="E406" s="5" t="n"/>
       <c r="J406" s="5" t="n"/>
       <c r="K406" s="6" t="n"/>
       <c r="M406" s="6" t="n"/>
+      <c r="O406" s="6" t="n"/>
     </row>
     <row r="407">
       <c r="E407" s="5" t="n"/>
       <c r="J407" s="5" t="n"/>
       <c r="K407" s="6" t="n"/>
       <c r="M407" s="6" t="n"/>
+      <c r="O407" s="6" t="n"/>
     </row>
     <row r="408">
       <c r="E408" s="5" t="n"/>
       <c r="J408" s="5" t="n"/>
       <c r="K408" s="6" t="n"/>
       <c r="M408" s="6" t="n"/>
+      <c r="O408" s="6" t="n"/>
     </row>
     <row r="409">
       <c r="E409" s="5" t="n"/>
       <c r="J409" s="5" t="n"/>
       <c r="K409" s="6" t="n"/>
       <c r="M409" s="6" t="n"/>
+      <c r="O409" s="6" t="n"/>
     </row>
     <row r="410">
       <c r="E410" s="5" t="n"/>
       <c r="J410" s="5" t="n"/>
       <c r="K410" s="6" t="n"/>
       <c r="M410" s="6" t="n"/>
+      <c r="O410" s="6" t="n"/>
     </row>
     <row r="411">
       <c r="E411" s="5" t="n"/>
       <c r="J411" s="5" t="n"/>
       <c r="K411" s="6" t="n"/>
       <c r="M411" s="6" t="n"/>
+      <c r="O411" s="6" t="n"/>
     </row>
     <row r="412">
       <c r="E412" s="5" t="n"/>
       <c r="J412" s="5" t="n"/>
       <c r="K412" s="6" t="n"/>
       <c r="M412" s="6" t="n"/>
+      <c r="O412" s="6" t="n"/>
     </row>
     <row r="413">
       <c r="E413" s="5" t="n"/>
       <c r="J413" s="5" t="n"/>
       <c r="K413" s="6" t="n"/>
       <c r="M413" s="6" t="n"/>
+      <c r="O413" s="6" t="n"/>
     </row>
     <row r="414">
       <c r="E414" s="5" t="n"/>
       <c r="J414" s="5" t="n"/>
       <c r="K414" s="6" t="n"/>
       <c r="M414" s="6" t="n"/>
+      <c r="O414" s="6" t="n"/>
     </row>
     <row r="415">
       <c r="E415" s="5" t="n"/>
       <c r="J415" s="5" t="n"/>
       <c r="K415" s="6" t="n"/>
       <c r="M415" s="6" t="n"/>
+      <c r="O415" s="6" t="n"/>
     </row>
     <row r="416">
       <c r="E416" s="5" t="n"/>
       <c r="J416" s="5" t="n"/>
       <c r="K416" s="6" t="n"/>
       <c r="M416" s="6" t="n"/>
+      <c r="O416" s="6" t="n"/>
     </row>
     <row r="417">
       <c r="E417" s="5" t="n"/>
       <c r="J417" s="5" t="n"/>
       <c r="K417" s="6" t="n"/>
       <c r="M417" s="6" t="n"/>
+      <c r="O417" s="6" t="n"/>
     </row>
     <row r="418">
       <c r="E418" s="5" t="n"/>
       <c r="J418" s="5" t="n"/>
       <c r="K418" s="6" t="n"/>
       <c r="M418" s="6" t="n"/>
+      <c r="O418" s="6" t="n"/>
     </row>
     <row r="419">
       <c r="E419" s="5" t="n"/>
       <c r="J419" s="5" t="n"/>
       <c r="K419" s="6" t="n"/>
       <c r="M419" s="6" t="n"/>
+      <c r="O419" s="6" t="n"/>
     </row>
     <row r="420">
       <c r="E420" s="5" t="n"/>
       <c r="J420" s="5" t="n"/>
       <c r="K420" s="6" t="n"/>
       <c r="M420" s="6" t="n"/>
+      <c r="O420" s="6" t="n"/>
     </row>
     <row r="421">
       <c r="E421" s="5" t="n"/>
       <c r="J421" s="5" t="n"/>
       <c r="K421" s="6" t="n"/>
       <c r="M421" s="6" t="n"/>
+      <c r="O421" s="6" t="n"/>
     </row>
     <row r="422">
       <c r="E422" s="5" t="n"/>
       <c r="J422" s="5" t="n"/>
       <c r="K422" s="6" t="n"/>
       <c r="M422" s="6" t="n"/>
+      <c r="O422" s="6" t="n"/>
     </row>
     <row r="423">
       <c r="E423" s="5" t="n"/>
       <c r="J423" s="5" t="n"/>
       <c r="K423" s="6" t="n"/>
       <c r="M423" s="6" t="n"/>
+      <c r="O423" s="6" t="n"/>
     </row>
     <row r="424">
       <c r="E424" s="5" t="n"/>
       <c r="J424" s="5" t="n"/>
       <c r="K424" s="6" t="n"/>
       <c r="M424" s="6" t="n"/>
+      <c r="O424" s="6" t="n"/>
     </row>
     <row r="425">
       <c r="E425" s="5" t="n"/>
       <c r="J425" s="5" t="n"/>
       <c r="K425" s="6" t="n"/>
       <c r="M425" s="6" t="n"/>
+      <c r="O425" s="6" t="n"/>
     </row>
     <row r="426">
       <c r="E426" s="5" t="n"/>
       <c r="J426" s="5" t="n"/>
       <c r="K426" s="6" t="n"/>
       <c r="M426" s="6" t="n"/>
+      <c r="O426" s="6" t="n"/>
     </row>
     <row r="427">
       <c r="E427" s="5" t="n"/>
       <c r="J427" s="5" t="n"/>
       <c r="K427" s="6" t="n"/>
       <c r="M427" s="6" t="n"/>
+      <c r="O427" s="6" t="n"/>
     </row>
     <row r="428">
       <c r="E428" s="5" t="n"/>
       <c r="J428" s="5" t="n"/>
       <c r="K428" s="6" t="n"/>
       <c r="M428" s="6" t="n"/>
+      <c r="O428" s="6" t="n"/>
     </row>
     <row r="429">
       <c r="E429" s="5" t="n"/>
       <c r="J429" s="5" t="n"/>
       <c r="K429" s="6" t="n"/>
       <c r="M429" s="6" t="n"/>
+      <c r="O429" s="6" t="n"/>
     </row>
     <row r="430">
       <c r="E430" s="5" t="n"/>
       <c r="J430" s="5" t="n"/>
       <c r="K430" s="6" t="n"/>
       <c r="M430" s="6" t="n"/>
+      <c r="O430" s="6" t="n"/>
     </row>
     <row r="431">
       <c r="E431" s="5" t="n"/>
       <c r="J431" s="5" t="n"/>
       <c r="K431" s="6" t="n"/>
       <c r="M431" s="6" t="n"/>
+      <c r="O431" s="6" t="n"/>
     </row>
     <row r="432">
       <c r="E432" s="5" t="n"/>
       <c r="J432" s="5" t="n"/>
       <c r="K432" s="6" t="n"/>
       <c r="M432" s="6" t="n"/>
+      <c r="O432" s="6" t="n"/>
     </row>
     <row r="433">
       <c r="E433" s="5" t="n"/>
       <c r="J433" s="5" t="n"/>
       <c r="K433" s="6" t="n"/>
       <c r="M433" s="6" t="n"/>
+      <c r="O433" s="6" t="n"/>
     </row>
     <row r="434">
       <c r="E434" s="5" t="n"/>
       <c r="J434" s="5" t="n"/>
       <c r="K434" s="6" t="n"/>
       <c r="M434" s="6" t="n"/>
+      <c r="O434" s="6" t="n"/>
     </row>
     <row r="435">
       <c r="E435" s="5" t="n"/>
       <c r="J435" s="5" t="n"/>
       <c r="K435" s="6" t="n"/>
       <c r="M435" s="6" t="n"/>
+      <c r="O435" s="6" t="n"/>
     </row>
     <row r="436">
       <c r="E436" s="5" t="n"/>
       <c r="J436" s="5" t="n"/>
       <c r="K436" s="6" t="n"/>
       <c r="M436" s="6" t="n"/>
+      <c r="O436" s="6" t="n"/>
     </row>
     <row r="437">
       <c r="E437" s="5" t="n"/>
       <c r="J437" s="5" t="n"/>
       <c r="K437" s="6" t="n"/>
       <c r="M437" s="6" t="n"/>
+      <c r="O437" s="6" t="n"/>
     </row>
     <row r="438">
       <c r="E438" s="5" t="n"/>
       <c r="J438" s="5" t="n"/>
       <c r="K438" s="6" t="n"/>
       <c r="M438" s="6" t="n"/>
+      <c r="O438" s="6" t="n"/>
     </row>
     <row r="439">
       <c r="E439" s="5" t="n"/>
       <c r="J439" s="5" t="n"/>
       <c r="K439" s="6" t="n"/>
       <c r="M439" s="6" t="n"/>
+      <c r="O439" s="6" t="n"/>
     </row>
     <row r="440">
       <c r="E440" s="5" t="n"/>
       <c r="J440" s="5" t="n"/>
       <c r="K440" s="6" t="n"/>
       <c r="M440" s="6" t="n"/>
+      <c r="O440" s="6" t="n"/>
     </row>
     <row r="441">
       <c r="E441" s="5" t="n"/>
       <c r="J441" s="5" t="n"/>
       <c r="K441" s="6" t="n"/>
       <c r="M441" s="6" t="n"/>
+      <c r="O441" s="6" t="n"/>
     </row>
     <row r="442">
       <c r="E442" s="5" t="n"/>
       <c r="J442" s="5" t="n"/>
       <c r="K442" s="6" t="n"/>
       <c r="M442" s="6" t="n"/>
+      <c r="O442" s="6" t="n"/>
     </row>
     <row r="443">
       <c r="E443" s="5" t="n"/>
       <c r="J443" s="5" t="n"/>
       <c r="K443" s="6" t="n"/>
       <c r="M443" s="6" t="n"/>
+      <c r="O443" s="6" t="n"/>
     </row>
     <row r="444">
       <c r="E444" s="5" t="n"/>
       <c r="J444" s="5" t="n"/>
       <c r="K444" s="6" t="n"/>
       <c r="M444" s="6" t="n"/>
+      <c r="O444" s="6" t="n"/>
     </row>
     <row r="445">
       <c r="E445" s="5" t="n"/>
       <c r="J445" s="5" t="n"/>
       <c r="K445" s="6" t="n"/>
       <c r="M445" s="6" t="n"/>
+      <c r="O445" s="6" t="n"/>
     </row>
     <row r="446">
       <c r="E446" s="5" t="n"/>
       <c r="J446" s="5" t="n"/>
       <c r="K446" s="6" t="n"/>
       <c r="M446" s="6" t="n"/>
+      <c r="O446" s="6" t="n"/>
     </row>
     <row r="447">
       <c r="E447" s="5" t="n"/>
       <c r="J447" s="5" t="n"/>
       <c r="K447" s="6" t="n"/>
       <c r="M447" s="6" t="n"/>
+      <c r="O447" s="6" t="n"/>
     </row>
     <row r="448">
       <c r="E448" s="5" t="n"/>
       <c r="J448" s="5" t="n"/>
       <c r="K448" s="6" t="n"/>
       <c r="M448" s="6" t="n"/>
+      <c r="O448" s="6" t="n"/>
     </row>
     <row r="449">
       <c r="E449" s="5" t="n"/>
       <c r="J449" s="5" t="n"/>
       <c r="K449" s="6" t="n"/>
       <c r="M449" s="6" t="n"/>
+      <c r="O449" s="6" t="n"/>
     </row>
     <row r="450">
       <c r="E450" s="5" t="n"/>
       <c r="J450" s="5" t="n"/>
       <c r="K450" s="6" t="n"/>
       <c r="M450" s="6" t="n"/>
+      <c r="O450" s="6" t="n"/>
     </row>
     <row r="451">
       <c r="E451" s="5" t="n"/>
       <c r="J451" s="5" t="n"/>
       <c r="K451" s="6" t="n"/>
       <c r="M451" s="6" t="n"/>
+      <c r="O451" s="6" t="n"/>
     </row>
     <row r="452">
       <c r="E452" s="5" t="n"/>
       <c r="J452" s="5" t="n"/>
       <c r="K452" s="6" t="n"/>
       <c r="M452" s="6" t="n"/>
+      <c r="O452" s="6" t="n"/>
     </row>
     <row r="453">
       <c r="E453" s="5" t="n"/>
       <c r="J453" s="5" t="n"/>
       <c r="K453" s="6" t="n"/>
       <c r="M453" s="6" t="n"/>
+      <c r="O453" s="6" t="n"/>
     </row>
     <row r="454">
       <c r="E454" s="5" t="n"/>
       <c r="J454" s="5" t="n"/>
       <c r="K454" s="6" t="n"/>
       <c r="M454" s="6" t="n"/>
+      <c r="O454" s="6" t="n"/>
     </row>
     <row r="455">
       <c r="E455" s="5" t="n"/>
       <c r="J455" s="5" t="n"/>
       <c r="K455" s="6" t="n"/>
       <c r="M455" s="6" t="n"/>
+      <c r="O455" s="6" t="n"/>
     </row>
     <row r="456">
       <c r="E456" s="5" t="n"/>
       <c r="J456" s="5" t="n"/>
       <c r="K456" s="6" t="n"/>
       <c r="M456" s="6" t="n"/>
+      <c r="O456" s="6" t="n"/>
     </row>
     <row r="457">
       <c r="E457" s="5" t="n"/>
       <c r="J457" s="5" t="n"/>
       <c r="K457" s="6" t="n"/>
       <c r="M457" s="6" t="n"/>
+      <c r="O457" s="6" t="n"/>
     </row>
     <row r="458">
       <c r="E458" s="5" t="n"/>
       <c r="J458" s="5" t="n"/>
       <c r="K458" s="6" t="n"/>
       <c r="M458" s="6" t="n"/>
+      <c r="O458" s="6" t="n"/>
     </row>
     <row r="459">
       <c r="E459" s="5" t="n"/>
       <c r="J459" s="5" t="n"/>
       <c r="K459" s="6" t="n"/>
       <c r="M459" s="6" t="n"/>
+      <c r="O459" s="6" t="n"/>
     </row>
     <row r="460">
       <c r="E460" s="5" t="n"/>
       <c r="J460" s="5" t="n"/>
       <c r="K460" s="6" t="n"/>
       <c r="M460" s="6" t="n"/>
+      <c r="O460" s="6" t="n"/>
     </row>
     <row r="461">
       <c r="E461" s="5" t="n"/>
       <c r="J461" s="5" t="n"/>
       <c r="K461" s="6" t="n"/>
       <c r="M461" s="6" t="n"/>
+      <c r="O461" s="6" t="n"/>
     </row>
     <row r="462">
       <c r="E462" s="5" t="n"/>
       <c r="J462" s="5" t="n"/>
       <c r="K462" s="6" t="n"/>
       <c r="M462" s="6" t="n"/>
+      <c r="O462" s="6" t="n"/>
     </row>
     <row r="463">
       <c r="E463" s="5" t="n"/>
       <c r="J463" s="5" t="n"/>
       <c r="K463" s="6" t="n"/>
       <c r="M463" s="6" t="n"/>
+      <c r="O463" s="6" t="n"/>
     </row>
     <row r="464">
       <c r="E464" s="5" t="n"/>
       <c r="J464" s="5" t="n"/>
       <c r="K464" s="6" t="n"/>
       <c r="M464" s="6" t="n"/>
+      <c r="O464" s="6" t="n"/>
     </row>
     <row r="465">
       <c r="E465" s="5" t="n"/>
       <c r="J465" s="5" t="n"/>
       <c r="K465" s="6" t="n"/>
       <c r="M465" s="6" t="n"/>
+      <c r="O465" s="6" t="n"/>
     </row>
     <row r="466">
       <c r="E466" s="5" t="n"/>
       <c r="J466" s="5" t="n"/>
       <c r="K466" s="6" t="n"/>
       <c r="M466" s="6" t="n"/>
+      <c r="O466" s="6" t="n"/>
     </row>
     <row r="467">
       <c r="E467" s="5" t="n"/>
       <c r="J467" s="5" t="n"/>
       <c r="K467" s="6" t="n"/>
       <c r="M467" s="6" t="n"/>
+      <c r="O467" s="6" t="n"/>
     </row>
     <row r="468">
       <c r="E468" s="5" t="n"/>
       <c r="J468" s="5" t="n"/>
       <c r="K468" s="6" t="n"/>
       <c r="M468" s="6" t="n"/>
+      <c r="O468" s="6" t="n"/>
     </row>
     <row r="469">
       <c r="E469" s="5" t="n"/>
       <c r="J469" s="5" t="n"/>
       <c r="K469" s="6" t="n"/>
       <c r="M469" s="6" t="n"/>
+      <c r="O469" s="6" t="n"/>
     </row>
     <row r="470">
       <c r="E470" s="5" t="n"/>
       <c r="J470" s="5" t="n"/>
       <c r="K470" s="6" t="n"/>
       <c r="M470" s="6" t="n"/>
+      <c r="O470" s="6" t="n"/>
     </row>
     <row r="471">
       <c r="E471" s="5" t="n"/>
       <c r="J471" s="5" t="n"/>
       <c r="K471" s="6" t="n"/>
       <c r="M471" s="6" t="n"/>
+      <c r="O471" s="6" t="n"/>
     </row>
     <row r="472">
       <c r="E472" s="5" t="n"/>
       <c r="J472" s="5" t="n"/>
       <c r="K472" s="6" t="n"/>
       <c r="M472" s="6" t="n"/>
+      <c r="O472" s="6" t="n"/>
     </row>
     <row r="473">
       <c r="E473" s="5" t="n"/>
       <c r="J473" s="5" t="n"/>
       <c r="K473" s="6" t="n"/>
       <c r="M473" s="6" t="n"/>
+      <c r="O473" s="6" t="n"/>
     </row>
     <row r="474">
       <c r="E474" s="5" t="n"/>
       <c r="J474" s="5" t="n"/>
       <c r="K474" s="6" t="n"/>
       <c r="M474" s="6" t="n"/>
+      <c r="O474" s="6" t="n"/>
     </row>
     <row r="475">
       <c r="E475" s="5" t="n"/>
       <c r="J475" s="5" t="n"/>
       <c r="K475" s="6" t="n"/>
       <c r="M475" s="6" t="n"/>
+      <c r="O475" s="6" t="n"/>
     </row>
     <row r="476">
       <c r="E476" s="5" t="n"/>
       <c r="J476" s="5" t="n"/>
       <c r="K476" s="6" t="n"/>
       <c r="M476" s="6" t="n"/>
+      <c r="O476" s="6" t="n"/>
     </row>
     <row r="477">
       <c r="E477" s="5" t="n"/>
       <c r="J477" s="5" t="n"/>
       <c r="K477" s="6" t="n"/>
       <c r="M477" s="6" t="n"/>
+      <c r="O477" s="6" t="n"/>
     </row>
     <row r="478">
       <c r="E478" s="5" t="n"/>
       <c r="J478" s="5" t="n"/>
       <c r="K478" s="6" t="n"/>
       <c r="M478" s="6" t="n"/>
+      <c r="O478" s="6" t="n"/>
     </row>
     <row r="479">
       <c r="E479" s="5" t="n"/>
       <c r="J479" s="5" t="n"/>
       <c r="K479" s="6" t="n"/>
       <c r="M479" s="6" t="n"/>
+      <c r="O479" s="6" t="n"/>
     </row>
     <row r="480">
       <c r="E480" s="5" t="n"/>
       <c r="J480" s="5" t="n"/>
       <c r="K480" s="6" t="n"/>
       <c r="M480" s="6" t="n"/>
+      <c r="O480" s="6" t="n"/>
     </row>
     <row r="481">
       <c r="E481" s="5" t="n"/>
       <c r="J481" s="5" t="n"/>
       <c r="K481" s="6" t="n"/>
       <c r="M481" s="6" t="n"/>
+      <c r="O481" s="6" t="n"/>
     </row>
     <row r="482">
       <c r="E482" s="5" t="n"/>
       <c r="J482" s="5" t="n"/>
       <c r="K482" s="6" t="n"/>
       <c r="M482" s="6" t="n"/>
+      <c r="O482" s="6" t="n"/>
     </row>
     <row r="483">
       <c r="E483" s="5" t="n"/>
       <c r="J483" s="5" t="n"/>
       <c r="K483" s="6" t="n"/>
       <c r="M483" s="6" t="n"/>
+      <c r="O483" s="6" t="n"/>
     </row>
     <row r="484">
       <c r="E484" s="5" t="n"/>
       <c r="J484" s="5" t="n"/>
       <c r="K484" s="6" t="n"/>
       <c r="M484" s="6" t="n"/>
+      <c r="O484" s="6" t="n"/>
     </row>
     <row r="485">
       <c r="E485" s="5" t="n"/>
       <c r="J485" s="5" t="n"/>
       <c r="K485" s="6" t="n"/>
       <c r="M485" s="6" t="n"/>
+      <c r="O485" s="6" t="n"/>
     </row>
     <row r="486">
       <c r="E486" s="5" t="n"/>
       <c r="J486" s="5" t="n"/>
       <c r="K486" s="6" t="n"/>
       <c r="M486" s="6" t="n"/>
+      <c r="O486" s="6" t="n"/>
     </row>
     <row r="487">
       <c r="E487" s="5" t="n"/>
       <c r="J487" s="5" t="n"/>
       <c r="K487" s="6" t="n"/>
       <c r="M487" s="6" t="n"/>
+      <c r="O487" s="6" t="n"/>
     </row>
     <row r="488">
       <c r="E488" s="5" t="n"/>
       <c r="J488" s="5" t="n"/>
       <c r="K488" s="6" t="n"/>
       <c r="M488" s="6" t="n"/>
+      <c r="O488" s="6" t="n"/>
     </row>
     <row r="489">
       <c r="E489" s="5" t="n"/>
       <c r="J489" s="5" t="n"/>
       <c r="K489" s="6" t="n"/>
       <c r="M489" s="6" t="n"/>
+      <c r="O489" s="6" t="n"/>
     </row>
     <row r="490">
       <c r="E490" s="5" t="n"/>
       <c r="J490" s="5" t="n"/>
       <c r="K490" s="6" t="n"/>
       <c r="M490" s="6" t="n"/>
+      <c r="O490" s="6" t="n"/>
     </row>
     <row r="491">
       <c r="E491" s="5" t="n"/>
       <c r="J491" s="5" t="n"/>
       <c r="K491" s="6" t="n"/>
       <c r="M491" s="6" t="n"/>
+      <c r="O491" s="6" t="n"/>
     </row>
     <row r="492">
       <c r="E492" s="5" t="n"/>
       <c r="J492" s="5" t="n"/>
       <c r="K492" s="6" t="n"/>
       <c r="M492" s="6" t="n"/>
+      <c r="O492" s="6" t="n"/>
     </row>
     <row r="493">
       <c r="E493" s="5" t="n"/>
       <c r="J493" s="5" t="n"/>
       <c r="K493" s="6" t="n"/>
       <c r="M493" s="6" t="n"/>
+      <c r="O493" s="6" t="n"/>
     </row>
     <row r="494">
       <c r="E494" s="5" t="n"/>
       <c r="J494" s="5" t="n"/>
       <c r="K494" s="6" t="n"/>
       <c r="M494" s="6" t="n"/>
+      <c r="O494" s="6" t="n"/>
     </row>
     <row r="495">
       <c r="E495" s="5" t="n"/>
       <c r="J495" s="5" t="n"/>
       <c r="K495" s="6" t="n"/>
       <c r="M495" s="6" t="n"/>
+      <c r="O495" s="6" t="n"/>
     </row>
     <row r="496">
       <c r="E496" s="5" t="n"/>
       <c r="J496" s="5" t="n"/>
       <c r="K496" s="6" t="n"/>
       <c r="M496" s="6" t="n"/>
+      <c r="O496" s="6" t="n"/>
     </row>
     <row r="497">
       <c r="E497" s="5" t="n"/>
       <c r="J497" s="5" t="n"/>
       <c r="K497" s="6" t="n"/>
       <c r="M497" s="6" t="n"/>
+      <c r="O497" s="6" t="n"/>
     </row>
     <row r="498">
       <c r="E498" s="5" t="n"/>
       <c r="J498" s="5" t="n"/>
       <c r="K498" s="6" t="n"/>
       <c r="M498" s="6" t="n"/>
+      <c r="O498" s="6" t="n"/>
     </row>
     <row r="499">
       <c r="E499" s="5" t="n"/>
       <c r="J499" s="5" t="n"/>
       <c r="K499" s="6" t="n"/>
       <c r="M499" s="6" t="n"/>
+      <c r="O499" s="6" t="n"/>
     </row>
     <row r="500">
       <c r="E500" s="5" t="n"/>
       <c r="J500" s="5" t="n"/>
       <c r="K500" s="6" t="n"/>
       <c r="M500" s="6" t="n"/>
+      <c r="O500" s="6" t="n"/>
     </row>
     <row r="501">
       <c r="E501" s="5" t="n"/>
       <c r="J501" s="5" t="n"/>
       <c r="K501" s="6" t="n"/>
       <c r="M501" s="6" t="n"/>
+      <c r="O501" s="6" t="n"/>
     </row>
     <row r="502">
       <c r="E502" s="5" t="n"/>
       <c r="J502" s="5" t="n"/>
       <c r="K502" s="6" t="n"/>
       <c r="M502" s="6" t="n"/>
+      <c r="O502" s="6" t="n"/>
     </row>
     <row r="503">
       <c r="E503" s="5" t="n"/>
       <c r="J503" s="5" t="n"/>
       <c r="K503" s="6" t="n"/>
       <c r="M503" s="6" t="n"/>
+      <c r="O503" s="6" t="n"/>
     </row>
     <row r="504">
       <c r="E504" s="5" t="n"/>
       <c r="J504" s="5" t="n"/>
       <c r="K504" s="6" t="n"/>
       <c r="M504" s="6" t="n"/>
+      <c r="O504" s="6" t="n"/>
     </row>
     <row r="505">
       <c r="E505" s="5" t="n"/>
       <c r="J505" s="5" t="n"/>
       <c r="K505" s="6" t="n"/>
       <c r="M505" s="6" t="n"/>
+      <c r="O505" s="6" t="n"/>
     </row>
     <row r="506">
       <c r="E506" s="5" t="n"/>
       <c r="J506" s="5" t="n"/>
       <c r="K506" s="6" t="n"/>
       <c r="M506" s="6" t="n"/>
+      <c r="O506" s="6" t="n"/>
     </row>
     <row r="507">
       <c r="E507" s="5" t="n"/>
       <c r="J507" s="5" t="n"/>
       <c r="K507" s="6" t="n"/>
       <c r="M507" s="6" t="n"/>
+      <c r="O507" s="6" t="n"/>
     </row>
     <row r="508">
       <c r="E508" s="5" t="n"/>
       <c r="J508" s="5" t="n"/>
       <c r="K508" s="6" t="n"/>
       <c r="M508" s="6" t="n"/>
+      <c r="O508" s="6" t="n"/>
     </row>
     <row r="509">
       <c r="E509" s="5" t="n"/>
       <c r="J509" s="5" t="n"/>
       <c r="K509" s="6" t="n"/>
       <c r="M509" s="6" t="n"/>
+      <c r="O509" s="6" t="n"/>
     </row>
     <row r="510">
       <c r="E510" s="5" t="n"/>
       <c r="J510" s="5" t="n"/>
       <c r="K510" s="6" t="n"/>
       <c r="M510" s="6" t="n"/>
+      <c r="O510" s="6" t="n"/>
     </row>
     <row r="511">
       <c r="E511" s="5" t="n"/>
       <c r="J511" s="5" t="n"/>
       <c r="K511" s="6" t="n"/>
       <c r="M511" s="6" t="n"/>
+      <c r="O511" s="6" t="n"/>
     </row>
     <row r="512">
       <c r="E512" s="5" t="n"/>
       <c r="J512" s="5" t="n"/>
       <c r="K512" s="6" t="n"/>
       <c r="M512" s="6" t="n"/>
+      <c r="O512" s="6" t="n"/>
     </row>
     <row r="513">
       <c r="E513" s="5" t="n"/>
       <c r="J513" s="5" t="n"/>
       <c r="K513" s="6" t="n"/>
       <c r="M513" s="6" t="n"/>
+      <c r="O513" s="6" t="n"/>
     </row>
     <row r="514">
       <c r="E514" s="5" t="n"/>
       <c r="J514" s="5" t="n"/>
       <c r="K514" s="6" t="n"/>
       <c r="M514" s="6" t="n"/>
+      <c r="O514" s="6" t="n"/>
     </row>
     <row r="515">
       <c r="E515" s="5" t="n"/>
       <c r="J515" s="5" t="n"/>
       <c r="K515" s="6" t="n"/>
       <c r="M515" s="6" t="n"/>
+      <c r="O515" s="6" t="n"/>
     </row>
     <row r="516">
       <c r="E516" s="5" t="n"/>
       <c r="J516" s="5" t="n"/>
       <c r="K516" s="6" t="n"/>
       <c r="M516" s="6" t="n"/>
+      <c r="O516" s="6" t="n"/>
     </row>
     <row r="517">
       <c r="E517" s="5" t="n"/>
       <c r="J517" s="5" t="n"/>
       <c r="K517" s="6" t="n"/>
       <c r="M517" s="6" t="n"/>
+      <c r="O517" s="6" t="n"/>
     </row>
     <row r="518">
       <c r="E518" s="5" t="n"/>
       <c r="J518" s="5" t="n"/>
       <c r="K518" s="6" t="n"/>
       <c r="M518" s="6" t="n"/>
+      <c r="O518" s="6" t="n"/>
     </row>
     <row r="519">
       <c r="E519" s="5" t="n"/>
       <c r="J519" s="5" t="n"/>
       <c r="K519" s="6" t="n"/>
       <c r="M519" s="6" t="n"/>
+      <c r="O519" s="6" t="n"/>
     </row>
     <row r="520">
       <c r="E520" s="5" t="n"/>
       <c r="J520" s="5" t="n"/>
       <c r="K520" s="6" t="n"/>
       <c r="M520" s="6" t="n"/>
+      <c r="O520" s="6" t="n"/>
     </row>
     <row r="521">
       <c r="E521" s="5" t="n"/>
       <c r="J521" s="5" t="n"/>
       <c r="K521" s="6" t="n"/>
       <c r="M521" s="6" t="n"/>
+      <c r="O521" s="6" t="n"/>
     </row>
     <row r="522">
       <c r="E522" s="5" t="n"/>
       <c r="J522" s="5" t="n"/>
       <c r="K522" s="6" t="n"/>
       <c r="M522" s="6" t="n"/>
+      <c r="O522" s="6" t="n"/>
     </row>
     <row r="523">
       <c r="E523" s="5" t="n"/>
       <c r="J523" s="5" t="n"/>
       <c r="K523" s="6" t="n"/>
       <c r="M523" s="6" t="n"/>
+      <c r="O523" s="6" t="n"/>
     </row>
     <row r="524">
       <c r="E524" s="5" t="n"/>
       <c r="J524" s="5" t="n"/>
       <c r="K524" s="6" t="n"/>
       <c r="M524" s="6" t="n"/>
+      <c r="O524" s="6" t="n"/>
     </row>
     <row r="525">
       <c r="E525" s="5" t="n"/>
       <c r="J525" s="5" t="n"/>
       <c r="K525" s="6" t="n"/>
       <c r="M525" s="6" t="n"/>
+      <c r="O525" s="6" t="n"/>
     </row>
     <row r="526">
       <c r="E526" s="5" t="n"/>
       <c r="J526" s="5" t="n"/>
       <c r="K526" s="6" t="n"/>
       <c r="M526" s="6" t="n"/>
+      <c r="O526" s="6" t="n"/>
     </row>
     <row r="527">
       <c r="E527" s="5" t="n"/>
       <c r="J527" s="5" t="n"/>
       <c r="K527" s="6" t="n"/>
       <c r="M527" s="6" t="n"/>
+      <c r="O527" s="6" t="n"/>
     </row>
     <row r="528">
       <c r="E528" s="5" t="n"/>
       <c r="J528" s="5" t="n"/>
       <c r="K528" s="6" t="n"/>
       <c r="M528" s="6" t="n"/>
+      <c r="O528" s="6" t="n"/>
     </row>
     <row r="529">
       <c r="E529" s="5" t="n"/>
       <c r="J529" s="5" t="n"/>
       <c r="K529" s="6" t="n"/>
       <c r="M529" s="6" t="n"/>
+      <c r="O529" s="6" t="n"/>
     </row>
     <row r="530">
       <c r="E530" s="5" t="n"/>
       <c r="J530" s="5" t="n"/>
       <c r="K530" s="6" t="n"/>
       <c r="M530" s="6" t="n"/>
+      <c r="O530" s="6" t="n"/>
     </row>
     <row r="531">
       <c r="E531" s="5" t="n"/>
       <c r="J531" s="5" t="n"/>
       <c r="K531" s="6" t="n"/>
       <c r="M531" s="6" t="n"/>
+      <c r="O531" s="6" t="n"/>
     </row>
     <row r="532">
       <c r="E532" s="5" t="n"/>
       <c r="J532" s="5" t="n"/>
       <c r="K532" s="6" t="n"/>
       <c r="M532" s="6" t="n"/>
+      <c r="O532" s="6" t="n"/>
     </row>
     <row r="533">
       <c r="E533" s="5" t="n"/>
       <c r="J533" s="5" t="n"/>
       <c r="K533" s="6" t="n"/>
       <c r="M533" s="6" t="n"/>
+      <c r="O533" s="6" t="n"/>
     </row>
     <row r="534">
       <c r="E534" s="5" t="n"/>
       <c r="J534" s="5" t="n"/>
       <c r="K534" s="6" t="n"/>
       <c r="M534" s="6" t="n"/>
+      <c r="O534" s="6" t="n"/>
     </row>
     <row r="535">
       <c r="E535" s="5" t="n"/>
       <c r="J535" s="5" t="n"/>
       <c r="K535" s="6" t="n"/>
       <c r="M535" s="6" t="n"/>
+      <c r="O535" s="6" t="n"/>
     </row>
     <row r="536">
       <c r="E536" s="5" t="n"/>
       <c r="J536" s="5" t="n"/>
       <c r="K536" s="6" t="n"/>
       <c r="M536" s="6" t="n"/>
+      <c r="O536" s="6" t="n"/>
     </row>
     <row r="537">
       <c r="E537" s="5" t="n"/>
       <c r="J537" s="5" t="n"/>
       <c r="K537" s="6" t="n"/>
       <c r="M537" s="6" t="n"/>
+      <c r="O537" s="6" t="n"/>
     </row>
     <row r="538">
       <c r="E538" s="5" t="n"/>
       <c r="J538" s="5" t="n"/>
       <c r="K538" s="6" t="n"/>
       <c r="M538" s="6" t="n"/>
+      <c r="O538" s="6" t="n"/>
     </row>
     <row r="539">
       <c r="E539" s="5" t="n"/>
       <c r="J539" s="5" t="n"/>
       <c r="K539" s="6" t="n"/>
       <c r="M539" s="6" t="n"/>
+      <c r="O539" s="6" t="n"/>
     </row>
     <row r="540">
       <c r="E540" s="5" t="n"/>
       <c r="J540" s="5" t="n"/>
       <c r="K540" s="6" t="n"/>
       <c r="M540" s="6" t="n"/>
+      <c r="O540" s="6" t="n"/>
     </row>
     <row r="541">
       <c r="E541" s="5" t="n"/>
       <c r="J541" s="5" t="n"/>
       <c r="K541" s="6" t="n"/>
       <c r="M541" s="6" t="n"/>
+      <c r="O541" s="6" t="n"/>
     </row>
     <row r="542">
       <c r="E542" s="5" t="n"/>
       <c r="J542" s="5" t="n"/>
       <c r="K542" s="6" t="n"/>
       <c r="M542" s="6" t="n"/>
+      <c r="O542" s="6" t="n"/>
     </row>
     <row r="543">
       <c r="E543" s="5" t="n"/>
       <c r="J543" s="5" t="n"/>
       <c r="K543" s="6" t="n"/>
       <c r="M543" s="6" t="n"/>
+      <c r="O543" s="6" t="n"/>
     </row>
     <row r="544">
       <c r="E544" s="5" t="n"/>
       <c r="J544" s="5" t="n"/>
       <c r="K544" s="6" t="n"/>
       <c r="M544" s="6" t="n"/>
+      <c r="O544" s="6" t="n"/>
     </row>
     <row r="545">
       <c r="E545" s="5" t="n"/>
       <c r="J545" s="5" t="n"/>
       <c r="K545" s="6" t="n"/>
       <c r="M545" s="6" t="n"/>
+      <c r="O545" s="6" t="n"/>
     </row>
     <row r="546">
       <c r="E546" s="5" t="n"/>
       <c r="J546" s="5" t="n"/>
       <c r="K546" s="6" t="n"/>
       <c r="M546" s="6" t="n"/>
+      <c r="O546" s="6" t="n"/>
     </row>
     <row r="547">
       <c r="E547" s="5" t="n"/>
       <c r="J547" s="5" t="n"/>
       <c r="K547" s="6" t="n"/>
       <c r="M547" s="6" t="n"/>
+      <c r="O547" s="6" t="n"/>
     </row>
     <row r="548">
       <c r="E548" s="5" t="n"/>
       <c r="J548" s="5" t="n"/>
       <c r="K548" s="6" t="n"/>
       <c r="M548" s="6" t="n"/>
+      <c r="O548" s="6" t="n"/>
     </row>
     <row r="549">
       <c r="E549" s="5" t="n"/>
       <c r="J549" s="5" t="n"/>
       <c r="K549" s="6" t="n"/>
       <c r="M549" s="6" t="n"/>
+      <c r="O549" s="6" t="n"/>
     </row>
     <row r="550">
       <c r="E550" s="5" t="n"/>
       <c r="J550" s="5" t="n"/>
       <c r="K550" s="6" t="n"/>
       <c r="M550" s="6" t="n"/>
+      <c r="O550" s="6" t="n"/>
     </row>
     <row r="551">
       <c r="E551" s="5" t="n"/>
       <c r="J551" s="5" t="n"/>
       <c r="K551" s="6" t="n"/>
       <c r="M551" s="6" t="n"/>
+      <c r="O551" s="6" t="n"/>
     </row>
     <row r="552">
       <c r="E552" s="5" t="n"/>
       <c r="J552" s="5" t="n"/>
       <c r="K552" s="6" t="n"/>
       <c r="M552" s="6" t="n"/>
+      <c r="O552" s="6" t="n"/>
     </row>
     <row r="553">
       <c r="E553" s="5" t="n"/>
       <c r="J553" s="5" t="n"/>
       <c r="K553" s="6" t="n"/>
       <c r="M553" s="6" t="n"/>
+      <c r="O553" s="6" t="n"/>
     </row>
     <row r="554">
       <c r="E554" s="5" t="n"/>
       <c r="J554" s="5" t="n"/>
       <c r="K554" s="6" t="n"/>
       <c r="M554" s="6" t="n"/>
+      <c r="O554" s="6" t="n"/>
     </row>
     <row r="555">
       <c r="E555" s="5" t="n"/>
       <c r="J555" s="5" t="n"/>
       <c r="K555" s="6" t="n"/>
       <c r="M555" s="6" t="n"/>
+      <c r="O555" s="6" t="n"/>
     </row>
     <row r="556">
       <c r="E556" s="5" t="n"/>
       <c r="J556" s="5" t="n"/>
       <c r="K556" s="6" t="n"/>
       <c r="M556" s="6" t="n"/>
+      <c r="O556" s="6" t="n"/>
     </row>
     <row r="557">
       <c r="E557" s="5" t="n"/>
       <c r="J557" s="5" t="n"/>
       <c r="K557" s="6" t="n"/>
       <c r="M557" s="6" t="n"/>
+      <c r="O557" s="6" t="n"/>
     </row>
     <row r="558">
       <c r="E558" s="5" t="n"/>
       <c r="J558" s="5" t="n"/>
       <c r="K558" s="6" t="n"/>
       <c r="M558" s="6" t="n"/>
+      <c r="O558" s="6" t="n"/>
     </row>
     <row r="559">
       <c r="E559" s="5" t="n"/>
       <c r="J559" s="5" t="n"/>
       <c r="K559" s="6" t="n"/>
       <c r="M559" s="6" t="n"/>
+      <c r="O559" s="6" t="n"/>
     </row>
     <row r="560">
       <c r="E560" s="5" t="n"/>
       <c r="J560" s="5" t="n"/>
       <c r="K560" s="6" t="n"/>
       <c r="M560" s="6" t="n"/>
+      <c r="O560" s="6" t="n"/>
     </row>
     <row r="561">
       <c r="E561" s="5" t="n"/>
       <c r="J561" s="5" t="n"/>
       <c r="K561" s="6" t="n"/>
       <c r="M561" s="6" t="n"/>
+      <c r="O561" s="6" t="n"/>
     </row>
     <row r="562">
       <c r="E562" s="5" t="n"/>
       <c r="J562" s="5" t="n"/>
       <c r="K562" s="6" t="n"/>
       <c r="M562" s="6" t="n"/>
+      <c r="O562" s="6" t="n"/>
     </row>
     <row r="563">
       <c r="E563" s="5" t="n"/>
       <c r="J563" s="5" t="n"/>
       <c r="K563" s="6" t="n"/>
       <c r="M563" s="6" t="n"/>
+      <c r="O563" s="6" t="n"/>
     </row>
     <row r="564">
       <c r="E564" s="5" t="n"/>
       <c r="J564" s="5" t="n"/>
       <c r="K564" s="6" t="n"/>
       <c r="M564" s="6" t="n"/>
+      <c r="O564" s="6" t="n"/>
     </row>
     <row r="565">
       <c r="E565" s="5" t="n"/>
       <c r="J565" s="5" t="n"/>
       <c r="K565" s="6" t="n"/>
       <c r="M565" s="6" t="n"/>
+      <c r="O565" s="6" t="n"/>
     </row>
     <row r="566">
       <c r="E566" s="5" t="n"/>
       <c r="J566" s="5" t="n"/>
       <c r="K566" s="6" t="n"/>
       <c r="M566" s="6" t="n"/>
+      <c r="O566" s="6" t="n"/>
     </row>
     <row r="567">
       <c r="E567" s="5" t="n"/>
       <c r="J567" s="5" t="n"/>
       <c r="K567" s="6" t="n"/>
       <c r="M567" s="6" t="n"/>
+      <c r="O567" s="6" t="n"/>
     </row>
     <row r="568">
       <c r="E568" s="5" t="n"/>
       <c r="J568" s="5" t="n"/>
       <c r="K568" s="6" t="n"/>
       <c r="M568" s="6" t="n"/>
+      <c r="O568" s="6" t="n"/>
     </row>
     <row r="569">
       <c r="E569" s="5" t="n"/>
       <c r="J569" s="5" t="n"/>
       <c r="K569" s="6" t="n"/>
       <c r="M569" s="6" t="n"/>
+      <c r="O569" s="6" t="n"/>
     </row>
     <row r="570">
       <c r="E570" s="5" t="n"/>
       <c r="J570" s="5" t="n"/>
       <c r="K570" s="6" t="n"/>
       <c r="M570" s="6" t="n"/>
+      <c r="O570" s="6" t="n"/>
     </row>
     <row r="571">
       <c r="E571" s="5" t="n"/>
       <c r="J571" s="5" t="n"/>
       <c r="K571" s="6" t="n"/>
       <c r="M571" s="6" t="n"/>
+      <c r="O571" s="6" t="n"/>
     </row>
     <row r="572">
       <c r="E572" s="5" t="n"/>
       <c r="J572" s="5" t="n"/>
       <c r="K572" s="6" t="n"/>
       <c r="M572" s="6" t="n"/>
+      <c r="O572" s="6" t="n"/>
     </row>
     <row r="573">
       <c r="E573" s="5" t="n"/>
       <c r="J573" s="5" t="n"/>
       <c r="K573" s="6" t="n"/>
       <c r="M573" s="6" t="n"/>
+      <c r="O573" s="6" t="n"/>
     </row>
     <row r="574">
       <c r="E574" s="5" t="n"/>
       <c r="J574" s="5" t="n"/>
       <c r="K574" s="6" t="n"/>
       <c r="M574" s="6" t="n"/>
+      <c r="O574" s="6" t="n"/>
     </row>
     <row r="575">
       <c r="E575" s="5" t="n"/>
       <c r="J575" s="5" t="n"/>
       <c r="K575" s="6" t="n"/>
       <c r="M575" s="6" t="n"/>
+      <c r="O575" s="6" t="n"/>
     </row>
     <row r="576">
       <c r="E576" s="5" t="n"/>
       <c r="J576" s="5" t="n"/>
       <c r="K576" s="6" t="n"/>
       <c r="M576" s="6" t="n"/>
+      <c r="O576" s="6" t="n"/>
     </row>
     <row r="577">
       <c r="E577" s="5" t="n"/>
       <c r="J577" s="5" t="n"/>
       <c r="K577" s="6" t="n"/>
       <c r="M577" s="6" t="n"/>
+      <c r="O577" s="6" t="n"/>
     </row>
     <row r="578">
       <c r="E578" s="5" t="n"/>
       <c r="J578" s="5" t="n"/>
       <c r="K578" s="6" t="n"/>
       <c r="M578" s="6" t="n"/>
+      <c r="O578" s="6" t="n"/>
     </row>
     <row r="579">
       <c r="E579" s="5" t="n"/>
       <c r="J579" s="5" t="n"/>
       <c r="K579" s="6" t="n"/>
       <c r="M579" s="6" t="n"/>
+      <c r="O579" s="6" t="n"/>
     </row>
     <row r="580">
       <c r="E580" s="5" t="n"/>
       <c r="J580" s="5" t="n"/>
       <c r="K580" s="6" t="n"/>
       <c r="M580" s="6" t="n"/>
+      <c r="O580" s="6" t="n"/>
     </row>
     <row r="581">
       <c r="E581" s="5" t="n"/>
       <c r="J581" s="5" t="n"/>
       <c r="K581" s="6" t="n"/>
       <c r="M581" s="6" t="n"/>
+      <c r="O581" s="6" t="n"/>
     </row>
     <row r="582">
       <c r="E582" s="5" t="n"/>
       <c r="J582" s="5" t="n"/>
       <c r="K582" s="6" t="n"/>
       <c r="M582" s="6" t="n"/>
+      <c r="O582" s="6" t="n"/>
     </row>
     <row r="583">
       <c r="E583" s="5" t="n"/>
       <c r="J583" s="5" t="n"/>
       <c r="K583" s="6" t="n"/>
       <c r="M583" s="6" t="n"/>
+      <c r="O583" s="6" t="n"/>
     </row>
     <row r="584">
       <c r="E584" s="5" t="n"/>
       <c r="J584" s="5" t="n"/>
       <c r="K584" s="6" t="n"/>
       <c r="M584" s="6" t="n"/>
+      <c r="O584" s="6" t="n"/>
     </row>
     <row r="585">
       <c r="E585" s="5" t="n"/>
       <c r="J585" s="5" t="n"/>
       <c r="K585" s="6" t="n"/>
       <c r="M585" s="6" t="n"/>
+      <c r="O585" s="6" t="n"/>
     </row>
     <row r="586">
       <c r="E586" s="5" t="n"/>
       <c r="J586" s="5" t="n"/>
       <c r="K586" s="6" t="n"/>
       <c r="M586" s="6" t="n"/>
+      <c r="O586" s="6" t="n"/>
     </row>
     <row r="587">
       <c r="E587" s="5" t="n"/>
       <c r="J587" s="5" t="n"/>
       <c r="K587" s="6" t="n"/>
       <c r="M587" s="6" t="n"/>
+      <c r="O587" s="6" t="n"/>
     </row>
     <row r="588">
       <c r="E588" s="5" t="n"/>
       <c r="J588" s="5" t="n"/>
       <c r="K588" s="6" t="n"/>
       <c r="M588" s="6" t="n"/>
+      <c r="O588" s="6" t="n"/>
     </row>
     <row r="589">
       <c r="E589" s="5" t="n"/>
       <c r="J589" s="5" t="n"/>
       <c r="K589" s="6" t="n"/>
       <c r="M589" s="6" t="n"/>
+      <c r="O589" s="6" t="n"/>
     </row>
     <row r="590">
       <c r="E590" s="5" t="n"/>
       <c r="J590" s="5" t="n"/>
       <c r="K590" s="6" t="n"/>
       <c r="M590" s="6" t="n"/>
+      <c r="O590" s="6" t="n"/>
     </row>
     <row r="591">
       <c r="E591" s="5" t="n"/>
       <c r="J591" s="5" t="n"/>
       <c r="K591" s="6" t="n"/>
       <c r="M591" s="6" t="n"/>
+      <c r="O591" s="6" t="n"/>
     </row>
     <row r="592">
       <c r="E592" s="5" t="n"/>
       <c r="J592" s="5" t="n"/>
       <c r="K592" s="6" t="n"/>
       <c r="M592" s="6" t="n"/>
+      <c r="O592" s="6" t="n"/>
     </row>
     <row r="593">
       <c r="E593" s="5" t="n"/>
       <c r="J593" s="5" t="n"/>
       <c r="K593" s="6" t="n"/>
       <c r="M593" s="6" t="n"/>
+      <c r="O593" s="6" t="n"/>
     </row>
     <row r="594">
       <c r="E594" s="5" t="n"/>
       <c r="J594" s="5" t="n"/>
       <c r="K594" s="6" t="n"/>
       <c r="M594" s="6" t="n"/>
+      <c r="O594" s="6" t="n"/>
     </row>
     <row r="595">
       <c r="E595" s="5" t="n"/>
       <c r="J595" s="5" t="n"/>
       <c r="K595" s="6" t="n"/>
       <c r="M595" s="6" t="n"/>
+      <c r="O595" s="6" t="n"/>
     </row>
     <row r="596">
       <c r="E596" s="5" t="n"/>
       <c r="J596" s="5" t="n"/>
       <c r="K596" s="6" t="n"/>
       <c r="M596" s="6" t="n"/>
+      <c r="O596" s="6" t="n"/>
     </row>
     <row r="597">
       <c r="E597" s="5" t="n"/>
       <c r="J597" s="5" t="n"/>
       <c r="K597" s="6" t="n"/>
       <c r="M597" s="6" t="n"/>
+      <c r="O597" s="6" t="n"/>
     </row>
     <row r="598">
       <c r="E598" s="5" t="n"/>
       <c r="J598" s="5" t="n"/>
       <c r="K598" s="6" t="n"/>
       <c r="M598" s="6" t="n"/>
+      <c r="O598" s="6" t="n"/>
     </row>
     <row r="599">
       <c r="E599" s="5" t="n"/>
       <c r="J599" s="5" t="n"/>
       <c r="K599" s="6" t="n"/>
       <c r="M599" s="6" t="n"/>
+      <c r="O599" s="6" t="n"/>
     </row>
     <row r="600">
       <c r="E600" s="5" t="n"/>
       <c r="J600" s="5" t="n"/>
       <c r="K600" s="6" t="n"/>
       <c r="M600" s="6" t="n"/>
+      <c r="O600" s="6" t="n"/>
     </row>
     <row r="601">
       <c r="E601" s="5" t="n"/>
       <c r="J601" s="5" t="n"/>
       <c r="K601" s="6" t="n"/>
       <c r="M601" s="6" t="n"/>
+      <c r="O601" s="6" t="n"/>
     </row>
     <row r="602">
       <c r="E602" s="5" t="n"/>
       <c r="J602" s="5" t="n"/>
       <c r="K602" s="6" t="n"/>
       <c r="M602" s="6" t="n"/>
+      <c r="O602" s="6" t="n"/>
     </row>
     <row r="603">
       <c r="E603" s="5" t="n"/>
       <c r="J603" s="5" t="n"/>
       <c r="K603" s="6" t="n"/>
       <c r="M603" s="6" t="n"/>
+      <c r="O603" s="6" t="n"/>
     </row>
     <row r="604">
       <c r="E604" s="5" t="n"/>
       <c r="J604" s="5" t="n"/>
       <c r="K604" s="6" t="n"/>
       <c r="M604" s="6" t="n"/>
+      <c r="O604" s="6" t="n"/>
     </row>
     <row r="605">
       <c r="E605" s="5" t="n"/>
       <c r="J605" s="5" t="n"/>
       <c r="K605" s="6" t="n"/>
       <c r="M605" s="6" t="n"/>
+      <c r="O605" s="6" t="n"/>
     </row>
     <row r="606">
       <c r="E606" s="5" t="n"/>
       <c r="J606" s="5" t="n"/>
       <c r="K606" s="6" t="n"/>
       <c r="M606" s="6" t="n"/>
+      <c r="O606" s="6" t="n"/>
     </row>
     <row r="607">
       <c r="E607" s="5" t="n"/>
       <c r="J607" s="5" t="n"/>
       <c r="K607" s="6" t="n"/>
       <c r="M607" s="6" t="n"/>
+      <c r="O607" s="6" t="n"/>
     </row>
     <row r="608">
       <c r="E608" s="5" t="n"/>
       <c r="J608" s="5" t="n"/>
       <c r="K608" s="6" t="n"/>
       <c r="M608" s="6" t="n"/>
+      <c r="O608" s="6" t="n"/>
     </row>
     <row r="609">
       <c r="E609" s="5" t="n"/>
       <c r="J609" s="5" t="n"/>
       <c r="K609" s="6" t="n"/>
       <c r="M609" s="6" t="n"/>
+      <c r="O609" s="6" t="n"/>
     </row>
     <row r="610">
       <c r="E610" s="5" t="n"/>
       <c r="J610" s="5" t="n"/>
       <c r="K610" s="6" t="n"/>
       <c r="M610" s="6" t="n"/>
+      <c r="O610" s="6" t="n"/>
     </row>
     <row r="611">
       <c r="E611" s="5" t="n"/>
       <c r="J611" s="5" t="n"/>
       <c r="K611" s="6" t="n"/>
       <c r="M611" s="6" t="n"/>
+      <c r="O611" s="6" t="n"/>
     </row>
     <row r="612">
       <c r="E612" s="5" t="n"/>
       <c r="J612" s="5" t="n"/>
       <c r="K612" s="6" t="n"/>
       <c r="M612" s="6" t="n"/>
+      <c r="O612" s="6" t="n"/>
     </row>
     <row r="613">
       <c r="E613" s="5" t="n"/>
       <c r="J613" s="5" t="n"/>
       <c r="K613" s="6" t="n"/>
       <c r="M613" s="6" t="n"/>
+      <c r="O613" s="6" t="n"/>
     </row>
     <row r="614">
       <c r="E614" s="5" t="n"/>
       <c r="J614" s="5" t="n"/>
       <c r="K614" s="6" t="n"/>
       <c r="M614" s="6" t="n"/>
+      <c r="O614" s="6" t="n"/>
     </row>
     <row r="615">
       <c r="E615" s="5" t="n"/>
       <c r="J615" s="5" t="n"/>
       <c r="K615" s="6" t="n"/>
       <c r="M615" s="6" t="n"/>
+      <c r="O615" s="6" t="n"/>
     </row>
     <row r="616">
       <c r="E616" s="5" t="n"/>
       <c r="J616" s="5" t="n"/>
       <c r="K616" s="6" t="n"/>
       <c r="M616" s="6" t="n"/>
+      <c r="O616" s="6" t="n"/>
     </row>
     <row r="617">
       <c r="E617" s="5" t="n"/>
       <c r="J617" s="5" t="n"/>
       <c r="K617" s="6" t="n"/>
       <c r="M617" s="6" t="n"/>
+      <c r="O617" s="6" t="n"/>
     </row>
     <row r="618">
       <c r="E618" s="5" t="n"/>
       <c r="J618" s="5" t="n"/>
       <c r="K618" s="6" t="n"/>
       <c r="M618" s="6" t="n"/>
+      <c r="O618" s="6" t="n"/>
     </row>
     <row r="619">
       <c r="E619" s="5" t="n"/>
       <c r="J619" s="5" t="n"/>
       <c r="K619" s="6" t="n"/>
       <c r="M619" s="6" t="n"/>
+      <c r="O619" s="6" t="n"/>
     </row>
     <row r="620">
       <c r="E620" s="5" t="n"/>
       <c r="J620" s="5" t="n"/>
       <c r="K620" s="6" t="n"/>
       <c r="M620" s="6" t="n"/>
+      <c r="O620" s="6" t="n"/>
     </row>
     <row r="621">
       <c r="E621" s="5" t="n"/>
       <c r="J621" s="5" t="n"/>
       <c r="K621" s="6" t="n"/>
       <c r="M621" s="6" t="n"/>
+      <c r="O621" s="6" t="n"/>
     </row>
     <row r="622">
       <c r="E622" s="5" t="n"/>
       <c r="J622" s="5" t="n"/>
       <c r="K622" s="6" t="n"/>
       <c r="M622" s="6" t="n"/>
+      <c r="O622" s="6" t="n"/>
     </row>
     <row r="623">
       <c r="E623" s="5" t="n"/>
       <c r="J623" s="5" t="n"/>
       <c r="K623" s="6" t="n"/>
       <c r="M623" s="6" t="n"/>
+      <c r="O623" s="6" t="n"/>
     </row>
     <row r="624">
       <c r="E624" s="5" t="n"/>
       <c r="J624" s="5" t="n"/>
       <c r="K624" s="6" t="n"/>
       <c r="M624" s="6" t="n"/>
+      <c r="O624" s="6" t="n"/>
     </row>
     <row r="625">
       <c r="E625" s="5" t="n"/>
       <c r="J625" s="5" t="n"/>
       <c r="K625" s="6" t="n"/>
       <c r="M625" s="6" t="n"/>
+      <c r="O625" s="6" t="n"/>
     </row>
     <row r="626">
       <c r="E626" s="5" t="n"/>
       <c r="J626" s="5" t="n"/>
       <c r="K626" s="6" t="n"/>
       <c r="M626" s="6" t="n"/>
+      <c r="O626" s="6" t="n"/>
     </row>
     <row r="627">
       <c r="E627" s="5" t="n"/>
       <c r="J627" s="5" t="n"/>
       <c r="K627" s="6" t="n"/>
       <c r="M627" s="6" t="n"/>
+      <c r="O627" s="6" t="n"/>
     </row>
     <row r="628">
       <c r="E628" s="5" t="n"/>
       <c r="J628" s="5" t="n"/>
       <c r="K628" s="6" t="n"/>
       <c r="M628" s="6" t="n"/>
+      <c r="O628" s="6" t="n"/>
     </row>
     <row r="629">
       <c r="E629" s="5" t="n"/>
       <c r="J629" s="5" t="n"/>
       <c r="K629" s="6" t="n"/>
       <c r="M629" s="6" t="n"/>
+      <c r="O629" s="6" t="n"/>
     </row>
     <row r="630">
       <c r="E630" s="5" t="n"/>
       <c r="J630" s="5" t="n"/>
       <c r="K630" s="6" t="n"/>
       <c r="M630" s="6" t="n"/>
+      <c r="O630" s="6" t="n"/>
     </row>
     <row r="631">
       <c r="E631" s="5" t="n"/>
       <c r="J631" s="5" t="n"/>
       <c r="K631" s="6" t="n"/>
       <c r="M631" s="6" t="n"/>
+      <c r="O631" s="6" t="n"/>
     </row>
     <row r="632">
       <c r="E632" s="5" t="n"/>
       <c r="J632" s="5" t="n"/>
       <c r="K632" s="6" t="n"/>
       <c r="M632" s="6" t="n"/>
+      <c r="O632" s="6" t="n"/>
     </row>
     <row r="633">
       <c r="E633" s="5" t="n"/>
       <c r="J633" s="5" t="n"/>
       <c r="K633" s="6" t="n"/>
       <c r="M633" s="6" t="n"/>
+      <c r="O633" s="6" t="n"/>
     </row>
     <row r="634">
       <c r="E634" s="5" t="n"/>
       <c r="J634" s="5" t="n"/>
       <c r="K634" s="6" t="n"/>
       <c r="M634" s="6" t="n"/>
+      <c r="O634" s="6" t="n"/>
     </row>
     <row r="635">
       <c r="E635" s="5" t="n"/>
       <c r="J635" s="5" t="n"/>
       <c r="K635" s="6" t="n"/>
       <c r="M635" s="6" t="n"/>
+      <c r="O635" s="6" t="n"/>
     </row>
     <row r="636">
       <c r="E636" s="5" t="n"/>
       <c r="J636" s="5" t="n"/>
       <c r="K636" s="6" t="n"/>
       <c r="M636" s="6" t="n"/>
+      <c r="O636" s="6" t="n"/>
     </row>
     <row r="637">
       <c r="E637" s="5" t="n"/>
       <c r="J637" s="5" t="n"/>
       <c r="K637" s="6" t="n"/>
       <c r="M637" s="6" t="n"/>
+      <c r="O637" s="6" t="n"/>
     </row>
     <row r="638">
       <c r="E638" s="5" t="n"/>
       <c r="J638" s="5" t="n"/>
       <c r="K638" s="6" t="n"/>
       <c r="M638" s="6" t="n"/>
+      <c r="O638" s="6" t="n"/>
     </row>
     <row r="639">
       <c r="E639" s="5" t="n"/>
       <c r="J639" s="5" t="n"/>
       <c r="K639" s="6" t="n"/>
       <c r="M639" s="6" t="n"/>
+      <c r="O639" s="6" t="n"/>
     </row>
     <row r="640">
       <c r="E640" s="5" t="n"/>
       <c r="J640" s="5" t="n"/>
       <c r="K640" s="6" t="n"/>
       <c r="M640" s="6" t="n"/>
+      <c r="O640" s="6" t="n"/>
     </row>
     <row r="641">
       <c r="E641" s="5" t="n"/>
       <c r="J641" s="5" t="n"/>
       <c r="K641" s="6" t="n"/>
       <c r="M641" s="6" t="n"/>
+      <c r="O641" s="6" t="n"/>
     </row>
     <row r="642">
       <c r="E642" s="5" t="n"/>
       <c r="J642" s="5" t="n"/>
       <c r="K642" s="6" t="n"/>
       <c r="M642" s="6" t="n"/>
+      <c r="O642" s="6" t="n"/>
     </row>
     <row r="643">
       <c r="E643" s="5" t="n"/>
       <c r="J643" s="5" t="n"/>
       <c r="K643" s="6" t="n"/>
       <c r="M643" s="6" t="n"/>
+      <c r="O643" s="6" t="n"/>
     </row>
     <row r="644">
       <c r="E644" s="5" t="n"/>
       <c r="J644" s="5" t="n"/>
       <c r="K644" s="6" t="n"/>
       <c r="M644" s="6" t="n"/>
+      <c r="O644" s="6" t="n"/>
     </row>
     <row r="645">
       <c r="E645" s="5" t="n"/>
       <c r="J645" s="5" t="n"/>
       <c r="K645" s="6" t="n"/>
       <c r="M645" s="6" t="n"/>
+      <c r="O645" s="6" t="n"/>
     </row>
     <row r="646">
       <c r="E646" s="5" t="n"/>
       <c r="J646" s="5" t="n"/>
       <c r="K646" s="6" t="n"/>
       <c r="M646" s="6" t="n"/>
+      <c r="O646" s="6" t="n"/>
     </row>
     <row r="647">
       <c r="E647" s="5" t="n"/>
       <c r="J647" s="5" t="n"/>
       <c r="K647" s="6" t="n"/>
       <c r="M647" s="6" t="n"/>
+      <c r="O647" s="6" t="n"/>
     </row>
     <row r="648">
       <c r="E648" s="5" t="n"/>
       <c r="J648" s="5" t="n"/>
       <c r="K648" s="6" t="n"/>
       <c r="M648" s="6" t="n"/>
+      <c r="O648" s="6" t="n"/>
     </row>
     <row r="649">
       <c r="E649" s="5" t="n"/>
       <c r="J649" s="5" t="n"/>
       <c r="K649" s="6" t="n"/>
       <c r="M649" s="6" t="n"/>
+      <c r="O649" s="6" t="n"/>
     </row>
     <row r="650">
       <c r="E650" s="5" t="n"/>
       <c r="J650" s="5" t="n"/>
       <c r="K650" s="6" t="n"/>
       <c r="M650" s="6" t="n"/>
+      <c r="O650" s="6" t="n"/>
     </row>
     <row r="651">
       <c r="E651" s="5" t="n"/>
       <c r="J651" s="5" t="n"/>
       <c r="K651" s="6" t="n"/>
       <c r="M651" s="6" t="n"/>
+      <c r="O651" s="6" t="n"/>
     </row>
     <row r="652">
       <c r="E652" s="5" t="n"/>
       <c r="J652" s="5" t="n"/>
       <c r="K652" s="6" t="n"/>
       <c r="M652" s="6" t="n"/>
+      <c r="O652" s="6" t="n"/>
     </row>
     <row r="653">
       <c r="E653" s="5" t="n"/>
       <c r="J653" s="5" t="n"/>
       <c r="K653" s="6" t="n"/>
       <c r="M653" s="6" t="n"/>
+      <c r="O653" s="6" t="n"/>
     </row>
     <row r="654">
       <c r="E654" s="5" t="n"/>
       <c r="J654" s="5" t="n"/>
       <c r="K654" s="6" t="n"/>
       <c r="M654" s="6" t="n"/>
+      <c r="O654" s="6" t="n"/>
     </row>
     <row r="655">
       <c r="E655" s="5" t="n"/>
       <c r="J655" s="5" t="n"/>
       <c r="K655" s="6" t="n"/>
       <c r="M655" s="6" t="n"/>
+      <c r="O655" s="6" t="n"/>
     </row>
     <row r="656">
       <c r="E656" s="5" t="n"/>
       <c r="J656" s="5" t="n"/>
       <c r="K656" s="6" t="n"/>
       <c r="M656" s="6" t="n"/>
+      <c r="O656" s="6" t="n"/>
     </row>
     <row r="657">
       <c r="E657" s="5" t="n"/>
       <c r="J657" s="5" t="n"/>
       <c r="K657" s="6" t="n"/>
       <c r="M657" s="6" t="n"/>
+      <c r="O657" s="6" t="n"/>
     </row>
     <row r="658">
       <c r="E658" s="5" t="n"/>
       <c r="J658" s="5" t="n"/>
       <c r="K658" s="6" t="n"/>
       <c r="M658" s="6" t="n"/>
+      <c r="O658" s="6" t="n"/>
     </row>
     <row r="659">
       <c r="E659" s="5" t="n"/>
       <c r="J659" s="5" t="n"/>
       <c r="K659" s="6" t="n"/>
       <c r="M659" s="6" t="n"/>
+      <c r="O659" s="6" t="n"/>
     </row>
     <row r="660">
       <c r="E660" s="5" t="n"/>
       <c r="J660" s="5" t="n"/>
       <c r="K660" s="6" t="n"/>
       <c r="M660" s="6" t="n"/>
+      <c r="O660" s="6" t="n"/>
     </row>
     <row r="661">
       <c r="E661" s="5" t="n"/>
       <c r="J661" s="5" t="n"/>
       <c r="K661" s="6" t="n"/>
       <c r="M661" s="6" t="n"/>
+      <c r="O661" s="6" t="n"/>
     </row>
     <row r="662">
       <c r="E662" s="5" t="n"/>
       <c r="J662" s="5" t="n"/>
       <c r="K662" s="6" t="n"/>
       <c r="M662" s="6" t="n"/>
+      <c r="O662" s="6" t="n"/>
     </row>
     <row r="663">
       <c r="E663" s="5" t="n"/>
       <c r="J663" s="5" t="n"/>
       <c r="K663" s="6" t="n"/>
       <c r="M663" s="6" t="n"/>
+      <c r="O663" s="6" t="n"/>
     </row>
     <row r="664">
       <c r="E664" s="5" t="n"/>
       <c r="J664" s="5" t="n"/>
       <c r="K664" s="6" t="n"/>
       <c r="M664" s="6" t="n"/>
+      <c r="O664" s="6" t="n"/>
     </row>
     <row r="665">
       <c r="E665" s="5" t="n"/>
       <c r="J665" s="5" t="n"/>
       <c r="K665" s="6" t="n"/>
       <c r="M665" s="6" t="n"/>
+      <c r="O665" s="6" t="n"/>
     </row>
     <row r="666">
       <c r="E666" s="5" t="n"/>
       <c r="J666" s="5" t="n"/>
       <c r="K666" s="6" t="n"/>
       <c r="M666" s="6" t="n"/>
+      <c r="O666" s="6" t="n"/>
     </row>
     <row r="667">
       <c r="E667" s="5" t="n"/>
       <c r="J667" s="5" t="n"/>
       <c r="K667" s="6" t="n"/>
       <c r="M667" s="6" t="n"/>
+      <c r="O667" s="6" t="n"/>
     </row>
     <row r="668">
       <c r="E668" s="5" t="n"/>
       <c r="J668" s="5" t="n"/>
       <c r="K668" s="6" t="n"/>
       <c r="M668" s="6" t="n"/>
+      <c r="O668" s="6" t="n"/>
     </row>
     <row r="669">
       <c r="E669" s="5" t="n"/>
       <c r="J669" s="5" t="n"/>
       <c r="K669" s="6" t="n"/>
       <c r="M669" s="6" t="n"/>
+      <c r="O669" s="6" t="n"/>
     </row>
     <row r="670">
       <c r="E670" s="5" t="n"/>
       <c r="J670" s="5" t="n"/>
       <c r="K670" s="6" t="n"/>
       <c r="M670" s="6" t="n"/>
+      <c r="O670" s="6" t="n"/>
     </row>
     <row r="671">
       <c r="E671" s="5" t="n"/>
       <c r="J671" s="5" t="n"/>
       <c r="K671" s="6" t="n"/>
       <c r="M671" s="6" t="n"/>
+      <c r="O671" s="6" t="n"/>
     </row>
     <row r="672">
       <c r="E672" s="5" t="n"/>
       <c r="J672" s="5" t="n"/>
       <c r="K672" s="6" t="n"/>
       <c r="M672" s="6" t="n"/>
+      <c r="O672" s="6" t="n"/>
     </row>
     <row r="673">
       <c r="E673" s="5" t="n"/>
       <c r="J673" s="5" t="n"/>
       <c r="K673" s="6" t="n"/>
       <c r="M673" s="6" t="n"/>
+      <c r="O673" s="6" t="n"/>
     </row>
     <row r="674">
       <c r="E674" s="5" t="n"/>
       <c r="J674" s="5" t="n"/>
       <c r="K674" s="6" t="n"/>
       <c r="M674" s="6" t="n"/>
+      <c r="O674" s="6" t="n"/>
     </row>
     <row r="675">
       <c r="E675" s="5" t="n"/>
       <c r="J675" s="5" t="n"/>
       <c r="K675" s="6" t="n"/>
       <c r="M675" s="6" t="n"/>
+      <c r="O675" s="6" t="n"/>
     </row>
     <row r="676">
       <c r="E676" s="5" t="n"/>
       <c r="J676" s="5" t="n"/>
       <c r="K676" s="6" t="n"/>
       <c r="M676" s="6" t="n"/>
+      <c r="O676" s="6" t="n"/>
     </row>
     <row r="677">
       <c r="E677" s="5" t="n"/>
       <c r="J677" s="5" t="n"/>
       <c r="K677" s="6" t="n"/>
       <c r="M677" s="6" t="n"/>
+      <c r="O677" s="6" t="n"/>
     </row>
     <row r="678">
       <c r="E678" s="5" t="n"/>
       <c r="J678" s="5" t="n"/>
       <c r="K678" s="6" t="n"/>
       <c r="M678" s="6" t="n"/>
+      <c r="O678" s="6" t="n"/>
     </row>
     <row r="679">
       <c r="E679" s="5" t="n"/>
       <c r="J679" s="5" t="n"/>
       <c r="K679" s="6" t="n"/>
       <c r="M679" s="6" t="n"/>
+      <c r="O679" s="6" t="n"/>
     </row>
     <row r="680">
       <c r="E680" s="5" t="n"/>
       <c r="J680" s="5" t="n"/>
       <c r="K680" s="6" t="n"/>
       <c r="M680" s="6" t="n"/>
+      <c r="O680" s="6" t="n"/>
     </row>
     <row r="681">
       <c r="E681" s="5" t="n"/>
       <c r="J681" s="5" t="n"/>
       <c r="K681" s="6" t="n"/>
       <c r="M681" s="6" t="n"/>
+      <c r="O681" s="6" t="n"/>
     </row>
     <row r="682">
       <c r="E682" s="5" t="n"/>
       <c r="J682" s="5" t="n"/>
       <c r="K682" s="6" t="n"/>
       <c r="M682" s="6" t="n"/>
+      <c r="O682" s="6" t="n"/>
     </row>
     <row r="683">
       <c r="E683" s="5" t="n"/>
       <c r="J683" s="5" t="n"/>
       <c r="K683" s="6" t="n"/>
       <c r="M683" s="6" t="n"/>
+      <c r="O683" s="6" t="n"/>
     </row>
     <row r="684">
       <c r="E684" s="5" t="n"/>
       <c r="J684" s="5" t="n"/>
       <c r="K684" s="6" t="n"/>
       <c r="M684" s="6" t="n"/>
+      <c r="O684" s="6" t="n"/>
     </row>
     <row r="685">
       <c r="E685" s="5" t="n"/>
       <c r="J685" s="5" t="n"/>
       <c r="K685" s="6" t="n"/>
       <c r="M685" s="6" t="n"/>
+      <c r="O685" s="6" t="n"/>
     </row>
     <row r="686">
       <c r="E686" s="5" t="n"/>
       <c r="J686" s="5" t="n"/>
       <c r="K686" s="6" t="n"/>
       <c r="M686" s="6" t="n"/>
+      <c r="O686" s="6" t="n"/>
     </row>
     <row r="687">
       <c r="E687" s="5" t="n"/>
       <c r="J687" s="5" t="n"/>
       <c r="K687" s="6" t="n"/>
       <c r="M687" s="6" t="n"/>
+      <c r="O687" s="6" t="n"/>
     </row>
     <row r="688">
       <c r="E688" s="5" t="n"/>
       <c r="J688" s="5" t="n"/>
       <c r="K688" s="6" t="n"/>
       <c r="M688" s="6" t="n"/>
+      <c r="O688" s="6" t="n"/>
     </row>
     <row r="689">
       <c r="E689" s="5" t="n"/>
       <c r="J689" s="5" t="n"/>
       <c r="K689" s="6" t="n"/>
       <c r="M689" s="6" t="n"/>
+      <c r="O689" s="6" t="n"/>
     </row>
     <row r="690">
       <c r="E690" s="5" t="n"/>
       <c r="J690" s="5" t="n"/>
       <c r="K690" s="6" t="n"/>
       <c r="M690" s="6" t="n"/>
+      <c r="O690" s="6" t="n"/>
     </row>
     <row r="691">
       <c r="E691" s="5" t="n"/>
       <c r="J691" s="5" t="n"/>
       <c r="K691" s="6" t="n"/>
       <c r="M691" s="6" t="n"/>
+      <c r="O691" s="6" t="n"/>
     </row>
     <row r="692">
       <c r="E692" s="5" t="n"/>
       <c r="J692" s="5" t="n"/>
       <c r="K692" s="6" t="n"/>
       <c r="M692" s="6" t="n"/>
+      <c r="O692" s="6" t="n"/>
     </row>
     <row r="693">
       <c r="E693" s="5" t="n"/>
       <c r="J693" s="5" t="n"/>
       <c r="K693" s="6" t="n"/>
       <c r="M693" s="6" t="n"/>
+      <c r="O693" s="6" t="n"/>
     </row>
     <row r="694">
       <c r="E694" s="5" t="n"/>
       <c r="J694" s="5" t="n"/>
       <c r="K694" s="6" t="n"/>
       <c r="M694" s="6" t="n"/>
+      <c r="O694" s="6" t="n"/>
     </row>
     <row r="695">
       <c r="E695" s="5" t="n"/>
       <c r="J695" s="5" t="n"/>
       <c r="K695" s="6" t="n"/>
       <c r="M695" s="6" t="n"/>
+      <c r="O695" s="6" t="n"/>
     </row>
     <row r="696">
       <c r="E696" s="5" t="n"/>
       <c r="J696" s="5" t="n"/>
       <c r="K696" s="6" t="n"/>
       <c r="M696" s="6" t="n"/>
+      <c r="O696" s="6" t="n"/>
     </row>
     <row r="697">
       <c r="E697" s="5" t="n"/>
       <c r="J697" s="5" t="n"/>
       <c r="K697" s="6" t="n"/>
       <c r="M697" s="6" t="n"/>
+      <c r="O697" s="6" t="n"/>
     </row>
     <row r="698">
       <c r="E698" s="5" t="n"/>
       <c r="J698" s="5" t="n"/>
       <c r="K698" s="6" t="n"/>
       <c r="M698" s="6" t="n"/>
+      <c r="O698" s="6" t="n"/>
     </row>
     <row r="699">
       <c r="E699" s="5" t="n"/>
       <c r="J699" s="5" t="n"/>
       <c r="K699" s="6" t="n"/>
       <c r="M699" s="6" t="n"/>
+      <c r="O699" s="6" t="n"/>
     </row>
     <row r="700">
       <c r="E700" s="5" t="n"/>
       <c r="J700" s="5" t="n"/>
       <c r="K700" s="6" t="n"/>
       <c r="M700" s="6" t="n"/>
+      <c r="O700" s="6" t="n"/>
     </row>
     <row r="701">
       <c r="E701" s="5" t="n"/>
       <c r="J701" s="5" t="n"/>
       <c r="K701" s="6" t="n"/>
       <c r="M701" s="6" t="n"/>
+      <c r="O701" s="6" t="n"/>
     </row>
     <row r="702">
       <c r="E702" s="5" t="n"/>
       <c r="J702" s="5" t="n"/>
       <c r="K702" s="6" t="n"/>
       <c r="M702" s="6" t="n"/>
+      <c r="O702" s="6" t="n"/>
     </row>
     <row r="703">
       <c r="E703" s="5" t="n"/>
       <c r="J703" s="5" t="n"/>
       <c r="K703" s="6" t="n"/>
       <c r="M703" s="6" t="n"/>
+      <c r="O703" s="6" t="n"/>
     </row>
     <row r="704">
       <c r="E704" s="5" t="n"/>
       <c r="J704" s="5" t="n"/>
       <c r="K704" s="6" t="n"/>
       <c r="M704" s="6" t="n"/>
+      <c r="O704" s="6" t="n"/>
     </row>
     <row r="705">
       <c r="E705" s="5" t="n"/>
       <c r="J705" s="5" t="n"/>
       <c r="K705" s="6" t="n"/>
       <c r="M705" s="6" t="n"/>
+      <c r="O705" s="6" t="n"/>
     </row>
     <row r="706">
       <c r="E706" s="5" t="n"/>
       <c r="J706" s="5" t="n"/>
       <c r="K706" s="6" t="n"/>
       <c r="M706" s="6" t="n"/>
+      <c r="O706" s="6" t="n"/>
     </row>
     <row r="707">
       <c r="E707" s="5" t="n"/>
       <c r="J707" s="5" t="n"/>
       <c r="K707" s="6" t="n"/>
       <c r="M707" s="6" t="n"/>
+      <c r="O707" s="6" t="n"/>
     </row>
     <row r="708">
       <c r="E708" s="5" t="n"/>
       <c r="J708" s="5" t="n"/>
       <c r="K708" s="6" t="n"/>
       <c r="M708" s="6" t="n"/>
+      <c r="O708" s="6" t="n"/>
     </row>
     <row r="709">
       <c r="E709" s="5" t="n"/>
       <c r="J709" s="5" t="n"/>
       <c r="K709" s="6" t="n"/>
       <c r="M709" s="6" t="n"/>
+      <c r="O709" s="6" t="n"/>
     </row>
     <row r="710">
       <c r="E710" s="5" t="n"/>
       <c r="J710" s="5" t="n"/>
       <c r="K710" s="6" t="n"/>
       <c r="M710" s="6" t="n"/>
+      <c r="O710" s="6" t="n"/>
     </row>
     <row r="711">
       <c r="E711" s="5" t="n"/>
       <c r="J711" s="5" t="n"/>
       <c r="K711" s="6" t="n"/>
       <c r="M711" s="6" t="n"/>
+      <c r="O711" s="6" t="n"/>
     </row>
     <row r="712">
       <c r="E712" s="5" t="n"/>
       <c r="J712" s="5" t="n"/>
       <c r="K712" s="6" t="n"/>
       <c r="M712" s="6" t="n"/>
+      <c r="O712" s="6" t="n"/>
     </row>
     <row r="713">
       <c r="E713" s="5" t="n"/>
       <c r="J713" s="5" t="n"/>
       <c r="K713" s="6" t="n"/>
       <c r="M713" s="6" t="n"/>
+      <c r="O713" s="6" t="n"/>
     </row>
     <row r="714">
       <c r="E714" s="5" t="n"/>
       <c r="J714" s="5" t="n"/>
       <c r="K714" s="6" t="n"/>
       <c r="M714" s="6" t="n"/>
+      <c r="O714" s="6" t="n"/>
     </row>
     <row r="715">
       <c r="E715" s="5" t="n"/>
       <c r="J715" s="5" t="n"/>
       <c r="K715" s="6" t="n"/>
       <c r="M715" s="6" t="n"/>
+      <c r="O715" s="6" t="n"/>
     </row>
     <row r="716">
       <c r="E716" s="5" t="n"/>
       <c r="J716" s="5" t="n"/>
       <c r="K716" s="6" t="n"/>
       <c r="M716" s="6" t="n"/>
+      <c r="O716" s="6" t="n"/>
     </row>
     <row r="717">
       <c r="E717" s="5" t="n"/>
       <c r="J717" s="5" t="n"/>
       <c r="K717" s="6" t="n"/>
       <c r="M717" s="6" t="n"/>
+      <c r="O717" s="6" t="n"/>
     </row>
     <row r="718">
       <c r="E718" s="5" t="n"/>
       <c r="J718" s="5" t="n"/>
       <c r="K718" s="6" t="n"/>
       <c r="M718" s="6" t="n"/>
+      <c r="O718" s="6" t="n"/>
     </row>
     <row r="719">
       <c r="E719" s="5" t="n"/>
       <c r="J719" s="5" t="n"/>
       <c r="K719" s="6" t="n"/>
       <c r="M719" s="6" t="n"/>
+      <c r="O719" s="6" t="n"/>
     </row>
     <row r="720">
       <c r="E720" s="5" t="n"/>
       <c r="J720" s="5" t="n"/>
       <c r="K720" s="6" t="n"/>
       <c r="M720" s="6" t="n"/>
+      <c r="O720" s="6" t="n"/>
     </row>
     <row r="721">
       <c r="E721" s="5" t="n"/>
       <c r="J721" s="5" t="n"/>
       <c r="K721" s="6" t="n"/>
       <c r="M721" s="6" t="n"/>
+      <c r="O721" s="6" t="n"/>
     </row>
     <row r="722">
       <c r="E722" s="5" t="n"/>
       <c r="J722" s="5" t="n"/>
       <c r="K722" s="6" t="n"/>
       <c r="M722" s="6" t="n"/>
+      <c r="O722" s="6" t="n"/>
     </row>
     <row r="723">
       <c r="E723" s="5" t="n"/>
       <c r="J723" s="5" t="n"/>
       <c r="K723" s="6" t="n"/>
       <c r="M723" s="6" t="n"/>
+      <c r="O723" s="6" t="n"/>
     </row>
     <row r="724">
       <c r="E724" s="5" t="n"/>
       <c r="J724" s="5" t="n"/>
       <c r="K724" s="6" t="n"/>
       <c r="M724" s="6" t="n"/>
+      <c r="O724" s="6" t="n"/>
     </row>
     <row r="725">
       <c r="E725" s="5" t="n"/>
       <c r="J725" s="5" t="n"/>
       <c r="K725" s="6" t="n"/>
       <c r="M725" s="6" t="n"/>
+      <c r="O725" s="6" t="n"/>
     </row>
     <row r="726">
       <c r="E726" s="5" t="n"/>
       <c r="J726" s="5" t="n"/>
       <c r="K726" s="6" t="n"/>
       <c r="M726" s="6" t="n"/>
+      <c r="O726" s="6" t="n"/>
     </row>
     <row r="727">
       <c r="E727" s="5" t="n"/>
       <c r="J727" s="5" t="n"/>
       <c r="K727" s="6" t="n"/>
       <c r="M727" s="6" t="n"/>
+      <c r="O727" s="6" t="n"/>
     </row>
     <row r="728">
       <c r="E728" s="5" t="n"/>
       <c r="J728" s="5" t="n"/>
       <c r="K728" s="6" t="n"/>
       <c r="M728" s="6" t="n"/>
+      <c r="O728" s="6" t="n"/>
     </row>
     <row r="729">
       <c r="E729" s="5" t="n"/>
       <c r="J729" s="5" t="n"/>
       <c r="K729" s="6" t="n"/>
       <c r="M729" s="6" t="n"/>
+      <c r="O729" s="6" t="n"/>
     </row>
     <row r="730">
       <c r="E730" s="5" t="n"/>
       <c r="J730" s="5" t="n"/>
       <c r="K730" s="6" t="n"/>
       <c r="M730" s="6" t="n"/>
+      <c r="O730" s="6" t="n"/>
     </row>
     <row r="731">
       <c r="E731" s="5" t="n"/>
       <c r="J731" s="5" t="n"/>
       <c r="K731" s="6" t="n"/>
       <c r="M731" s="6" t="n"/>
+      <c r="O731" s="6" t="n"/>
     </row>
     <row r="732">
       <c r="E732" s="5" t="n"/>
       <c r="J732" s="5" t="n"/>
       <c r="K732" s="6" t="n"/>
       <c r="M732" s="6" t="n"/>
+      <c r="O732" s="6" t="n"/>
     </row>
     <row r="733">
       <c r="E733" s="5" t="n"/>
       <c r="J733" s="5" t="n"/>
       <c r="K733" s="6" t="n"/>
       <c r="M733" s="6" t="n"/>
+      <c r="O733" s="6" t="n"/>
     </row>
     <row r="734">
       <c r="E734" s="5" t="n"/>
       <c r="J734" s="5" t="n"/>
       <c r="K734" s="6" t="n"/>
       <c r="M734" s="6" t="n"/>
+      <c r="O734" s="6" t="n"/>
     </row>
     <row r="735">
       <c r="E735" s="5" t="n"/>
       <c r="J735" s="5" t="n"/>
       <c r="K735" s="6" t="n"/>
       <c r="M735" s="6" t="n"/>
+      <c r="O735" s="6" t="n"/>
     </row>
     <row r="736">
       <c r="E736" s="5" t="n"/>
       <c r="J736" s="5" t="n"/>
       <c r="K736" s="6" t="n"/>
       <c r="M736" s="6" t="n"/>
+      <c r="O736" s="6" t="n"/>
     </row>
     <row r="737">
       <c r="E737" s="5" t="n"/>
       <c r="J737" s="5" t="n"/>
       <c r="K737" s="6" t="n"/>
       <c r="M737" s="6" t="n"/>
+      <c r="O737" s="6" t="n"/>
     </row>
     <row r="738">
       <c r="E738" s="5" t="n"/>
       <c r="J738" s="5" t="n"/>
       <c r="K738" s="6" t="n"/>
       <c r="M738" s="6" t="n"/>
+      <c r="O738" s="6" t="n"/>
     </row>
     <row r="739">
       <c r="E739" s="5" t="n"/>
       <c r="J739" s="5" t="n"/>
       <c r="K739" s="6" t="n"/>
       <c r="M739" s="6" t="n"/>
+      <c r="O739" s="6" t="n"/>
     </row>
     <row r="740">
       <c r="E740" s="5" t="n"/>
       <c r="J740" s="5" t="n"/>
       <c r="K740" s="6" t="n"/>
       <c r="M740" s="6" t="n"/>
+      <c r="O740" s="6" t="n"/>
     </row>
     <row r="741">
       <c r="E741" s="5" t="n"/>
       <c r="J741" s="5" t="n"/>
       <c r="K741" s="6" t="n"/>
       <c r="M741" s="6" t="n"/>
+      <c r="O741" s="6" t="n"/>
     </row>
     <row r="742">
       <c r="E742" s="5" t="n"/>
       <c r="J742" s="5" t="n"/>
       <c r="K742" s="6" t="n"/>
       <c r="M742" s="6" t="n"/>
+      <c r="O742" s="6" t="n"/>
     </row>
     <row r="743">
       <c r="E743" s="5" t="n"/>
       <c r="J743" s="5" t="n"/>
       <c r="K743" s="6" t="n"/>
       <c r="M743" s="6" t="n"/>
+      <c r="O743" s="6" t="n"/>
     </row>
     <row r="744">
       <c r="E744" s="5" t="n"/>
       <c r="J744" s="5" t="n"/>
       <c r="K744" s="6" t="n"/>
       <c r="M744" s="6" t="n"/>
+      <c r="O744" s="6" t="n"/>
     </row>
     <row r="745">
       <c r="E745" s="5" t="n"/>
       <c r="J745" s="5" t="n"/>
       <c r="K745" s="6" t="n"/>
       <c r="M745" s="6" t="n"/>
+      <c r="O745" s="6" t="n"/>
     </row>
     <row r="746">
       <c r="E746" s="5" t="n"/>
       <c r="J746" s="5" t="n"/>
       <c r="K746" s="6" t="n"/>
       <c r="M746" s="6" t="n"/>
+      <c r="O746" s="6" t="n"/>
     </row>
     <row r="747">
       <c r="E747" s="5" t="n"/>
       <c r="J747" s="5" t="n"/>
       <c r="K747" s="6" t="n"/>
       <c r="M747" s="6" t="n"/>
+      <c r="O747" s="6" t="n"/>
     </row>
     <row r="748">
       <c r="E748" s="5" t="n"/>
       <c r="J748" s="5" t="n"/>
       <c r="K748" s="6" t="n"/>
       <c r="M748" s="6" t="n"/>
+      <c r="O748" s="6" t="n"/>
     </row>
     <row r="749">
       <c r="E749" s="5" t="n"/>
       <c r="J749" s="5" t="n"/>
       <c r="K749" s="6" t="n"/>
       <c r="M749" s="6" t="n"/>
+      <c r="O749" s="6" t="n"/>
     </row>
     <row r="750">
       <c r="E750" s="5" t="n"/>
       <c r="J750" s="5" t="n"/>
       <c r="K750" s="6" t="n"/>
       <c r="M750" s="6" t="n"/>
+      <c r="O750" s="6" t="n"/>
     </row>
     <row r="751">
       <c r="E751" s="5" t="n"/>
       <c r="J751" s="5" t="n"/>
       <c r="K751" s="6" t="n"/>
       <c r="M751" s="6" t="n"/>
+      <c r="O751" s="6" t="n"/>
     </row>
     <row r="752">
       <c r="E752" s="5" t="n"/>
       <c r="J752" s="5" t="n"/>
       <c r="K752" s="6" t="n"/>
       <c r="M752" s="6" t="n"/>
+      <c r="O752" s="6" t="n"/>
     </row>
     <row r="753">
       <c r="E753" s="5" t="n"/>
       <c r="J753" s="5" t="n"/>
       <c r="K753" s="6" t="n"/>
       <c r="M753" s="6" t="n"/>
+      <c r="O753" s="6" t="n"/>
     </row>
     <row r="754">
       <c r="E754" s="5" t="n"/>
       <c r="J754" s="5" t="n"/>
       <c r="K754" s="6" t="n"/>
       <c r="M754" s="6" t="n"/>
+      <c r="O754" s="6" t="n"/>
     </row>
     <row r="755">
       <c r="E755" s="5" t="n"/>
       <c r="J755" s="5" t="n"/>
       <c r="K755" s="6" t="n"/>
       <c r="M755" s="6" t="n"/>
+      <c r="O755" s="6" t="n"/>
     </row>
     <row r="756">
       <c r="E756" s="5" t="n"/>
       <c r="J756" s="5" t="n"/>
       <c r="K756" s="6" t="n"/>
       <c r="M756" s="6" t="n"/>
+      <c r="O756" s="6" t="n"/>
     </row>
     <row r="757">
       <c r="E757" s="5" t="n"/>
       <c r="J757" s="5" t="n"/>
       <c r="K757" s="6" t="n"/>
       <c r="M757" s="6" t="n"/>
+      <c r="O757" s="6" t="n"/>
     </row>
     <row r="758">
       <c r="E758" s="5" t="n"/>
       <c r="J758" s="5" t="n"/>
       <c r="K758" s="6" t="n"/>
       <c r="M758" s="6" t="n"/>
+      <c r="O758" s="6" t="n"/>
     </row>
     <row r="759">
       <c r="E759" s="5" t="n"/>
       <c r="J759" s="5" t="n"/>
       <c r="K759" s="6" t="n"/>
       <c r="M759" s="6" t="n"/>
+      <c r="O759" s="6" t="n"/>
     </row>
     <row r="760">
       <c r="E760" s="5" t="n"/>
       <c r="J760" s="5" t="n"/>
       <c r="K760" s="6" t="n"/>
       <c r="M760" s="6" t="n"/>
+      <c r="O760" s="6" t="n"/>
     </row>
     <row r="761">
       <c r="E761" s="5" t="n"/>
       <c r="J761" s="5" t="n"/>
       <c r="K761" s="6" t="n"/>
       <c r="M761" s="6" t="n"/>
+      <c r="O761" s="6" t="n"/>
     </row>
     <row r="762">
       <c r="E762" s="5" t="n"/>
       <c r="J762" s="5" t="n"/>
       <c r="K762" s="6" t="n"/>
       <c r="M762" s="6" t="n"/>
+      <c r="O762" s="6" t="n"/>
     </row>
     <row r="763">
       <c r="E763" s="5" t="n"/>
       <c r="J763" s="5" t="n"/>
       <c r="K763" s="6" t="n"/>
       <c r="M763" s="6" t="n"/>
+      <c r="O763" s="6" t="n"/>
     </row>
     <row r="764">
       <c r="E764" s="5" t="n"/>
       <c r="J764" s="5" t="n"/>
       <c r="K764" s="6" t="n"/>
       <c r="M764" s="6" t="n"/>
+      <c r="O764" s="6" t="n"/>
     </row>
     <row r="765">
       <c r="E765" s="5" t="n"/>
       <c r="J765" s="5" t="n"/>
       <c r="K765" s="6" t="n"/>
       <c r="M765" s="6" t="n"/>
+      <c r="O765" s="6" t="n"/>
     </row>
     <row r="766">
       <c r="E766" s="5" t="n"/>
       <c r="J766" s="5" t="n"/>
       <c r="K766" s="6" t="n"/>
       <c r="M766" s="6" t="n"/>
+      <c r="O766" s="6" t="n"/>
     </row>
     <row r="767">
       <c r="E767" s="5" t="n"/>
       <c r="J767" s="5" t="n"/>
       <c r="K767" s="6" t="n"/>
       <c r="M767" s="6" t="n"/>
+      <c r="O767" s="6" t="n"/>
     </row>
     <row r="768">
       <c r="E768" s="5" t="n"/>
       <c r="J768" s="5" t="n"/>
       <c r="K768" s="6" t="n"/>
       <c r="M768" s="6" t="n"/>
+      <c r="O768" s="6" t="n"/>
     </row>
     <row r="769">
       <c r="E769" s="5" t="n"/>
       <c r="J769" s="5" t="n"/>
       <c r="K769" s="6" t="n"/>
       <c r="M769" s="6" t="n"/>
+      <c r="O769" s="6" t="n"/>
     </row>
     <row r="770">
       <c r="E770" s="5" t="n"/>
       <c r="J770" s="5" t="n"/>
       <c r="K770" s="6" t="n"/>
       <c r="M770" s="6" t="n"/>
+      <c r="O770" s="6" t="n"/>
     </row>
     <row r="771">
       <c r="E771" s="5" t="n"/>
       <c r="J771" s="5" t="n"/>
       <c r="K771" s="6" t="n"/>
       <c r="M771" s="6" t="n"/>
+      <c r="O771" s="6" t="n"/>
     </row>
     <row r="772">
       <c r="E772" s="5" t="n"/>
       <c r="J772" s="5" t="n"/>
       <c r="K772" s="6" t="n"/>
       <c r="M772" s="6" t="n"/>
+      <c r="O772" s="6" t="n"/>
     </row>
     <row r="773">
       <c r="E773" s="5" t="n"/>
       <c r="J773" s="5" t="n"/>
       <c r="K773" s="6" t="n"/>
       <c r="M773" s="6" t="n"/>
+      <c r="O773" s="6" t="n"/>
     </row>
     <row r="774">
       <c r="E774" s="5" t="n"/>
       <c r="J774" s="5" t="n"/>
       <c r="K774" s="6" t="n"/>
       <c r="M774" s="6" t="n"/>
+      <c r="O774" s="6" t="n"/>
     </row>
     <row r="775">
       <c r="E775" s="5" t="n"/>
       <c r="J775" s="5" t="n"/>
       <c r="K775" s="6" t="n"/>
       <c r="M775" s="6" t="n"/>
+      <c r="O775" s="6" t="n"/>
     </row>
     <row r="776">
       <c r="E776" s="5" t="n"/>
       <c r="J776" s="5" t="n"/>
       <c r="K776" s="6" t="n"/>
       <c r="M776" s="6" t="n"/>
+      <c r="O776" s="6" t="n"/>
     </row>
     <row r="777">
       <c r="E777" s="5" t="n"/>
       <c r="J777" s="5" t="n"/>
       <c r="K777" s="6" t="n"/>
       <c r="M777" s="6" t="n"/>
+      <c r="O777" s="6" t="n"/>
     </row>
     <row r="778">
       <c r="E778" s="5" t="n"/>
       <c r="J778" s="5" t="n"/>
       <c r="K778" s="6" t="n"/>
       <c r="M778" s="6" t="n"/>
+      <c r="O778" s="6" t="n"/>
     </row>
     <row r="779">
       <c r="E779" s="5" t="n"/>
       <c r="J779" s="5" t="n"/>
       <c r="K779" s="6" t="n"/>
       <c r="M779" s="6" t="n"/>
+      <c r="O779" s="6" t="n"/>
     </row>
     <row r="780">
       <c r="E780" s="5" t="n"/>
       <c r="J780" s="5" t="n"/>
       <c r="K780" s="6" t="n"/>
       <c r="M780" s="6" t="n"/>
+      <c r="O780" s="6" t="n"/>
     </row>
     <row r="781">
       <c r="E781" s="5" t="n"/>
       <c r="J781" s="5" t="n"/>
       <c r="K781" s="6" t="n"/>
       <c r="M781" s="6" t="n"/>
+      <c r="O781" s="6" t="n"/>
     </row>
     <row r="782">
       <c r="E782" s="5" t="n"/>
       <c r="J782" s="5" t="n"/>
       <c r="K782" s="6" t="n"/>
       <c r="M782" s="6" t="n"/>
+      <c r="O782" s="6" t="n"/>
     </row>
     <row r="783">
       <c r="E783" s="5" t="n"/>
       <c r="J783" s="5" t="n"/>
       <c r="K783" s="6" t="n"/>
       <c r="M783" s="6" t="n"/>
+      <c r="O783" s="6" t="n"/>
     </row>
     <row r="784">
       <c r="E784" s="5" t="n"/>
       <c r="J784" s="5" t="n"/>
       <c r="K784" s="6" t="n"/>
       <c r="M784" s="6" t="n"/>
+      <c r="O784" s="6" t="n"/>
     </row>
     <row r="785">
       <c r="E785" s="5" t="n"/>
       <c r="J785" s="5" t="n"/>
       <c r="K785" s="6" t="n"/>
       <c r="M785" s="6" t="n"/>
+      <c r="O785" s="6" t="n"/>
     </row>
     <row r="786">
       <c r="E786" s="5" t="n"/>
       <c r="J786" s="5" t="n"/>
       <c r="K786" s="6" t="n"/>
       <c r="M786" s="6" t="n"/>
+      <c r="O786" s="6" t="n"/>
     </row>
     <row r="787">
       <c r="E787" s="5" t="n"/>
       <c r="J787" s="5" t="n"/>
       <c r="K787" s="6" t="n"/>
       <c r="M787" s="6" t="n"/>
+      <c r="O787" s="6" t="n"/>
     </row>
     <row r="788">
       <c r="E788" s="5" t="n"/>
       <c r="J788" s="5" t="n"/>
       <c r="K788" s="6" t="n"/>
       <c r="M788" s="6" t="n"/>
+      <c r="O788" s="6" t="n"/>
     </row>
     <row r="789">
       <c r="E789" s="5" t="n"/>
       <c r="J789" s="5" t="n"/>
       <c r="K789" s="6" t="n"/>
       <c r="M789" s="6" t="n"/>
+      <c r="O789" s="6" t="n"/>
     </row>
     <row r="790">
       <c r="E790" s="5" t="n"/>
       <c r="J790" s="5" t="n"/>
       <c r="K790" s="6" t="n"/>
       <c r="M790" s="6" t="n"/>
+      <c r="O790" s="6" t="n"/>
     </row>
     <row r="791">
       <c r="E791" s="5" t="n"/>
       <c r="J791" s="5" t="n"/>
       <c r="K791" s="6" t="n"/>
       <c r="M791" s="6" t="n"/>
+      <c r="O791" s="6" t="n"/>
     </row>
     <row r="792">
       <c r="E792" s="5" t="n"/>
       <c r="J792" s="5" t="n"/>
       <c r="K792" s="6" t="n"/>
       <c r="M792" s="6" t="n"/>
+      <c r="O792" s="6" t="n"/>
     </row>
     <row r="793">
       <c r="E793" s="5" t="n"/>
       <c r="J793" s="5" t="n"/>
       <c r="K793" s="6" t="n"/>
       <c r="M793" s="6" t="n"/>
+      <c r="O793" s="6" t="n"/>
     </row>
     <row r="794">
       <c r="E794" s="5" t="n"/>
       <c r="J794" s="5" t="n"/>
       <c r="K794" s="6" t="n"/>
       <c r="M794" s="6" t="n"/>
+      <c r="O794" s="6" t="n"/>
     </row>
     <row r="795">
       <c r="E795" s="5" t="n"/>
       <c r="J795" s="5" t="n"/>
       <c r="K795" s="6" t="n"/>
       <c r="M795" s="6" t="n"/>
+      <c r="O795" s="6" t="n"/>
     </row>
     <row r="796">
       <c r="E796" s="5" t="n"/>
       <c r="J796" s="5" t="n"/>
       <c r="K796" s="6" t="n"/>
       <c r="M796" s="6" t="n"/>
+      <c r="O796" s="6" t="n"/>
     </row>
     <row r="797">
       <c r="E797" s="5" t="n"/>
       <c r="J797" s="5" t="n"/>
       <c r="K797" s="6" t="n"/>
       <c r="M797" s="6" t="n"/>
+      <c r="O797" s="6" t="n"/>
     </row>
     <row r="798">
       <c r="E798" s="5" t="n"/>
       <c r="J798" s="5" t="n"/>
       <c r="K798" s="6" t="n"/>
       <c r="M798" s="6" t="n"/>
+      <c r="O798" s="6" t="n"/>
     </row>
     <row r="799">
       <c r="E799" s="5" t="n"/>
       <c r="J799" s="5" t="n"/>
       <c r="K799" s="6" t="n"/>
       <c r="M799" s="6" t="n"/>
+      <c r="O799" s="6" t="n"/>
     </row>
     <row r="800">
       <c r="E800" s="5" t="n"/>
       <c r="J800" s="5" t="n"/>
       <c r="K800" s="6" t="n"/>
       <c r="M800" s="6" t="n"/>
+      <c r="O800" s="6" t="n"/>
     </row>
     <row r="801">
       <c r="E801" s="5" t="n"/>
       <c r="J801" s="5" t="n"/>
       <c r="K801" s="6" t="n"/>
       <c r="M801" s="6" t="n"/>
+      <c r="O801" s="6" t="n"/>
     </row>
     <row r="802">
       <c r="E802" s="5" t="n"/>
       <c r="J802" s="5" t="n"/>
       <c r="K802" s="6" t="n"/>
       <c r="M802" s="6" t="n"/>
+      <c r="O802" s="6" t="n"/>
     </row>
     <row r="803">
       <c r="E803" s="5" t="n"/>
       <c r="J803" s="5" t="n"/>
       <c r="K803" s="6" t="n"/>
       <c r="M803" s="6" t="n"/>
+      <c r="O803" s="6" t="n"/>
     </row>
     <row r="804">
       <c r="E804" s="5" t="n"/>
       <c r="J804" s="5" t="n"/>
       <c r="K804" s="6" t="n"/>
       <c r="M804" s="6" t="n"/>
+      <c r="O804" s="6" t="n"/>
     </row>
     <row r="805">
       <c r="E805" s="5" t="n"/>
       <c r="J805" s="5" t="n"/>
       <c r="K805" s="6" t="n"/>
       <c r="M805" s="6" t="n"/>
+      <c r="O805" s="6" t="n"/>
     </row>
     <row r="806">
       <c r="E806" s="5" t="n"/>
       <c r="J806" s="5" t="n"/>
       <c r="K806" s="6" t="n"/>
       <c r="M806" s="6" t="n"/>
+      <c r="O806" s="6" t="n"/>
     </row>
     <row r="807">
       <c r="E807" s="5" t="n"/>
       <c r="J807" s="5" t="n"/>
       <c r="K807" s="6" t="n"/>
       <c r="M807" s="6" t="n"/>
+      <c r="O807" s="6" t="n"/>
     </row>
     <row r="808">
       <c r="E808" s="5" t="n"/>
       <c r="J808" s="5" t="n"/>
       <c r="K808" s="6" t="n"/>
       <c r="M808" s="6" t="n"/>
+      <c r="O808" s="6" t="n"/>
     </row>
     <row r="809">
       <c r="E809" s="5" t="n"/>
       <c r="J809" s="5" t="n"/>
       <c r="K809" s="6" t="n"/>
       <c r="M809" s="6" t="n"/>
+      <c r="O809" s="6" t="n"/>
     </row>
     <row r="810">
       <c r="E810" s="5" t="n"/>
       <c r="J810" s="5" t="n"/>
       <c r="K810" s="6" t="n"/>
       <c r="M810" s="6" t="n"/>
+      <c r="O810" s="6" t="n"/>
     </row>
     <row r="811">
       <c r="E811" s="5" t="n"/>
       <c r="J811" s="5" t="n"/>
       <c r="K811" s="6" t="n"/>
       <c r="M811" s="6" t="n"/>
+      <c r="O811" s="6" t="n"/>
     </row>
     <row r="812">
       <c r="E812" s="5" t="n"/>
       <c r="J812" s="5" t="n"/>
       <c r="K812" s="6" t="n"/>
       <c r="M812" s="6" t="n"/>
+      <c r="O812" s="6" t="n"/>
     </row>
     <row r="813">
       <c r="E813" s="5" t="n"/>
       <c r="J813" s="5" t="n"/>
       <c r="K813" s="6" t="n"/>
       <c r="M813" s="6" t="n"/>
+      <c r="O813" s="6" t="n"/>
     </row>
     <row r="814">
       <c r="E814" s="5" t="n"/>
       <c r="J814" s="5" t="n"/>
       <c r="K814" s="6" t="n"/>
       <c r="M814" s="6" t="n"/>
+      <c r="O814" s="6" t="n"/>
     </row>
     <row r="815">
       <c r="E815" s="5" t="n"/>
       <c r="J815" s="5" t="n"/>
       <c r="K815" s="6" t="n"/>
       <c r="M815" s="6" t="n"/>
+      <c r="O815" s="6" t="n"/>
     </row>
     <row r="816">
       <c r="E816" s="5" t="n"/>
       <c r="J816" s="5" t="n"/>
       <c r="K816" s="6" t="n"/>
       <c r="M816" s="6" t="n"/>
+      <c r="O816" s="6" t="n"/>
     </row>
     <row r="817">
       <c r="E817" s="5" t="n"/>
       <c r="J817" s="5" t="n"/>
       <c r="K817" s="6" t="n"/>
       <c r="M817" s="6" t="n"/>
+      <c r="O817" s="6" t="n"/>
     </row>
     <row r="818">
       <c r="E818" s="5" t="n"/>
       <c r="J818" s="5" t="n"/>
       <c r="K818" s="6" t="n"/>
       <c r="M818" s="6" t="n"/>
+      <c r="O818" s="6" t="n"/>
     </row>
     <row r="819">
       <c r="E819" s="5" t="n"/>
       <c r="J819" s="5" t="n"/>
       <c r="K819" s="6" t="n"/>
       <c r="M819" s="6" t="n"/>
+      <c r="O819" s="6" t="n"/>
     </row>
     <row r="820">
       <c r="E820" s="5" t="n"/>
       <c r="J820" s="5" t="n"/>
       <c r="K820" s="6" t="n"/>
       <c r="M820" s="6" t="n"/>
+      <c r="O820" s="6" t="n"/>
     </row>
     <row r="821">
       <c r="E821" s="5" t="n"/>
       <c r="J821" s="5" t="n"/>
       <c r="K821" s="6" t="n"/>
       <c r="M821" s="6" t="n"/>
+      <c r="O821" s="6" t="n"/>
     </row>
     <row r="822">
       <c r="E822" s="5" t="n"/>
       <c r="J822" s="5" t="n"/>
       <c r="K822" s="6" t="n"/>
       <c r="M822" s="6" t="n"/>
+      <c r="O822" s="6" t="n"/>
     </row>
     <row r="823">
       <c r="E823" s="5" t="n"/>
       <c r="J823" s="5" t="n"/>
       <c r="K823" s="6" t="n"/>
       <c r="M823" s="6" t="n"/>
+      <c r="O823" s="6" t="n"/>
     </row>
     <row r="824">
       <c r="E824" s="5" t="n"/>
       <c r="J824" s="5" t="n"/>
       <c r="K824" s="6" t="n"/>
       <c r="M824" s="6" t="n"/>
+      <c r="O824" s="6" t="n"/>
     </row>
     <row r="825">
       <c r="E825" s="5" t="n"/>
       <c r="J825" s="5" t="n"/>
       <c r="K825" s="6" t="n"/>
       <c r="M825" s="6" t="n"/>
+      <c r="O825" s="6" t="n"/>
     </row>
     <row r="826">
       <c r="E826" s="5" t="n"/>
       <c r="J826" s="5" t="n"/>
       <c r="K826" s="6" t="n"/>
       <c r="M826" s="6" t="n"/>
+      <c r="O826" s="6" t="n"/>
     </row>
     <row r="827">
       <c r="E827" s="5" t="n"/>
       <c r="J827" s="5" t="n"/>
       <c r="K827" s="6" t="n"/>
       <c r="M827" s="6" t="n"/>
+      <c r="O827" s="6" t="n"/>
     </row>
     <row r="828">
       <c r="E828" s="5" t="n"/>
       <c r="J828" s="5" t="n"/>
       <c r="K828" s="6" t="n"/>
       <c r="M828" s="6" t="n"/>
+      <c r="O828" s="6" t="n"/>
     </row>
     <row r="829">
       <c r="E829" s="5" t="n"/>
       <c r="J829" s="5" t="n"/>
       <c r="K829" s="6" t="n"/>
       <c r="M829" s="6" t="n"/>
+      <c r="O829" s="6" t="n"/>
     </row>
     <row r="830">
       <c r="E830" s="5" t="n"/>
       <c r="J830" s="5" t="n"/>
       <c r="K830" s="6" t="n"/>
       <c r="M830" s="6" t="n"/>
+      <c r="O830" s="6" t="n"/>
     </row>
     <row r="831">
       <c r="E831" s="5" t="n"/>
       <c r="J831" s="5" t="n"/>
       <c r="K831" s="6" t="n"/>
       <c r="M831" s="6" t="n"/>
+      <c r="O831" s="6" t="n"/>
     </row>
     <row r="832">
       <c r="E832" s="5" t="n"/>
       <c r="J832" s="5" t="n"/>
       <c r="K832" s="6" t="n"/>
       <c r="M832" s="6" t="n"/>
+      <c r="O832" s="6" t="n"/>
     </row>
     <row r="833">
       <c r="E833" s="5" t="n"/>
       <c r="J833" s="5" t="n"/>
       <c r="K833" s="6" t="n"/>
       <c r="M833" s="6" t="n"/>
+      <c r="O833" s="6" t="n"/>
     </row>
     <row r="834">
       <c r="E834" s="5" t="n"/>
       <c r="J834" s="5" t="n"/>
       <c r="K834" s="6" t="n"/>
       <c r="M834" s="6" t="n"/>
+      <c r="O834" s="6" t="n"/>
     </row>
     <row r="835">
       <c r="E835" s="5" t="n"/>
       <c r="J835" s="5" t="n"/>
       <c r="K835" s="6" t="n"/>
       <c r="M835" s="6" t="n"/>
+      <c r="O835" s="6" t="n"/>
     </row>
     <row r="836">
       <c r="E836" s="5" t="n"/>
       <c r="J836" s="5" t="n"/>
       <c r="K836" s="6" t="n"/>
       <c r="M836" s="6" t="n"/>
+      <c r="O836" s="6" t="n"/>
     </row>
     <row r="837">
       <c r="E837" s="5" t="n"/>
       <c r="J837" s="5" t="n"/>
       <c r="K837" s="6" t="n"/>
       <c r="M837" s="6" t="n"/>
+      <c r="O837" s="6" t="n"/>
     </row>
     <row r="838">
       <c r="E838" s="5" t="n"/>
       <c r="J838" s="5" t="n"/>
       <c r="K838" s="6" t="n"/>
       <c r="M838" s="6" t="n"/>
+      <c r="O838" s="6" t="n"/>
     </row>
     <row r="839">
       <c r="E839" s="5" t="n"/>
       <c r="J839" s="5" t="n"/>
       <c r="K839" s="6" t="n"/>
       <c r="M839" s="6" t="n"/>
+      <c r="O839" s="6" t="n"/>
     </row>
     <row r="840">
       <c r="E840" s="5" t="n"/>
       <c r="J840" s="5" t="n"/>
       <c r="K840" s="6" t="n"/>
       <c r="M840" s="6" t="n"/>
+      <c r="O840" s="6" t="n"/>
     </row>
     <row r="841">
       <c r="E841" s="5" t="n"/>
       <c r="J841" s="5" t="n"/>
       <c r="K841" s="6" t="n"/>
       <c r="M841" s="6" t="n"/>
+      <c r="O841" s="6" t="n"/>
     </row>
     <row r="842">
       <c r="E842" s="5" t="n"/>
       <c r="J842" s="5" t="n"/>
       <c r="K842" s="6" t="n"/>
       <c r="M842" s="6" t="n"/>
+      <c r="O842" s="6" t="n"/>
     </row>
     <row r="843">
       <c r="E843" s="5" t="n"/>
       <c r="J843" s="5" t="n"/>
       <c r="K843" s="6" t="n"/>
       <c r="M843" s="6" t="n"/>
+      <c r="O843" s="6" t="n"/>
     </row>
     <row r="844">
       <c r="E844" s="5" t="n"/>
       <c r="J844" s="5" t="n"/>
       <c r="K844" s="6" t="n"/>
       <c r="M844" s="6" t="n"/>
+      <c r="O844" s="6" t="n"/>
     </row>
     <row r="845">
       <c r="E845" s="5" t="n"/>
       <c r="J845" s="5" t="n"/>
       <c r="K845" s="6" t="n"/>
       <c r="M845" s="6" t="n"/>
+      <c r="O845" s="6" t="n"/>
     </row>
     <row r="846">
       <c r="E846" s="5" t="n"/>
       <c r="J846" s="5" t="n"/>
       <c r="K846" s="6" t="n"/>
       <c r="M846" s="6" t="n"/>
+      <c r="O846" s="6" t="n"/>
     </row>
     <row r="847">
       <c r="E847" s="5" t="n"/>
       <c r="J847" s="5" t="n"/>
       <c r="K847" s="6" t="n"/>
       <c r="M847" s="6" t="n"/>
+      <c r="O847" s="6" t="n"/>
     </row>
     <row r="848">
       <c r="E848" s="5" t="n"/>
       <c r="J848" s="5" t="n"/>
       <c r="K848" s="6" t="n"/>
       <c r="M848" s="6" t="n"/>
+      <c r="O848" s="6" t="n"/>
     </row>
     <row r="849">
       <c r="E849" s="5" t="n"/>
       <c r="J849" s="5" t="n"/>
       <c r="K849" s="6" t="n"/>
       <c r="M849" s="6" t="n"/>
+      <c r="O849" s="6" t="n"/>
     </row>
     <row r="850">
       <c r="E850" s="5" t="n"/>
       <c r="J850" s="5" t="n"/>
       <c r="K850" s="6" t="n"/>
       <c r="M850" s="6" t="n"/>
+      <c r="O850" s="6" t="n"/>
     </row>
     <row r="851">
       <c r="E851" s="5" t="n"/>
       <c r="J851" s="5" t="n"/>
       <c r="K851" s="6" t="n"/>
       <c r="M851" s="6" t="n"/>
+      <c r="O851" s="6" t="n"/>
     </row>
     <row r="852">
       <c r="E852" s="5" t="n"/>
       <c r="J852" s="5" t="n"/>
       <c r="K852" s="6" t="n"/>
       <c r="M852" s="6" t="n"/>
+      <c r="O852" s="6" t="n"/>
     </row>
     <row r="853">
       <c r="E853" s="5" t="n"/>
       <c r="J853" s="5" t="n"/>
       <c r="K853" s="6" t="n"/>
       <c r="M853" s="6" t="n"/>
+      <c r="O853" s="6" t="n"/>
     </row>
     <row r="854">
       <c r="E854" s="5" t="n"/>
       <c r="J854" s="5" t="n"/>
       <c r="K854" s="6" t="n"/>
       <c r="M854" s="6" t="n"/>
+      <c r="O854" s="6" t="n"/>
     </row>
     <row r="855">
       <c r="E855" s="5" t="n"/>
       <c r="J855" s="5" t="n"/>
       <c r="K855" s="6" t="n"/>
       <c r="M855" s="6" t="n"/>
+      <c r="O855" s="6" t="n"/>
     </row>
     <row r="856">
       <c r="E856" s="5" t="n"/>
       <c r="J856" s="5" t="n"/>
       <c r="K856" s="6" t="n"/>
       <c r="M856" s="6" t="n"/>
+      <c r="O856" s="6" t="n"/>
     </row>
     <row r="857">
       <c r="E857" s="5" t="n"/>
       <c r="J857" s="5" t="n"/>
       <c r="K857" s="6" t="n"/>
       <c r="M857" s="6" t="n"/>
+      <c r="O857" s="6" t="n"/>
     </row>
     <row r="858">
       <c r="E858" s="5" t="n"/>
       <c r="J858" s="5" t="n"/>
       <c r="K858" s="6" t="n"/>
       <c r="M858" s="6" t="n"/>
+      <c r="O858" s="6" t="n"/>
     </row>
     <row r="859">
       <c r="E859" s="5" t="n"/>
       <c r="J859" s="5" t="n"/>
       <c r="K859" s="6" t="n"/>
       <c r="M859" s="6" t="n"/>
+      <c r="O859" s="6" t="n"/>
     </row>
     <row r="860">
       <c r="E860" s="5" t="n"/>
       <c r="J860" s="5" t="n"/>
       <c r="K860" s="6" t="n"/>
       <c r="M860" s="6" t="n"/>
+      <c r="O860" s="6" t="n"/>
     </row>
     <row r="861">
       <c r="E861" s="5" t="n"/>
       <c r="J861" s="5" t="n"/>
       <c r="K861" s="6" t="n"/>
       <c r="M861" s="6" t="n"/>
+      <c r="O861" s="6" t="n"/>
     </row>
     <row r="862">
       <c r="E862" s="5" t="n"/>
       <c r="J862" s="5" t="n"/>
       <c r="K862" s="6" t="n"/>
       <c r="M862" s="6" t="n"/>
+      <c r="O862" s="6" t="n"/>
     </row>
     <row r="863">
       <c r="E863" s="5" t="n"/>
       <c r="J863" s="5" t="n"/>
       <c r="K863" s="6" t="n"/>
       <c r="M863" s="6" t="n"/>
+      <c r="O863" s="6" t="n"/>
     </row>
     <row r="864">
       <c r="E864" s="5" t="n"/>
       <c r="J864" s="5" t="n"/>
       <c r="K864" s="6" t="n"/>
       <c r="M864" s="6" t="n"/>
+      <c r="O864" s="6" t="n"/>
     </row>
     <row r="865">
       <c r="E865" s="5" t="n"/>
       <c r="J865" s="5" t="n"/>
       <c r="K865" s="6" t="n"/>
       <c r="M865" s="6" t="n"/>
+      <c r="O865" s="6" t="n"/>
     </row>
     <row r="866">
       <c r="E866" s="5" t="n"/>
       <c r="J866" s="5" t="n"/>
       <c r="K866" s="6" t="n"/>
       <c r="M866" s="6" t="n"/>
+      <c r="O866" s="6" t="n"/>
     </row>
     <row r="867">
       <c r="E867" s="5" t="n"/>
       <c r="J867" s="5" t="n"/>
       <c r="K867" s="6" t="n"/>
       <c r="M867" s="6" t="n"/>
+      <c r="O867" s="6" t="n"/>
     </row>
     <row r="868">
       <c r="E868" s="5" t="n"/>
       <c r="J868" s="5" t="n"/>
       <c r="K868" s="6" t="n"/>
       <c r="M868" s="6" t="n"/>
+      <c r="O868" s="6" t="n"/>
     </row>
     <row r="869">
       <c r="E869" s="5" t="n"/>
       <c r="J869" s="5" t="n"/>
       <c r="K869" s="6" t="n"/>
       <c r="M869" s="6" t="n"/>
+      <c r="O869" s="6" t="n"/>
     </row>
     <row r="870">
       <c r="E870" s="5" t="n"/>
       <c r="J870" s="5" t="n"/>
       <c r="K870" s="6" t="n"/>
       <c r="M870" s="6" t="n"/>
+      <c r="O870" s="6" t="n"/>
     </row>
     <row r="871">
       <c r="E871" s="5" t="n"/>
       <c r="J871" s="5" t="n"/>
       <c r="K871" s="6" t="n"/>
       <c r="M871" s="6" t="n"/>
+      <c r="O871" s="6" t="n"/>
     </row>
     <row r="872">
       <c r="E872" s="5" t="n"/>
       <c r="J872" s="5" t="n"/>
       <c r="K872" s="6" t="n"/>
       <c r="M872" s="6" t="n"/>
+      <c r="O872" s="6" t="n"/>
     </row>
     <row r="873">
       <c r="E873" s="5" t="n"/>
       <c r="J873" s="5" t="n"/>
       <c r="K873" s="6" t="n"/>
       <c r="M873" s="6" t="n"/>
+      <c r="O873" s="6" t="n"/>
     </row>
     <row r="874">
       <c r="E874" s="5" t="n"/>
       <c r="J874" s="5" t="n"/>
       <c r="K874" s="6" t="n"/>
       <c r="M874" s="6" t="n"/>
+      <c r="O874" s="6" t="n"/>
     </row>
     <row r="875">
       <c r="E875" s="5" t="n"/>
       <c r="J875" s="5" t="n"/>
       <c r="K875" s="6" t="n"/>
       <c r="M875" s="6" t="n"/>
+      <c r="O875" s="6" t="n"/>
     </row>
     <row r="876">
       <c r="E876" s="5" t="n"/>
       <c r="J876" s="5" t="n"/>
       <c r="K876" s="6" t="n"/>
       <c r="M876" s="6" t="n"/>
+      <c r="O876" s="6" t="n"/>
     </row>
     <row r="877">
       <c r="E877" s="5" t="n"/>
       <c r="J877" s="5" t="n"/>
       <c r="K877" s="6" t="n"/>
       <c r="M877" s="6" t="n"/>
+      <c r="O877" s="6" t="n"/>
     </row>
     <row r="878">
       <c r="E878" s="5" t="n"/>
       <c r="J878" s="5" t="n"/>
       <c r="K878" s="6" t="n"/>
       <c r="M878" s="6" t="n"/>
+      <c r="O878" s="6" t="n"/>
     </row>
     <row r="879">
       <c r="E879" s="5" t="n"/>
       <c r="J879" s="5" t="n"/>
       <c r="K879" s="6" t="n"/>
       <c r="M879" s="6" t="n"/>
+      <c r="O879" s="6" t="n"/>
     </row>
     <row r="880">
       <c r="E880" s="5" t="n"/>
       <c r="J880" s="5" t="n"/>
       <c r="K880" s="6" t="n"/>
       <c r="M880" s="6" t="n"/>
+      <c r="O880" s="6" t="n"/>
     </row>
     <row r="881">
       <c r="E881" s="5" t="n"/>
       <c r="J881" s="5" t="n"/>
       <c r="K881" s="6" t="n"/>
       <c r="M881" s="6" t="n"/>
+      <c r="O881" s="6" t="n"/>
     </row>
     <row r="882">
       <c r="E882" s="5" t="n"/>
       <c r="J882" s="5" t="n"/>
       <c r="K882" s="6" t="n"/>
       <c r="M882" s="6" t="n"/>
+      <c r="O882" s="6" t="n"/>
     </row>
     <row r="883">
       <c r="E883" s="5" t="n"/>
       <c r="J883" s="5" t="n"/>
       <c r="K883" s="6" t="n"/>
       <c r="M883" s="6" t="n"/>
+      <c r="O883" s="6" t="n"/>
     </row>
     <row r="884">
       <c r="E884" s="5" t="n"/>
       <c r="J884" s="5" t="n"/>
       <c r="K884" s="6" t="n"/>
       <c r="M884" s="6" t="n"/>
+      <c r="O884" s="6" t="n"/>
     </row>
     <row r="885">
       <c r="E885" s="5" t="n"/>
       <c r="J885" s="5" t="n"/>
       <c r="K885" s="6" t="n"/>
       <c r="M885" s="6" t="n"/>
+      <c r="O885" s="6" t="n"/>
     </row>
     <row r="886">
       <c r="E886" s="5" t="n"/>
       <c r="J886" s="5" t="n"/>
       <c r="K886" s="6" t="n"/>
       <c r="M886" s="6" t="n"/>
+      <c r="O886" s="6" t="n"/>
     </row>
     <row r="887">
       <c r="E887" s="5" t="n"/>
       <c r="J887" s="5" t="n"/>
       <c r="K887" s="6" t="n"/>
       <c r="M887" s="6" t="n"/>
+      <c r="O887" s="6" t="n"/>
     </row>
     <row r="888">
       <c r="E888" s="5" t="n"/>
       <c r="J888" s="5" t="n"/>
       <c r="K888" s="6" t="n"/>
       <c r="M888" s="6" t="n"/>
+      <c r="O888" s="6" t="n"/>
     </row>
     <row r="889">
       <c r="E889" s="5" t="n"/>
       <c r="J889" s="5" t="n"/>
       <c r="K889" s="6" t="n"/>
       <c r="M889" s="6" t="n"/>
+      <c r="O889" s="6" t="n"/>
     </row>
     <row r="890">
       <c r="E890" s="5" t="n"/>
       <c r="J890" s="5" t="n"/>
       <c r="K890" s="6" t="n"/>
       <c r="M890" s="6" t="n"/>
+      <c r="O890" s="6" t="n"/>
     </row>
     <row r="891">
       <c r="E891" s="5" t="n"/>
       <c r="J891" s="5" t="n"/>
       <c r="K891" s="6" t="n"/>
       <c r="M891" s="6" t="n"/>
+      <c r="O891" s="6" t="n"/>
     </row>
     <row r="892">
       <c r="E892" s="5" t="n"/>
       <c r="J892" s="5" t="n"/>
       <c r="K892" s="6" t="n"/>
       <c r="M892" s="6" t="n"/>
+      <c r="O892" s="6" t="n"/>
     </row>
     <row r="893">
       <c r="E893" s="5" t="n"/>
       <c r="J893" s="5" t="n"/>
       <c r="K893" s="6" t="n"/>
       <c r="M893" s="6" t="n"/>
+      <c r="O893" s="6" t="n"/>
     </row>
     <row r="894">
       <c r="E894" s="5" t="n"/>
       <c r="J894" s="5" t="n"/>
       <c r="K894" s="6" t="n"/>
       <c r="M894" s="6" t="n"/>
+      <c r="O894" s="6" t="n"/>
     </row>
     <row r="895">
       <c r="E895" s="5" t="n"/>
       <c r="J895" s="5" t="n"/>
       <c r="K895" s="6" t="n"/>
       <c r="M895" s="6" t="n"/>
+      <c r="O895" s="6" t="n"/>
     </row>
     <row r="896">
       <c r="E896" s="5" t="n"/>
       <c r="J896" s="5" t="n"/>
       <c r="K896" s="6" t="n"/>
       <c r="M896" s="6" t="n"/>
+      <c r="O896" s="6" t="n"/>
     </row>
     <row r="897">
       <c r="E897" s="5" t="n"/>
       <c r="J897" s="5" t="n"/>
       <c r="K897" s="6" t="n"/>
       <c r="M897" s="6" t="n"/>
+      <c r="O897" s="6" t="n"/>
     </row>
     <row r="898">
       <c r="E898" s="5" t="n"/>
       <c r="J898" s="5" t="n"/>
       <c r="K898" s="6" t="n"/>
       <c r="M898" s="6" t="n"/>
+      <c r="O898" s="6" t="n"/>
     </row>
     <row r="899">
       <c r="E899" s="5" t="n"/>
       <c r="J899" s="5" t="n"/>
       <c r="K899" s="6" t="n"/>
       <c r="M899" s="6" t="n"/>
+      <c r="O899" s="6" t="n"/>
     </row>
     <row r="900">
       <c r="E900" s="5" t="n"/>
       <c r="J900" s="5" t="n"/>
       <c r="K900" s="6" t="n"/>
       <c r="M900" s="6" t="n"/>
+      <c r="O900" s="6" t="n"/>
     </row>
     <row r="901">
       <c r="E901" s="5" t="n"/>
       <c r="J901" s="5" t="n"/>
       <c r="K901" s="6" t="n"/>
       <c r="M901" s="6" t="n"/>
+      <c r="O901" s="6" t="n"/>
     </row>
     <row r="902">
       <c r="E902" s="5" t="n"/>
       <c r="J902" s="5" t="n"/>
       <c r="K902" s="6" t="n"/>
       <c r="M902" s="6" t="n"/>
+      <c r="O902" s="6" t="n"/>
     </row>
     <row r="903">
       <c r="E903" s="5" t="n"/>
       <c r="J903" s="5" t="n"/>
       <c r="K903" s="6" t="n"/>
       <c r="M903" s="6" t="n"/>
+      <c r="O903" s="6" t="n"/>
     </row>
     <row r="904">
       <c r="E904" s="5" t="n"/>
       <c r="J904" s="5" t="n"/>
       <c r="K904" s="6" t="n"/>
       <c r="M904" s="6" t="n"/>
+      <c r="O904" s="6" t="n"/>
     </row>
     <row r="905">
       <c r="E905" s="5" t="n"/>
       <c r="J905" s="5" t="n"/>
       <c r="K905" s="6" t="n"/>
       <c r="M905" s="6" t="n"/>
+      <c r="O905" s="6" t="n"/>
     </row>
     <row r="906">
       <c r="E906" s="5" t="n"/>
       <c r="J906" s="5" t="n"/>
       <c r="K906" s="6" t="n"/>
       <c r="M906" s="6" t="n"/>
+      <c r="O906" s="6" t="n"/>
     </row>
     <row r="907">
       <c r="E907" s="5" t="n"/>
       <c r="J907" s="5" t="n"/>
       <c r="K907" s="6" t="n"/>
       <c r="M907" s="6" t="n"/>
+      <c r="O907" s="6" t="n"/>
     </row>
     <row r="908">
       <c r="E908" s="5" t="n"/>
       <c r="J908" s="5" t="n"/>
       <c r="K908" s="6" t="n"/>
       <c r="M908" s="6" t="n"/>
+      <c r="O908" s="6" t="n"/>
     </row>
     <row r="909">
       <c r="E909" s="5" t="n"/>
       <c r="J909" s="5" t="n"/>
       <c r="K909" s="6" t="n"/>
       <c r="M909" s="6" t="n"/>
+      <c r="O909" s="6" t="n"/>
     </row>
     <row r="910">
       <c r="E910" s="5" t="n"/>
       <c r="J910" s="5" t="n"/>
       <c r="K910" s="6" t="n"/>
       <c r="M910" s="6" t="n"/>
+      <c r="O910" s="6" t="n"/>
     </row>
     <row r="911">
       <c r="E911" s="5" t="n"/>
       <c r="J911" s="5" t="n"/>
       <c r="K911" s="6" t="n"/>
       <c r="M911" s="6" t="n"/>
+      <c r="O911" s="6" t="n"/>
     </row>
     <row r="912">
       <c r="E912" s="5" t="n"/>
       <c r="J912" s="5" t="n"/>
       <c r="K912" s="6" t="n"/>
       <c r="M912" s="6" t="n"/>
+      <c r="O912" s="6" t="n"/>
     </row>
     <row r="913">
       <c r="E913" s="5" t="n"/>
       <c r="J913" s="5" t="n"/>
       <c r="K913" s="6" t="n"/>
       <c r="M913" s="6" t="n"/>
+      <c r="O913" s="6" t="n"/>
     </row>
     <row r="914">
       <c r="E914" s="5" t="n"/>
       <c r="J914" s="5" t="n"/>
       <c r="K914" s="6" t="n"/>
       <c r="M914" s="6" t="n"/>
+      <c r="O914" s="6" t="n"/>
     </row>
     <row r="915">
       <c r="E915" s="5" t="n"/>
       <c r="J915" s="5" t="n"/>
       <c r="K915" s="6" t="n"/>
       <c r="M915" s="6" t="n"/>
+      <c r="O915" s="6" t="n"/>
     </row>
     <row r="916">
       <c r="E916" s="5" t="n"/>
       <c r="J916" s="5" t="n"/>
       <c r="K916" s="6" t="n"/>
       <c r="M916" s="6" t="n"/>
+      <c r="O916" s="6" t="n"/>
     </row>
     <row r="917">
       <c r="E917" s="5" t="n"/>
       <c r="J917" s="5" t="n"/>
       <c r="K917" s="6" t="n"/>
       <c r="M917" s="6" t="n"/>
+      <c r="O917" s="6" t="n"/>
     </row>
     <row r="918">
       <c r="E918" s="5" t="n"/>
       <c r="J918" s="5" t="n"/>
       <c r="K918" s="6" t="n"/>
       <c r="M918" s="6" t="n"/>
+      <c r="O918" s="6" t="n"/>
     </row>
     <row r="919">
       <c r="E919" s="5" t="n"/>
       <c r="J919" s="5" t="n"/>
       <c r="K919" s="6" t="n"/>
       <c r="M919" s="6" t="n"/>
+      <c r="O919" s="6" t="n"/>
     </row>
     <row r="920">
       <c r="E920" s="5" t="n"/>
       <c r="J920" s="5" t="n"/>
       <c r="K920" s="6" t="n"/>
       <c r="M920" s="6" t="n"/>
+      <c r="O920" s="6" t="n"/>
     </row>
     <row r="921">
       <c r="E921" s="5" t="n"/>
       <c r="J921" s="5" t="n"/>
       <c r="K921" s="6" t="n"/>
       <c r="M921" s="6" t="n"/>
+      <c r="O921" s="6" t="n"/>
     </row>
     <row r="922">
       <c r="E922" s="5" t="n"/>
       <c r="J922" s="5" t="n"/>
       <c r="K922" s="6" t="n"/>
       <c r="M922" s="6" t="n"/>
+      <c r="O922" s="6" t="n"/>
     </row>
     <row r="923">
       <c r="E923" s="5" t="n"/>
       <c r="J923" s="5" t="n"/>
       <c r="K923" s="6" t="n"/>
       <c r="M923" s="6" t="n"/>
+      <c r="O923" s="6" t="n"/>
     </row>
     <row r="924">
       <c r="E924" s="5" t="n"/>
       <c r="J924" s="5" t="n"/>
       <c r="K924" s="6" t="n"/>
       <c r="M924" s="6" t="n"/>
+      <c r="O924" s="6" t="n"/>
     </row>
     <row r="925">
       <c r="E925" s="5" t="n"/>
       <c r="J925" s="5" t="n"/>
       <c r="K925" s="6" t="n"/>
       <c r="M925" s="6" t="n"/>
+      <c r="O925" s="6" t="n"/>
     </row>
     <row r="926">
       <c r="E926" s="5" t="n"/>
       <c r="J926" s="5" t="n"/>
       <c r="K926" s="6" t="n"/>
       <c r="M926" s="6" t="n"/>
+      <c r="O926" s="6" t="n"/>
     </row>
     <row r="927">
       <c r="E927" s="5" t="n"/>
       <c r="J927" s="5" t="n"/>
       <c r="K927" s="6" t="n"/>
       <c r="M927" s="6" t="n"/>
+      <c r="O927" s="6" t="n"/>
     </row>
     <row r="928">
       <c r="E928" s="5" t="n"/>
       <c r="J928" s="5" t="n"/>
       <c r="K928" s="6" t="n"/>
       <c r="M928" s="6" t="n"/>
+      <c r="O928" s="6" t="n"/>
     </row>
     <row r="929">
       <c r="E929" s="5" t="n"/>
       <c r="J929" s="5" t="n"/>
       <c r="K929" s="6" t="n"/>
       <c r="M929" s="6" t="n"/>
+      <c r="O929" s="6" t="n"/>
     </row>
     <row r="930">
       <c r="E930" s="5" t="n"/>
       <c r="J930" s="5" t="n"/>
       <c r="K930" s="6" t="n"/>
       <c r="M930" s="6" t="n"/>
+      <c r="O930" s="6" t="n"/>
     </row>
     <row r="931">
       <c r="E931" s="5" t="n"/>
       <c r="J931" s="5" t="n"/>
       <c r="K931" s="6" t="n"/>
       <c r="M931" s="6" t="n"/>
+      <c r="O931" s="6" t="n"/>
     </row>
     <row r="932">
       <c r="E932" s="5" t="n"/>
       <c r="J932" s="5" t="n"/>
       <c r="K932" s="6" t="n"/>
       <c r="M932" s="6" t="n"/>
+      <c r="O932" s="6" t="n"/>
     </row>
     <row r="933">
       <c r="E933" s="5" t="n"/>
       <c r="J933" s="5" t="n"/>
       <c r="K933" s="6" t="n"/>
       <c r="M933" s="6" t="n"/>
+      <c r="O933" s="6" t="n"/>
     </row>
     <row r="934">
       <c r="E934" s="5" t="n"/>
       <c r="J934" s="5" t="n"/>
       <c r="K934" s="6" t="n"/>
       <c r="M934" s="6" t="n"/>
+      <c r="O934" s="6" t="n"/>
     </row>
     <row r="935">
       <c r="E935" s="5" t="n"/>
       <c r="J935" s="5" t="n"/>
       <c r="K935" s="6" t="n"/>
       <c r="M935" s="6" t="n"/>
+      <c r="O935" s="6" t="n"/>
     </row>
     <row r="936">
       <c r="E936" s="5" t="n"/>
       <c r="J936" s="5" t="n"/>
       <c r="K936" s="6" t="n"/>
       <c r="M936" s="6" t="n"/>
+      <c r="O936" s="6" t="n"/>
     </row>
     <row r="937">
       <c r="E937" s="5" t="n"/>
       <c r="J937" s="5" t="n"/>
       <c r="K937" s="6" t="n"/>
       <c r="M937" s="6" t="n"/>
+      <c r="O937" s="6" t="n"/>
     </row>
     <row r="938">
       <c r="E938" s="5" t="n"/>
       <c r="J938" s="5" t="n"/>
       <c r="K938" s="6" t="n"/>
       <c r="M938" s="6" t="n"/>
+      <c r="O938" s="6" t="n"/>
     </row>
     <row r="939">
       <c r="E939" s="5" t="n"/>
       <c r="J939" s="5" t="n"/>
       <c r="K939" s="6" t="n"/>
       <c r="M939" s="6" t="n"/>
+      <c r="O939" s="6" t="n"/>
     </row>
     <row r="940">
       <c r="E940" s="5" t="n"/>
       <c r="J940" s="5" t="n"/>
       <c r="K940" s="6" t="n"/>
       <c r="M940" s="6" t="n"/>
+      <c r="O940" s="6" t="n"/>
     </row>
     <row r="941">
       <c r="E941" s="5" t="n"/>
       <c r="J941" s="5" t="n"/>
       <c r="K941" s="6" t="n"/>
       <c r="M941" s="6" t="n"/>
+      <c r="O941" s="6" t="n"/>
     </row>
     <row r="942">
       <c r="E942" s="5" t="n"/>
       <c r="J942" s="5" t="n"/>
       <c r="K942" s="6" t="n"/>
       <c r="M942" s="6" t="n"/>
+      <c r="O942" s="6" t="n"/>
     </row>
     <row r="943">
       <c r="E943" s="5" t="n"/>
       <c r="J943" s="5" t="n"/>
       <c r="K943" s="6" t="n"/>
       <c r="M943" s="6" t="n"/>
+      <c r="O943" s="6" t="n"/>
     </row>
     <row r="944">
       <c r="E944" s="5" t="n"/>
       <c r="J944" s="5" t="n"/>
       <c r="K944" s="6" t="n"/>
       <c r="M944" s="6" t="n"/>
+      <c r="O944" s="6" t="n"/>
     </row>
     <row r="945">
       <c r="E945" s="5" t="n"/>
       <c r="J945" s="5" t="n"/>
       <c r="K945" s="6" t="n"/>
       <c r="M945" s="6" t="n"/>
+      <c r="O945" s="6" t="n"/>
     </row>
     <row r="946">
       <c r="E946" s="5" t="n"/>
       <c r="J946" s="5" t="n"/>
       <c r="K946" s="6" t="n"/>
       <c r="M946" s="6" t="n"/>
+      <c r="O946" s="6" t="n"/>
     </row>
     <row r="947">
       <c r="E947" s="5" t="n"/>
       <c r="J947" s="5" t="n"/>
       <c r="K947" s="6" t="n"/>
       <c r="M947" s="6" t="n"/>
+      <c r="O947" s="6" t="n"/>
     </row>
     <row r="948">
       <c r="E948" s="5" t="n"/>
       <c r="J948" s="5" t="n"/>
       <c r="K948" s="6" t="n"/>
       <c r="M948" s="6" t="n"/>
+      <c r="O948" s="6" t="n"/>
     </row>
     <row r="949">
       <c r="E949" s="5" t="n"/>
       <c r="J949" s="5" t="n"/>
       <c r="K949" s="6" t="n"/>
       <c r="M949" s="6" t="n"/>
+      <c r="O949" s="6" t="n"/>
     </row>
     <row r="950">
       <c r="E950" s="5" t="n"/>
       <c r="J950" s="5" t="n"/>
       <c r="K950" s="6" t="n"/>
       <c r="M950" s="6" t="n"/>
+      <c r="O950" s="6" t="n"/>
     </row>
     <row r="951">
       <c r="E951" s="5" t="n"/>
       <c r="J951" s="5" t="n"/>
       <c r="K951" s="6" t="n"/>
       <c r="M951" s="6" t="n"/>
+      <c r="O951" s="6" t="n"/>
     </row>
     <row r="952">
       <c r="E952" s="5" t="n"/>
       <c r="J952" s="5" t="n"/>
       <c r="K952" s="6" t="n"/>
       <c r="M952" s="6" t="n"/>
+      <c r="O952" s="6" t="n"/>
     </row>
     <row r="953">
       <c r="E953" s="5" t="n"/>
       <c r="J953" s="5" t="n"/>
       <c r="K953" s="6" t="n"/>
       <c r="M953" s="6" t="n"/>
+      <c r="O953" s="6" t="n"/>
     </row>
     <row r="954">
       <c r="E954" s="5" t="n"/>
       <c r="J954" s="5" t="n"/>
       <c r="K954" s="6" t="n"/>
       <c r="M954" s="6" t="n"/>
+      <c r="O954" s="6" t="n"/>
     </row>
     <row r="955">
       <c r="E955" s="5" t="n"/>
       <c r="J955" s="5" t="n"/>
       <c r="K955" s="6" t="n"/>
       <c r="M955" s="6" t="n"/>
+      <c r="O955" s="6" t="n"/>
     </row>
     <row r="956">
       <c r="E956" s="5" t="n"/>
       <c r="J956" s="5" t="n"/>
       <c r="K956" s="6" t="n"/>
       <c r="M956" s="6" t="n"/>
+      <c r="O956" s="6" t="n"/>
     </row>
     <row r="957">
       <c r="E957" s="5" t="n"/>
       <c r="J957" s="5" t="n"/>
       <c r="K957" s="6" t="n"/>
       <c r="M957" s="6" t="n"/>
+      <c r="O957" s="6" t="n"/>
     </row>
     <row r="958">
       <c r="E958" s="5" t="n"/>
       <c r="J958" s="5" t="n"/>
       <c r="K958" s="6" t="n"/>
       <c r="M958" s="6" t="n"/>
+      <c r="O958" s="6" t="n"/>
     </row>
     <row r="959">
       <c r="E959" s="5" t="n"/>
       <c r="J959" s="5" t="n"/>
       <c r="K959" s="6" t="n"/>
       <c r="M959" s="6" t="n"/>
+      <c r="O959" s="6" t="n"/>
     </row>
     <row r="960">
       <c r="E960" s="5" t="n"/>
       <c r="J960" s="5" t="n"/>
       <c r="K960" s="6" t="n"/>
       <c r="M960" s="6" t="n"/>
+      <c r="O960" s="6" t="n"/>
     </row>
     <row r="961">
       <c r="E961" s="5" t="n"/>
       <c r="J961" s="5" t="n"/>
       <c r="K961" s="6" t="n"/>
       <c r="M961" s="6" t="n"/>
+      <c r="O961" s="6" t="n"/>
     </row>
     <row r="962">
       <c r="E962" s="5" t="n"/>
       <c r="J962" s="5" t="n"/>
       <c r="K962" s="6" t="n"/>
       <c r="M962" s="6" t="n"/>
+      <c r="O962" s="6" t="n"/>
     </row>
     <row r="963">
       <c r="E963" s="5" t="n"/>
       <c r="J963" s="5" t="n"/>
       <c r="K963" s="6" t="n"/>
       <c r="M963" s="6" t="n"/>
+      <c r="O963" s="6" t="n"/>
     </row>
     <row r="964">
       <c r="E964" s="5" t="n"/>
       <c r="J964" s="5" t="n"/>
       <c r="K964" s="6" t="n"/>
       <c r="M964" s="6" t="n"/>
+      <c r="O964" s="6" t="n"/>
     </row>
     <row r="965">
       <c r="E965" s="5" t="n"/>
       <c r="J965" s="5" t="n"/>
       <c r="K965" s="6" t="n"/>
       <c r="M965" s="6" t="n"/>
+      <c r="O965" s="6" t="n"/>
     </row>
     <row r="966">
       <c r="E966" s="5" t="n"/>
       <c r="J966" s="5" t="n"/>
       <c r="K966" s="6" t="n"/>
       <c r="M966" s="6" t="n"/>
+      <c r="O966" s="6" t="n"/>
     </row>
     <row r="967">
       <c r="E967" s="5" t="n"/>
       <c r="J967" s="5" t="n"/>
       <c r="K967" s="6" t="n"/>
       <c r="M967" s="6" t="n"/>
+      <c r="O967" s="6" t="n"/>
     </row>
     <row r="968">
       <c r="E968" s="5" t="n"/>
       <c r="J968" s="5" t="n"/>
       <c r="K968" s="6" t="n"/>
       <c r="M968" s="6" t="n"/>
+      <c r="O968" s="6" t="n"/>
     </row>
     <row r="969">
       <c r="E969" s="5" t="n"/>
       <c r="J969" s="5" t="n"/>
       <c r="K969" s="6" t="n"/>
       <c r="M969" s="6" t="n"/>
+      <c r="O969" s="6" t="n"/>
     </row>
     <row r="970">
       <c r="E970" s="5" t="n"/>
       <c r="J970" s="5" t="n"/>
       <c r="K970" s="6" t="n"/>
       <c r="M970" s="6" t="n"/>
+      <c r="O970" s="6" t="n"/>
     </row>
     <row r="971">
       <c r="E971" s="5" t="n"/>
       <c r="J971" s="5" t="n"/>
       <c r="K971" s="6" t="n"/>
       <c r="M971" s="6" t="n"/>
+      <c r="O971" s="6" t="n"/>
     </row>
     <row r="972">
       <c r="E972" s="5" t="n"/>
       <c r="J972" s="5" t="n"/>
       <c r="K972" s="6" t="n"/>
       <c r="M972" s="6" t="n"/>
+      <c r="O972" s="6" t="n"/>
     </row>
     <row r="973">
       <c r="E973" s="5" t="n"/>
       <c r="J973" s="5" t="n"/>
       <c r="K973" s="6" t="n"/>
       <c r="M973" s="6" t="n"/>
+      <c r="O973" s="6" t="n"/>
     </row>
     <row r="974">
       <c r="E974" s="5" t="n"/>
       <c r="J974" s="5" t="n"/>
       <c r="K974" s="6" t="n"/>
       <c r="M974" s="6" t="n"/>
+      <c r="O974" s="6" t="n"/>
     </row>
     <row r="975">
       <c r="E975" s="5" t="n"/>
       <c r="J975" s="5" t="n"/>
       <c r="K975" s="6" t="n"/>
       <c r="M975" s="6" t="n"/>
+      <c r="O975" s="6" t="n"/>
     </row>
     <row r="976">
       <c r="E976" s="5" t="n"/>
       <c r="J976" s="5" t="n"/>
       <c r="K976" s="6" t="n"/>
       <c r="M976" s="6" t="n"/>
+      <c r="O976" s="6" t="n"/>
     </row>
     <row r="977">
       <c r="E977" s="5" t="n"/>
       <c r="J977" s="5" t="n"/>
       <c r="K977" s="6" t="n"/>
       <c r="M977" s="6" t="n"/>
+      <c r="O977" s="6" t="n"/>
     </row>
     <row r="978">
       <c r="E978" s="5" t="n"/>
       <c r="J978" s="5" t="n"/>
       <c r="K978" s="6" t="n"/>
       <c r="M978" s="6" t="n"/>
+      <c r="O978" s="6" t="n"/>
     </row>
     <row r="979">
       <c r="E979" s="5" t="n"/>
       <c r="J979" s="5" t="n"/>
       <c r="K979" s="6" t="n"/>
       <c r="M979" s="6" t="n"/>
+      <c r="O979" s="6" t="n"/>
     </row>
     <row r="980">
       <c r="E980" s="5" t="n"/>
       <c r="J980" s="5" t="n"/>
       <c r="K980" s="6" t="n"/>
       <c r="M980" s="6" t="n"/>
+      <c r="O980" s="6" t="n"/>
     </row>
     <row r="981">
       <c r="E981" s="5" t="n"/>
       <c r="J981" s="5" t="n"/>
       <c r="K981" s="6" t="n"/>
       <c r="M981" s="6" t="n"/>
+      <c r="O981" s="6" t="n"/>
     </row>
     <row r="982">
       <c r="E982" s="5" t="n"/>
       <c r="J982" s="5" t="n"/>
       <c r="K982" s="6" t="n"/>
       <c r="M982" s="6" t="n"/>
+      <c r="O982" s="6" t="n"/>
     </row>
     <row r="983">
       <c r="E983" s="5" t="n"/>
       <c r="J983" s="5" t="n"/>
       <c r="K983" s="6" t="n"/>
       <c r="M983" s="6" t="n"/>
+      <c r="O983" s="6" t="n"/>
     </row>
     <row r="984">
       <c r="E984" s="5" t="n"/>
       <c r="J984" s="5" t="n"/>
       <c r="K984" s="6" t="n"/>
       <c r="M984" s="6" t="n"/>
+      <c r="O984" s="6" t="n"/>
     </row>
     <row r="985">
       <c r="E985" s="5" t="n"/>
       <c r="J985" s="5" t="n"/>
       <c r="K985" s="6" t="n"/>
       <c r="M985" s="6" t="n"/>
+      <c r="O985" s="6" t="n"/>
     </row>
     <row r="986">
       <c r="E986" s="5" t="n"/>
       <c r="J986" s="5" t="n"/>
       <c r="K986" s="6" t="n"/>
       <c r="M986" s="6" t="n"/>
+      <c r="O986" s="6" t="n"/>
     </row>
     <row r="987">
       <c r="E987" s="5" t="n"/>
       <c r="J987" s="5" t="n"/>
       <c r="K987" s="6" t="n"/>
       <c r="M987" s="6" t="n"/>
+      <c r="O987" s="6" t="n"/>
     </row>
     <row r="988">
       <c r="E988" s="5" t="n"/>
       <c r="J988" s="5" t="n"/>
       <c r="K988" s="6" t="n"/>
       <c r="M988" s="6" t="n"/>
+      <c r="O988" s="6" t="n"/>
     </row>
     <row r="989">
       <c r="E989" s="5" t="n"/>
       <c r="J989" s="5" t="n"/>
       <c r="K989" s="6" t="n"/>
       <c r="M989" s="6" t="n"/>
+      <c r="O989" s="6" t="n"/>
     </row>
     <row r="990">
       <c r="E990" s="5" t="n"/>
       <c r="J990" s="5" t="n"/>
       <c r="K990" s="6" t="n"/>
       <c r="M990" s="6" t="n"/>
+      <c r="O990" s="6" t="n"/>
     </row>
     <row r="991">
       <c r="E991" s="5" t="n"/>
       <c r="J991" s="5" t="n"/>
       <c r="K991" s="6" t="n"/>
       <c r="M991" s="6" t="n"/>
+      <c r="O991" s="6" t="n"/>
     </row>
     <row r="992">
       <c r="E992" s="5" t="n"/>
       <c r="J992" s="5" t="n"/>
       <c r="K992" s="6" t="n"/>
       <c r="M992" s="6" t="n"/>
+      <c r="O992" s="6" t="n"/>
     </row>
     <row r="993">
       <c r="E993" s="5" t="n"/>
       <c r="J993" s="5" t="n"/>
       <c r="K993" s="6" t="n"/>
       <c r="M993" s="6" t="n"/>
+      <c r="O993" s="6" t="n"/>
     </row>
     <row r="994">
       <c r="E994" s="5" t="n"/>
       <c r="J994" s="5" t="n"/>
       <c r="K994" s="6" t="n"/>
       <c r="M994" s="6" t="n"/>
+      <c r="O994" s="6" t="n"/>
     </row>
     <row r="995">
       <c r="E995" s="5" t="n"/>
       <c r="J995" s="5" t="n"/>
       <c r="K995" s="6" t="n"/>
       <c r="M995" s="6" t="n"/>
+      <c r="O995" s="6" t="n"/>
     </row>
     <row r="996">
       <c r="E996" s="5" t="n"/>
       <c r="J996" s="5" t="n"/>
       <c r="K996" s="6" t="n"/>
       <c r="M996" s="6" t="n"/>
+      <c r="O996" s="6" t="n"/>
     </row>
     <row r="997">
       <c r="E997" s="5" t="n"/>
       <c r="J997" s="5" t="n"/>
       <c r="K997" s="6" t="n"/>
       <c r="M997" s="6" t="n"/>
+      <c r="O997" s="6" t="n"/>
     </row>
     <row r="998">
       <c r="E998" s="5" t="n"/>
       <c r="J998" s="5" t="n"/>
       <c r="K998" s="6" t="n"/>
       <c r="M998" s="6" t="n"/>
+      <c r="O998" s="6" t="n"/>
     </row>
     <row r="999">
       <c r="E999" s="5" t="n"/>
       <c r="J999" s="5" t="n"/>
       <c r="K999" s="6" t="n"/>
       <c r="M999" s="6" t="n"/>
+      <c r="O999" s="6" t="n"/>
     </row>
     <row r="1000">
       <c r="E1000" s="5" t="n"/>
       <c r="J1000" s="5" t="n"/>
       <c r="K1000" s="6" t="n"/>
       <c r="M1000" s="6" t="n"/>
+      <c r="O1000" s="6" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unknown role" error="Choose a role from the list (election lookup definitions)." promptTitle="Role" prompt="Office from the election lookup definitions, or Member." type="list">
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unknown role" error="Choose a role from the list (election lookup definitions)." promptTitle="Role" prompt="Office from the election lookup definitions, or Member." type="list">
       <formula1>=Lists!$A$2:$A$22</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Charter Member" error="Choose Yes or No." type="list">
@@ -6633,7 +7640,7 @@
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Member Number" error="Member Number is a whole number above 0." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000 M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date" error="Enter a date (YYYY-MM-DD)." type="date" operator="greaterThan">
+    <dataValidation sqref="K2:K1000 M2:M1000 O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Date" error="Enter a date (YYYY-MM-DD)." type="date" operator="greaterThan">
       <formula1>DATE(1882,3,29)</formula1>
     </dataValidation>
   </dataValidations>
@@ -6830,7 +7837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7034,10 +8041,22 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
+          <t>First Degree Date</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Optional. The First Degree / Initiation Date from Supreme (YYYY-MM-DD). Drives the merit tiers; a date within 30 days of the council institution date marks a charter member.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>Planning aid only, from the drop-down. The import does not assign offices: fill them through elections and the Grand Knight's appointments.</t>
         </is>
